--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,32 +468,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="B2" t="b">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01487831093686012</v>
+        <v>3.087407458217597e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9848690542994365</v>
+        <v>0.0004454550784634666</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002526347637033592</v>
+        <v>0.9995542361807908</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B3" t="b">
@@ -503,22 +503,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8711690313982517</v>
+        <v>0.4914004173276788</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1106877979123835</v>
+        <v>1.76298911609951e-21</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0181431706893647</v>
+        <v>0.5085995826723212</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="B4" t="b">
@@ -531,19 +531,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9540545094958949</v>
+        <v>0.9923109997065596</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002807242753091349</v>
+        <v>3.164110014493942e-31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04566476622879603</v>
+        <v>0.007689000293440389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="B5" t="b">
@@ -556,19 +556,19 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008573369008223228</v>
+        <v>5.591281972096291e-41</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9991271278483522</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.553525082548828e-05</v>
+        <v>1.802842715030217e-22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="B6" t="b">
@@ -581,69 +581,69 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9654560535928789</v>
+        <v>0.9999832426546784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007727555779536036</v>
+        <v>1.306677823309202e-38</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02681639062758501</v>
+        <v>1.67573453217262e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="B7" t="b">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9226368474428683</v>
+        <v>0.009466166955558028</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04985481641676101</v>
+        <v>1.044460087014875e-17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02750833614037066</v>
+        <v>0.990533833044442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="B8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4494793559583735</v>
+        <v>0.8398950809379471</v>
       </c>
       <c r="F8" t="n">
-        <v>1.850908566288664e-05</v>
+        <v>1.578134166518372e-33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5505021349559636</v>
+        <v>0.1601049190620529</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B9" t="b">
@@ -656,69 +656,69 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3235681196957009</v>
+        <v>4.098311769095971e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002916811157976414</v>
+        <v>1.389305986185035e-13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6735150691463226</v>
+        <v>0.9999999590167433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="B10" t="b">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3100136146546491</v>
+        <v>0.9997911998552943</v>
       </c>
       <c r="F10" t="n">
-        <v>9.251689784047635e-08</v>
+        <v>5.202797010085763e-46</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6899862928284531</v>
+        <v>0.0002088001447057823</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="B11" t="b">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4549337988709731</v>
+        <v>0.9969974431840656</v>
       </c>
       <c r="F11" t="n">
-        <v>1.26089577140717e-07</v>
+        <v>7.199514498689118e-42</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5450660750394498</v>
+        <v>0.00300255681593442</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="B12" t="b">
@@ -731,48 +731,48 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2404785955764892</v>
+        <v>2.611832215504022e-11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.126118857017671</v>
+        <v>3.501167734718652e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6334025474058398</v>
+        <v>0.9999649882965345</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3318880725519352</v>
+        <v>2.010106612071253e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00742943265197482</v>
+        <v>1.548740374912976e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6606824947960901</v>
+        <v>0.9999979898933877</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="B14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -781,19 +781,19 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7992675997067096</v>
+        <v>0.8080806095201328</v>
       </c>
       <c r="F14" t="n">
-        <v>1.373821357853867e-05</v>
+        <v>2.574192200577748e-30</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2007186620797119</v>
+        <v>0.1919193904798671</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="B15" t="b">
@@ -806,19 +806,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4170311180001376</v>
+        <v>0.004567424675958377</v>
       </c>
       <c r="F15" t="n">
-        <v>1.158058085811164e-05</v>
+        <v>1.307425154089226e-26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5829573014190044</v>
+        <v>0.9954325753240416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="B16" t="b">
@@ -831,44 +831,44 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5.430714272179665e-06</v>
+        <v>7.032263721216192e-49</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999924200467657</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.149238962149512e-06</v>
+        <v>1.330922383340078e-27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7267036568232763</v>
+        <v>2.928582176072454e-06</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0003459419143945563</v>
+        <v>1.502098810388144e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2729504012623292</v>
+        <v>0.9999970714178238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="B18" t="b">
@@ -881,19 +881,19 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.029413450115589e-05</v>
+        <v>4.550041318435578e-33</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999820527228547</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>7.653142644257887e-06</v>
+        <v>9.738331216437072e-17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="B19" t="b">
@@ -906,98 +906,98 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5.340584443524183e-05</v>
+        <v>7.541212149956982e-52</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999095210622415</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3.707309332330635e-05</v>
+        <v>2.658079960030139e-29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="B20" t="b">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7975442684059808</v>
+        <v>0.005432446568790727</v>
       </c>
       <c r="F20" t="n">
-        <v>1.21228178840397e-05</v>
+        <v>2.712763681233794e-23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2024436087761351</v>
+        <v>0.9945675534312093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="B21" t="b">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4374954160821675</v>
+        <v>9.530089124385959e-15</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3188777145754799</v>
+        <v>0.878740970287779</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2436268693423525</v>
+        <v>0.1212590297122116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="B22" t="b">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8172988284473712</v>
+        <v>1.947223043681752e-07</v>
       </c>
       <c r="F22" t="n">
-        <v>3.826978630159386e-06</v>
+        <v>3.702775517301102e-15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1826973445739986</v>
+        <v>0.9999998052776919</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="B23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -1006,19 +1006,19 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00836434685723909</v>
+        <v>1.214525477926596e-14</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9890230215271709</v>
+        <v>0.9980637300967947</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002612631615590071</v>
+        <v>0.001936269903193108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="B24" t="b">
@@ -1031,23 +1031,23 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.007548583501765e-08</v>
+        <v>1.866588397325232e-79</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999999797484538</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1.760605825084686e-10</v>
+        <v>2.516254454230679e-51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -1056,19 +1056,19 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.825246633247909e-05</v>
+        <v>8.661513651670974e-32</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999813665299389</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>3.810037287462259e-07</v>
+        <v>3.271755151167421e-17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B26" t="b">
@@ -1081,19 +1081,19 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>8.879276523289411e-07</v>
+        <v>4.188245128938946e-42</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999990339835166</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.808883099327338e-08</v>
+        <v>5.765329706443533e-24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="B27" t="b">
@@ -1106,19 +1106,19 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.845697195251089e-11</v>
+        <v>1.821732616404615e-57</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9999999999615343</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>8.557295210991896e-15</v>
+        <v>1.560970380667772e-37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B28" t="b">
@@ -1131,23 +1131,23 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.006978757123890844</v>
+        <v>1.552559975159302e-29</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9904446089285911</v>
+        <v>0.9999999999999027</v>
       </c>
       <c r="G28" t="n">
-        <v>0.002576633947518036</v>
+        <v>9.733214621016334e-14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
@@ -1156,23 +1156,23 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>4.423731254808763e-09</v>
+        <v>2.741206003103437e-38</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9999999955761854</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>8.318683072902986e-14</v>
+        <v>6.813549918722915e-22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="B30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -1181,44 +1181,44 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.119111423094613e-07</v>
+        <v>1.854326531038739e-22</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9999995646986414</v>
+        <v>0.9999999997533553</v>
       </c>
       <c r="G30" t="n">
-        <v>2.339021633336265e-08</v>
+        <v>2.466447232439013e-10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="B31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0003620298644050648</v>
+        <v>4.750234082104595e-44</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9994948776725275</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001430924630675426</v>
+        <v>8.243439691575271e-24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="B32" t="b">
@@ -1231,44 +1231,44 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>1.438005130553574e-06</v>
+        <v>4.612486712971901e-57</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9999978496594985</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>7.123353710875429e-07</v>
+        <v>7.894664766377426e-33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.08060227257193432</v>
+        <v>6.712395074666319e-31</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9193846727981806</v>
+        <v>0.9999999999999725</v>
       </c>
       <c r="G33" t="n">
-        <v>1.305462988501398e-05</v>
+        <v>2.743268276460132e-14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="B34" t="b">
@@ -1281,69 +1281,69 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1.024878354184139e-07</v>
+        <v>2.449532166197732e-73</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9999998863718402</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1.114032439152578e-08</v>
+        <v>7.416023577513104e-45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="B35" t="b">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9778240781778847</v>
+        <v>0.0005415236098069511</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00168510258562073</v>
+        <v>3.249461217081503e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02049081923649469</v>
+        <v>0.9994584763901927</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="B36" t="b">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9914328366897376</v>
+        <v>2.116637667430632e-07</v>
       </c>
       <c r="F36" t="n">
-        <v>0.005374461271092952</v>
+        <v>1.138747628527472e-08</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003192702039169418</v>
+        <v>0.999999776948757</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="B37" t="b">
@@ -1356,19 +1356,19 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>5.209502437628167e-07</v>
+        <v>2.496750149940891e-52</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9999994612666974</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1.778305882111941e-08</v>
+        <v>7.317863530130667e-32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="B38" t="b">
@@ -1381,19 +1381,19 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>1.71795882054132e-05</v>
+        <v>3.912093025267857e-38</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9999803590401407</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>2.461371653890721e-06</v>
+        <v>6.994537947584044e-21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="B39" t="b">
@@ -1406,19 +1406,19 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.362781405774266e-10</v>
+        <v>9.244763094430002e-71</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9999999998635944</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1.274426032276716e-13</v>
+        <v>5.601077577127239e-46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="B40" t="b">
@@ -1431,19 +1431,19 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0009919627968647288</v>
+        <v>5.736727069363971e-14</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9990074711257558</v>
+        <v>0.9995190353988762</v>
       </c>
       <c r="G40" t="n">
-        <v>5.66077379337709e-07</v>
+        <v>0.000480964601066419</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="B41" t="b">
@@ -1456,19 +1456,19 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.05161301089508924</v>
+        <v>9.231325602973444e-34</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9446633460211717</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.003723643083739045</v>
+        <v>4.376575301819715e-17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="B42" t="b">
@@ -1481,19 +1481,19 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.675956874159316e-06</v>
+        <v>6.686264696723161e-22</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9999940215326455</v>
+        <v>0.9999999997206745</v>
       </c>
       <c r="G42" t="n">
-        <v>3.025104805221073e-07</v>
+        <v>2.793255549220871e-10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="B43" t="b">
@@ -1506,23 +1506,23 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>6.903946303294208e-06</v>
+        <v>4.64346560390073e-38</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9999926904195207</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>4.056341761853388e-07</v>
+        <v>3.530453362548754e-21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="B44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
@@ -1531,48 +1531,48 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>0.002660900360722133</v>
+        <v>1.850466482091454e-25</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9971060151655772</v>
+        <v>0.9999999999890814</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0002330844737008179</v>
+        <v>1.091856927324187e-11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="B45" t="b">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.980115496397667</v>
+        <v>2.409930092011533e-08</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0003233947430020265</v>
+        <v>2.242707565813235e-08</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01956110885933092</v>
+        <v>0.9999999534736234</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="B46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -1581,23 +1581,23 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0008740448592348439</v>
+        <v>4.662958791025905e-11</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9990905847484745</v>
+        <v>0.9773731871994982</v>
       </c>
       <c r="G46" t="n">
-        <v>3.537039229063912e-05</v>
+        <v>0.02262681275387213</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="B47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1606,19 +1606,19 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9308010431704465</v>
+        <v>0.8360529835718359</v>
       </c>
       <c r="F47" t="n">
-        <v>6.174869961613486e-06</v>
+        <v>6.684541515823535e-35</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06919278195959194</v>
+        <v>0.1639470164281642</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="B48" t="b">
@@ -1631,19 +1631,19 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5108324107483413</v>
+        <v>0.9756114387067848</v>
       </c>
       <c r="F48" t="n">
-        <v>6.512258686082535e-07</v>
+        <v>3.009361454726731e-38</v>
       </c>
       <c r="G48" t="n">
-        <v>0.48916693802579</v>
+        <v>0.02438856129321522</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B49" t="b">
@@ -1656,44 +1656,44 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6116801065997893</v>
+        <v>0.9995526880205594</v>
       </c>
       <c r="F49" t="n">
-        <v>3.711260240836151e-07</v>
+        <v>6.905400780465352e-45</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3883195222741865</v>
+        <v>0.000447311979440594</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="B50" t="b">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9231581408855336</v>
+        <v>0.0001097655519664342</v>
       </c>
       <c r="F50" t="n">
-        <v>9.772987397684056e-06</v>
+        <v>5.056432567670912e-22</v>
       </c>
       <c r="G50" t="n">
-        <v>0.07683208612706867</v>
+        <v>0.9998902344480335</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B51" t="b">
@@ -1703,22 +1703,22 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5287840691012985</v>
+        <v>2.242107158608158e-08</v>
       </c>
       <c r="F51" t="n">
-        <v>0.07405375053826374</v>
+        <v>6.625979709576053e-11</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3971621803604378</v>
+        <v>0.9999999775126686</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="B52" t="b">
@@ -1731,69 +1731,69 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.899738840962532</v>
+        <v>0.5435522104524301</v>
       </c>
       <c r="F52" t="n">
-        <v>1.379415294423925e-06</v>
+        <v>1.245777059550773e-33</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1002597796221737</v>
+        <v>0.45644778954757</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="B53" t="b">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9200573123253838</v>
+        <v>0.0009960660605856984</v>
       </c>
       <c r="F53" t="n">
-        <v>3.106451315277456e-06</v>
+        <v>7.85149837273157e-25</v>
       </c>
       <c r="G53" t="n">
-        <v>0.07993958122330075</v>
+        <v>0.9990039339394142</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="B54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00434672916813738</v>
+        <v>3.82586783687399e-06</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9910411929109547</v>
+        <v>1.214665132238641e-12</v>
       </c>
       <c r="G54" t="n">
-        <v>0.004612077920907683</v>
+        <v>0.9999961741309483</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="B55" t="b">
@@ -1806,44 +1806,44 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6210505148288504</v>
+        <v>0.999983015933076</v>
       </c>
       <c r="F55" t="n">
-        <v>5.69299352637896e-07</v>
+        <v>3.054583183313724e-48</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3789489158717969</v>
+        <v>1.698406692397459e-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B56" t="b">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2991889492749532</v>
+        <v>3.061297653740543e-05</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4352211723755948</v>
+        <v>2.487595470297807e-16</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2655898783494521</v>
+        <v>0.9999693870234623</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="B57" t="b">
@@ -1856,219 +1856,219 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9543281064738596</v>
+        <v>0.8033121004772862</v>
       </c>
       <c r="F57" t="n">
-        <v>2.442323986675186e-05</v>
+        <v>3.166693409134696e-33</v>
       </c>
       <c r="G57" t="n">
-        <v>0.04564747028627369</v>
+        <v>0.1966878995227138</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6116277717879361</v>
+        <v>5.173938765476805e-07</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02200407466492656</v>
+        <v>1.34074020420173e-14</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3663681535471373</v>
+        <v>0.9999994826061099</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9584179505649902</v>
+        <v>0.0004766501040335004</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0002989282270360484</v>
+        <v>9.499084300941895e-24</v>
       </c>
       <c r="G59" t="n">
-        <v>0.04128312120797374</v>
+        <v>0.9995233498959665</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1472522578906352</v>
+        <v>1.039839269974045e-16</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8196102013652803</v>
+        <v>0.9992839879545359</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0331375407440845</v>
+        <v>0.0007160120454640274</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5889079192382201</v>
+        <v>0.9999829829335232</v>
       </c>
       <c r="F61" t="n">
-        <v>3.04786279996106e-07</v>
+        <v>1.460641766532878e-48</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4110917759754999</v>
+        <v>1.701706647690897e-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9499614438582766</v>
+        <v>6.090220025578483e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>2.434284273834917e-06</v>
+        <v>2.819620327627155e-20</v>
       </c>
       <c r="G62" t="n">
-        <v>0.05003612185744966</v>
+        <v>0.9999939097799744</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7115994437105554</v>
+        <v>0.0004537031833414897</v>
       </c>
       <c r="F63" t="n">
-        <v>2.804522028907466e-07</v>
+        <v>6.399441533796586e-24</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2884002758372416</v>
+        <v>0.9995462968166585</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="B64" t="b">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9640570873913451</v>
+        <v>0.08231868989932635</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03469864050056865</v>
+        <v>1.615892381075924e-20</v>
       </c>
       <c r="G64" t="n">
-        <v>0.00124427210808625</v>
+        <v>0.9176813101006738</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="B65" t="b">
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9667674853046506</v>
+        <v>6.511345487142944e-12</v>
       </c>
       <c r="F65" t="n">
-        <v>0.03166280456430811</v>
+        <v>0.9375361035892245</v>
       </c>
       <c r="G65" t="n">
-        <v>0.001569710131041142</v>
+        <v>0.06246389640426421</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="B66" t="b">
@@ -2081,94 +2081,94 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.115804830302644e-06</v>
+        <v>2.076738695538381e-32</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9999947978326452</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>8.63625244606478e-08</v>
+        <v>7.076261280490595e-18</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="B67" t="b">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9909508920062944</v>
+        <v>1.69893924574503e-06</v>
       </c>
       <c r="F67" t="n">
-        <v>0.003631903306080793</v>
+        <v>4.246651756084691e-10</v>
       </c>
       <c r="G67" t="n">
-        <v>0.005417204687624752</v>
+        <v>0.999998300636089</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="B68" t="b">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9682209504199204</v>
+        <v>6.509050868844883e-07</v>
       </c>
       <c r="F68" t="n">
-        <v>0.02500796533093347</v>
+        <v>8.915521145545311e-08</v>
       </c>
       <c r="G68" t="n">
-        <v>0.006771084249146106</v>
+        <v>0.9999992599397017</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="B69" t="b">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9673519539432662</v>
+        <v>1.499554926941969e-06</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02595914217147752</v>
+        <v>1.478246291271676e-08</v>
       </c>
       <c r="G69" t="n">
-        <v>0.006688903885256232</v>
+        <v>0.9999984856626103</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="B70" t="b">
@@ -2181,44 +2181,44 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>2.768108091423718e-07</v>
+        <v>1.070463232524215e-36</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9999997227354431</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>4.537476626786121e-10</v>
+        <v>1.01490891292299e-20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="B71" t="b">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9861842234502115</v>
+        <v>3.809032252351955e-07</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01267653064789989</v>
+        <v>1.889492028984095e-07</v>
       </c>
       <c r="G71" t="n">
-        <v>0.001139245901888722</v>
+        <v>0.999999430147572</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="B72" t="b">
@@ -2231,69 +2231,69 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.709765144412378e-07</v>
+        <v>1.332162093615787e-23</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9999998264022055</v>
+        <v>0.9999999999931404</v>
       </c>
       <c r="G72" t="n">
-        <v>2.621279987864779e-09</v>
+        <v>6.859644616125063e-12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="B73" t="b">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9845160565071136</v>
+        <v>0.0005404850378843065</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01491091189137772</v>
+        <v>3.111546525476096e-16</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0005730316015086628</v>
+        <v>0.9994595149621154</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="B74" t="b">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9787808199485336</v>
+        <v>5.448752294323436e-05</v>
       </c>
       <c r="F74" t="n">
-        <v>0.002884233156534599</v>
+        <v>2.297234455560046e-14</v>
       </c>
       <c r="G74" t="n">
-        <v>0.01833494689493189</v>
+        <v>0.9999455124770338</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="B75" t="b">
@@ -2306,119 +2306,119 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8937518002067906</v>
+        <v>0.7540090075931345</v>
       </c>
       <c r="F75" t="n">
-        <v>0.03591561623621066</v>
+        <v>2.564504534703931e-28</v>
       </c>
       <c r="G75" t="n">
-        <v>0.07033258355699884</v>
+        <v>0.2459909924068655</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="B76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0105653863090689</v>
+        <v>0.2911907455286852</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9893360331645505</v>
+        <v>5.919258866282412e-18</v>
       </c>
       <c r="G76" t="n">
-        <v>9.85805263805592e-05</v>
+        <v>0.7088092544713148</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="B77" t="b">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9515847882491331</v>
+        <v>0.008041753323046859</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0001238363425536737</v>
+        <v>9.847088980091378e-21</v>
       </c>
       <c r="G77" t="n">
-        <v>0.04829137540831341</v>
+        <v>0.9919582466769531</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="B78" t="b">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9874824278101167</v>
+        <v>1.370962407278819e-07</v>
       </c>
       <c r="F78" t="n">
-        <v>0.002978252421063163</v>
+        <v>2.646776667457095e-08</v>
       </c>
       <c r="G78" t="n">
-        <v>0.009539319768820267</v>
+        <v>0.9999998364359927</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="B79" t="b">
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>0.945100848052476</v>
+        <v>0.1863344487229622</v>
       </c>
       <c r="F79" t="n">
-        <v>0.05417626745257415</v>
+        <v>1.111579768986998e-20</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0007228844949499253</v>
+        <v>0.8136655512770379</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="B80" t="b">
@@ -2431,94 +2431,94 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0.05591459964955948</v>
+        <v>1.485460179297859e-27</v>
       </c>
       <c r="F80" t="n">
-        <v>0.942410665787234</v>
+        <v>0.9999999999990239</v>
       </c>
       <c r="G80" t="n">
-        <v>0.001674734563206597</v>
+        <v>9.760144507991976e-13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="B81" t="b">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9916617069893593</v>
+        <v>0.0002919310404194629</v>
       </c>
       <c r="F81" t="n">
-        <v>0.005337075678950143</v>
+        <v>2.452888329343602e-15</v>
       </c>
       <c r="G81" t="n">
-        <v>0.003001217331690472</v>
+        <v>0.9997080689595781</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="B82" t="b">
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9804737736860815</v>
+        <v>6.465432783197535e-06</v>
       </c>
       <c r="F82" t="n">
-        <v>0.004776405663702375</v>
+        <v>1.448131979287122e-11</v>
       </c>
       <c r="G82" t="n">
-        <v>0.01474982065021635</v>
+        <v>0.9999935345527354</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="B83" t="b">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9973226248288171</v>
+        <v>9.378264415970747e-05</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0008674581752458279</v>
+        <v>1.639093629470576e-16</v>
       </c>
       <c r="G83" t="n">
-        <v>0.001809916995937232</v>
+        <v>0.9999062173558402</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="B84" t="b">
@@ -2531,298 +2531,298 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9539689115572653</v>
+        <v>0.9999700030151101</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0002186243770189943</v>
+        <v>6.840333330053895e-40</v>
       </c>
       <c r="G84" t="n">
-        <v>0.04581246406571574</v>
+        <v>2.999698488987039e-05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="B85" t="b">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9750986342392051</v>
+        <v>0.008816815158721828</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0006058095534009359</v>
+        <v>2.112859645551748e-19</v>
       </c>
       <c r="G85" t="n">
-        <v>0.02429555620739413</v>
+        <v>0.9911831848412781</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="B86" t="b">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6542824786532893</v>
+        <v>3.937150495322335e-08</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1829193803966292</v>
+        <v>5.225455912077447e-09</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1627981409500814</v>
+        <v>0.9999999554030392</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="B87" t="b">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9519008084520642</v>
+        <v>1.504606661244661e-08</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0001967884449050045</v>
+        <v>9.518957474908841e-11</v>
       </c>
       <c r="G87" t="n">
-        <v>0.04790240310303075</v>
+        <v>0.9999999848587438</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="B88" t="b">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>0.73405071354517</v>
+        <v>2.43576425308378e-07</v>
       </c>
       <c r="F88" t="n">
-        <v>8.507592698626228e-05</v>
+        <v>4.032627471506166e-15</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2658642105278437</v>
+        <v>0.9999997564235705</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="B89" t="b">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9407434303979693</v>
+        <v>3.892226183128858e-07</v>
       </c>
       <c r="F89" t="n">
-        <v>5.727472821060668e-05</v>
+        <v>4.3181631310833e-15</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0591992948738202</v>
+        <v>0.9999996107773773</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="B90" t="b">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9592363092242611</v>
+        <v>4.208423940005464e-05</v>
       </c>
       <c r="F90" t="n">
-        <v>4.930486999191265e-05</v>
+        <v>1.235115760372905e-20</v>
       </c>
       <c r="G90" t="n">
-        <v>0.04071438590574707</v>
+        <v>0.9999579157605999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="B91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7871024560842821</v>
+        <v>0.006908100178166612</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0003357831302574726</v>
+        <v>1.348444969893505e-22</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2125617607854604</v>
+        <v>0.9930918998218333</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="B92" t="b">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7950899825725248</v>
+        <v>8.225942999573415e-05</v>
       </c>
       <c r="F92" t="n">
-        <v>4.908340832446081e-06</v>
+        <v>8.956827761626626e-17</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2049051090866426</v>
+        <v>0.9999177405700043</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7594105957389029</v>
+        <v>0.0006132722338878922</v>
       </c>
       <c r="F93" t="n">
-        <v>0.01651120805067401</v>
+        <v>2.10242000719677e-22</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2240781962104231</v>
+        <v>0.9993867277661121</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="B94" t="b">
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>0.777784677416917</v>
+        <v>3.421276814224403e-06</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05430665094308901</v>
+        <v>1.162136828010865e-13</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1679086716399939</v>
+        <v>0.9999965787230697</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>0.854216244297216</v>
+        <v>4.452045330423855e-09</v>
       </c>
       <c r="F95" t="n">
-        <v>1.84951081946398e-06</v>
+        <v>3.624817801607503e-07</v>
       </c>
       <c r="G95" t="n">
-        <v>0.1457819061919644</v>
+        <v>0.9999996330661746</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2831,94 +2831,94 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0.80511146637227</v>
+        <v>0.9811234885426894</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0003910747991264633</v>
+        <v>1.898841446727086e-36</v>
       </c>
       <c r="G96" t="n">
-        <v>0.1944974588286036</v>
+        <v>0.01887651145731052</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8380812809162387</v>
+        <v>0.3652250162064756</v>
       </c>
       <c r="F97" t="n">
-        <v>0.03370275285224348</v>
+        <v>1.171446580014517e-26</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1282159662315177</v>
+        <v>0.6347749837935245</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6527361836116538</v>
+        <v>0.0002779462404193438</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2969546231136485</v>
+        <v>1.750992354023995e-17</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0503091932746977</v>
+        <v>0.9997220537595806</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="B99" t="b">
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8641786880555008</v>
+        <v>6.986347374622582e-07</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0001199699375958137</v>
+        <v>5.443774449246546e-11</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1357013420069033</v>
+        <v>0.9999993013108247</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B100" t="b">
@@ -2928,72 +2928,72 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8724838535943112</v>
+        <v>8.408178932678543e-07</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1067157255526522</v>
+        <v>2.045946738789998e-14</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02080042085303651</v>
+        <v>0.9999991591820863</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="B101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9538486601068155</v>
+        <v>3.947032061178055e-09</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0004705190173690836</v>
+        <v>0.003447184961849877</v>
       </c>
       <c r="G101" t="n">
-        <v>0.04568082087581546</v>
+        <v>0.9965528110911182</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="B102" t="b">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0.07205008160911905</v>
+        <v>0.9989912442312248</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9276909290177506</v>
+        <v>5.370997515783539e-34</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0002589893731303018</v>
+        <v>0.00100875576877532</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="B103" t="b">
@@ -3006,23 +3006,23 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2431105275143956</v>
+        <v>2.969168772378235e-27</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7556641037771091</v>
+        <v>0.9999999999984774</v>
       </c>
       <c r="G103" t="n">
-        <v>0.001225368708495386</v>
+        <v>1.522476298896751e-12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="B104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
         <v>2</v>
@@ -3031,94 +3031,94 @@
         <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>0.00252833182742124</v>
+        <v>2.171599363668507e-19</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9973005409515686</v>
+        <v>0.9999993645949151</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0001711272210100248</v>
+        <v>6.354050848383377e-07</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="B105" t="b">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9532356188557406</v>
+        <v>8.452909580111206e-16</v>
       </c>
       <c r="F105" t="n">
-        <v>0.000538373447185571</v>
+        <v>0.9999581598692833</v>
       </c>
       <c r="G105" t="n">
-        <v>0.04622600769707389</v>
+        <v>4.184013071597197e-05</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="B106" t="b">
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9410263054349404</v>
+        <v>3.357671205001748e-05</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0146500543441245</v>
+        <v>6.010226630720555e-17</v>
       </c>
       <c r="G106" t="n">
-        <v>0.04432364022093499</v>
+        <v>0.9999664232879499</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="B107" t="b">
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>0.7965698261800038</v>
+        <v>9.165848869863005e-09</v>
       </c>
       <c r="F107" t="n">
-        <v>2.880425204437286e-06</v>
+        <v>5.856024199799487e-07</v>
       </c>
       <c r="G107" t="n">
-        <v>0.2034272933947918</v>
+        <v>0.9999994052317311</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="B108" t="b">
@@ -3131,19 +3131,19 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8419149553748662</v>
+        <v>0.9534278568402272</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0004594608768594735</v>
+        <v>2.772670887587876e-34</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1576255837482744</v>
+        <v>0.04657214315977284</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="B109" t="b">
@@ -3156,94 +3156,94 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9568879363899297</v>
+        <v>0.998480221182793</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0001312371648551567</v>
+        <v>4.320547022829381e-36</v>
       </c>
       <c r="G109" t="n">
-        <v>0.04298082644521509</v>
+        <v>0.001519778817207079</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="B110" t="b">
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9678026268731132</v>
+        <v>4.278190880381659e-07</v>
       </c>
       <c r="F110" t="n">
-        <v>0.003593990775333041</v>
+        <v>3.923720026817798e-07</v>
       </c>
       <c r="G110" t="n">
-        <v>0.02860338235155374</v>
+        <v>0.9999991798089093</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="B111" t="b">
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9630459622631659</v>
+        <v>0.01263193767943844</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0002786686911066978</v>
+        <v>1.26557879698727e-24</v>
       </c>
       <c r="G111" t="n">
-        <v>0.03667536904572736</v>
+        <v>0.9873680623205616</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="B112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
         <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E112" t="n">
-        <v>0.6939071164967441</v>
+        <v>7.326642612633931e-06</v>
       </c>
       <c r="F112" t="n">
-        <v>8.566065000124497e-06</v>
+        <v>4.18752062000309e-16</v>
       </c>
       <c r="G112" t="n">
-        <v>0.3060843174382558</v>
+        <v>0.9999926733573868</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="B113" t="b">
@@ -3256,23 +3256,23 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.689279787873148</v>
+        <v>0.9999312169214921</v>
       </c>
       <c r="F113" t="n">
-        <v>2.654892226070844e-06</v>
+        <v>1.025134081291806e-37</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3107175572346259</v>
+        <v>6.878307850779439e-05</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -3281,19 +3281,19 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9606896404122718</v>
+        <v>0.999999599309811</v>
       </c>
       <c r="F114" t="n">
-        <v>3.244810582040932e-05</v>
+        <v>2.433602805658487e-51</v>
       </c>
       <c r="G114" t="n">
-        <v>0.03927791148190778</v>
+        <v>4.006901890331989e-07</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="B115" t="b">
@@ -3306,44 +3306,44 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.6003102784794129</v>
+        <v>0.9999951401063114</v>
       </c>
       <c r="F115" t="n">
-        <v>2.924727580438575e-07</v>
+        <v>7.513971801629144e-47</v>
       </c>
       <c r="G115" t="n">
-        <v>0.3996894290478291</v>
+        <v>4.859893688471918e-06</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.07645165086337528</v>
+        <v>0.9434858434122564</v>
       </c>
       <c r="F116" t="n">
-        <v>4.611260137019246e-10</v>
+        <v>3.4861163351444e-32</v>
       </c>
       <c r="G116" t="n">
-        <v>0.9235483486754987</v>
+        <v>0.05651415658774357</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="B117" t="b">
@@ -3356,23 +3356,23 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6673917200704605</v>
+        <v>0.9999999866719735</v>
       </c>
       <c r="F117" t="n">
-        <v>1.142078452993842e-05</v>
+        <v>4.468683222689963e-59</v>
       </c>
       <c r="G117" t="n">
-        <v>0.3325968591450095</v>
+        <v>1.332802660620859e-08</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -3381,48 +3381,48 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7549841585034729</v>
+        <v>0.999999999853433</v>
       </c>
       <c r="F118" t="n">
-        <v>4.125058893763906e-06</v>
+        <v>5.579149018947006e-70</v>
       </c>
       <c r="G118" t="n">
-        <v>0.2450117164376333</v>
+        <v>1.465670515033747e-10</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7091347644476387</v>
+        <v>0.07829304867839018</v>
       </c>
       <c r="F119" t="n">
-        <v>6.970273561217452e-05</v>
+        <v>1.097069786508977e-28</v>
       </c>
       <c r="G119" t="n">
-        <v>0.2907955328167492</v>
+        <v>0.9217069513216098</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -3431,98 +3431,98 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.883768405687628</v>
+        <v>0.9994961593998823</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0002823882316365066</v>
+        <v>5.507451050981829e-41</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1159492060807354</v>
+        <v>0.0005038406001176753</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="B121" t="b">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8976386357134678</v>
+        <v>3.419107936208321e-05</v>
       </c>
       <c r="F121" t="n">
-        <v>8.770740232009204e-06</v>
+        <v>2.212399207610356e-15</v>
       </c>
       <c r="G121" t="n">
-        <v>0.1023525935463002</v>
+        <v>0.9999658089206357</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="B122" t="b">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
-        <v>0.834546591946413</v>
+        <v>0.02269945981505498</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0001906681563817756</v>
+        <v>1.793865781821426e-25</v>
       </c>
       <c r="G122" t="n">
-        <v>0.1652627398972051</v>
+        <v>0.9773005401849452</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>0.9059284414708116</v>
+        <v>0.0008733383837855163</v>
       </c>
       <c r="F123" t="n">
-        <v>0.008835048806132459</v>
+        <v>2.789955739355438e-22</v>
       </c>
       <c r="G123" t="n">
-        <v>0.08523650972305588</v>
+        <v>0.9991266616162144</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -3531,69 +3531,69 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.907760508786328</v>
+        <v>0.9098973748970235</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0004415535316048984</v>
+        <v>6.443919329298773e-33</v>
       </c>
       <c r="G124" t="n">
-        <v>0.09179793768206716</v>
+        <v>0.09010262510297665</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
-        <v>0.9777301985249542</v>
+        <v>0.05670444379523303</v>
       </c>
       <c r="F125" t="n">
-        <v>0.001117273256674298</v>
+        <v>2.884218623747994e-25</v>
       </c>
       <c r="G125" t="n">
-        <v>0.02115252821837162</v>
+        <v>0.943295556204767</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
-        <v>0.9908821632456366</v>
+        <v>4.922783384216739e-05</v>
       </c>
       <c r="F126" t="n">
-        <v>2.178330136914699e-06</v>
+        <v>2.497697121293739e-17</v>
       </c>
       <c r="G126" t="n">
-        <v>0.009115658424226528</v>
+        <v>0.9999507721661578</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="B127" t="b">
@@ -3606,73 +3606,73 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>0.7466667575028976</v>
+        <v>0.9900153712257058</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0006291173736809929</v>
+        <v>8.697754234004185e-34</v>
       </c>
       <c r="G127" t="n">
-        <v>0.2527041251234215</v>
+        <v>0.009984628774294322</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>0.7083424415108733</v>
+        <v>0.002690981243843975</v>
       </c>
       <c r="F128" t="n">
-        <v>5.458588487296824e-07</v>
+        <v>5.35945526971653e-22</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2916570126302779</v>
+        <v>0.9973090187561561</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>0.9499447579233966</v>
+        <v>0.0001916344552161711</v>
       </c>
       <c r="F129" t="n">
-        <v>0.01070245762981633</v>
+        <v>9.342885039606009e-26</v>
       </c>
       <c r="G129" t="n">
-        <v>0.03935278444678689</v>
+        <v>0.9998083655447838</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -3681,19 +3681,19 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.9255222023067124</v>
+        <v>0.8703391515563766</v>
       </c>
       <c r="F130" t="n">
-        <v>7.983084832853561e-05</v>
+        <v>6.080854167637393e-31</v>
       </c>
       <c r="G130" t="n">
-        <v>0.07439796684495902</v>
+        <v>0.1296608484436232</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="B131" t="b">
@@ -3706,119 +3706,119 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0.9000723283091573</v>
+        <v>0.5536712317137564</v>
       </c>
       <c r="F131" t="n">
-        <v>0.000697594133730793</v>
+        <v>9.993692981832124e-33</v>
       </c>
       <c r="G131" t="n">
-        <v>0.09923007755711202</v>
+        <v>0.4463287682862435</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="B132" t="b">
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>0.9515822149617416</v>
+        <v>0.002075128929846473</v>
       </c>
       <c r="F132" t="n">
-        <v>4.76037143505494e-05</v>
+        <v>1.925805346176193e-19</v>
       </c>
       <c r="G132" t="n">
-        <v>0.04837018132390787</v>
+        <v>0.9979248710701536</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
-        <v>0.941625295896459</v>
+        <v>9.657027928612704e-07</v>
       </c>
       <c r="F133" t="n">
-        <v>1.091552090351425e-05</v>
+        <v>7.661194044044215e-14</v>
       </c>
       <c r="G133" t="n">
-        <v>0.05836378858263747</v>
+        <v>0.9999990342971306</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="B134" t="b">
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>0.9872458528722946</v>
+        <v>3.133727728663439e-07</v>
       </c>
       <c r="F134" t="n">
-        <v>3.005876524902271e-05</v>
+        <v>3.556465042415595e-12</v>
       </c>
       <c r="G134" t="n">
-        <v>0.01272408836245639</v>
+        <v>0.9999996866236708</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="B135" t="b">
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
-        <v>0.79090533880773</v>
+        <v>1.665002364563145e-08</v>
       </c>
       <c r="F135" t="n">
-        <v>0.08614358779793962</v>
+        <v>1.690752536018941e-10</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1229510733943305</v>
+        <v>0.9999999831809011</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="B136" t="b">
@@ -3831,19 +3831,19 @@
         <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4176818396040093</v>
+        <v>5.792081635845467e-08</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0003574795761849057</v>
+        <v>9.091925841177132e-08</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5819606808198057</v>
+        <v>0.9999998511599253</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="B137" t="b">
@@ -3856,19 +3856,19 @@
         <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1233615949741068</v>
+        <v>7.209544904401512e-23</v>
       </c>
       <c r="F137" t="n">
-        <v>0.8723406350651409</v>
+        <v>0.9999999735839713</v>
       </c>
       <c r="G137" t="n">
-        <v>0.004297769960752436</v>
+        <v>2.641602875615632e-08</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="B138" t="b">
@@ -3881,44 +3881,44 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.9382108767318776</v>
+        <v>0.9476240752768248</v>
       </c>
       <c r="F138" t="n">
-        <v>2.351862995870429e-05</v>
+        <v>1.625917603939927e-29</v>
       </c>
       <c r="G138" t="n">
-        <v>0.06176560463816367</v>
+        <v>0.0523759247231752</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="B139" t="b">
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
-        <v>0.668022808024451</v>
+        <v>2.160838781000729e-10</v>
       </c>
       <c r="F139" t="n">
-        <v>3.38843660686078e-05</v>
+        <v>0.0003389388781093649</v>
       </c>
       <c r="G139" t="n">
-        <v>0.3319433076094803</v>
+        <v>0.9996610609058069</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="B140" t="b">
@@ -3931,98 +3931,98 @@
         <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3676330169857502</v>
+        <v>0.00264799344413942</v>
       </c>
       <c r="F140" t="n">
-        <v>4.724546524513005e-05</v>
+        <v>1.851261994769127e-22</v>
       </c>
       <c r="G140" t="n">
-        <v>0.6323197375490047</v>
+        <v>0.9973520065558605</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="B141" t="b">
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>0.404827129464525</v>
+        <v>2.353217640338208e-14</v>
       </c>
       <c r="F141" t="n">
-        <v>2.595407887212876e-09</v>
+        <v>0.8412017471052515</v>
       </c>
       <c r="G141" t="n">
-        <v>0.5951728679400672</v>
+        <v>0.158798252894725</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="B142" t="b">
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>0.748708174741033</v>
+        <v>1.325622090378949e-18</v>
       </c>
       <c r="F142" t="n">
-        <v>2.911735885936394e-05</v>
+        <v>0.9999704162799889</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2512627079001076</v>
+        <v>2.958372001111805e-05</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="B143" t="b">
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>0.09300587575722788</v>
+        <v>3.109297949319793e-12</v>
       </c>
       <c r="F143" t="n">
-        <v>0.4084060699545257</v>
+        <v>0.9743135682898272</v>
       </c>
       <c r="G143" t="n">
-        <v>0.4985880542882464</v>
+        <v>0.02568643170706353</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="B144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
@@ -4031,144 +4031,144 @@
         <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>0.02956497089645847</v>
+        <v>0.02589980405187923</v>
       </c>
       <c r="F144" t="n">
-        <v>3.413384498961783e-12</v>
+        <v>1.046402424892478e-22</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9704350291001282</v>
+        <v>0.9741001959481208</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="B145" t="b">
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>0.6700077008027432</v>
+        <v>7.017040473794504e-14</v>
       </c>
       <c r="F145" t="n">
-        <v>1.244318698648127e-05</v>
+        <v>0.7256973074075096</v>
       </c>
       <c r="G145" t="n">
-        <v>0.3299798560102704</v>
+        <v>0.2743026925924202</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="B146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
         <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4161782956845052</v>
+        <v>0.01766368211083314</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0004498456430531582</v>
+        <v>6.05845811699154e-22</v>
       </c>
       <c r="G146" t="n">
-        <v>0.5833718586724417</v>
+        <v>0.9823363178891668</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="B147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E147" t="n">
-        <v>0.8103868194386609</v>
+        <v>0.1020699810307639</v>
       </c>
       <c r="F147" t="n">
-        <v>1.757922826634908e-05</v>
+        <v>9.79812599775795e-28</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1895956013330727</v>
+        <v>0.8979300189692362</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="B148" t="b">
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>0.8457200143015531</v>
+        <v>0.0001322374340553959</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0002768264333563938</v>
+        <v>4.707431257708982e-23</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1540031592650906</v>
+        <v>0.9998677625659446</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="B149" t="b">
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1710111116354498</v>
+        <v>0.9385329584819204</v>
       </c>
       <c r="F149" t="n">
-        <v>0.7962235449623137</v>
+        <v>1.820755595022802e-34</v>
       </c>
       <c r="G149" t="n">
-        <v>0.03276534340223629</v>
+        <v>0.06146704151807955</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="B150" t="b">
@@ -4181,69 +4181,69 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.9613805235086095</v>
+        <v>0.9999821680822918</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0005552739007998384</v>
+        <v>6.655762820535641e-51</v>
       </c>
       <c r="G150" t="n">
-        <v>0.03806420259059069</v>
+        <v>1.783191770817292e-05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="B151" t="b">
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7042171481711454</v>
+        <v>0.0004964626181906184</v>
       </c>
       <c r="F151" t="n">
-        <v>4.432467761829573e-06</v>
+        <v>4.328374861081873e-25</v>
       </c>
       <c r="G151" t="n">
-        <v>0.2957784193610927</v>
+        <v>0.9995035373818093</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="B152" t="b">
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>0.5852866101571659</v>
+        <v>0.0002068178427265421</v>
       </c>
       <c r="F152" t="n">
-        <v>0.2971617838433602</v>
+        <v>3.25638883288533e-18</v>
       </c>
       <c r="G152" t="n">
-        <v>0.1175516059994739</v>
+        <v>0.9997931821572734</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="B153" t="b">
@@ -4256,94 +4256,94 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.8178044165569236</v>
+        <v>0.9990901599142695</v>
       </c>
       <c r="F153" t="n">
-        <v>6.311304042719183e-06</v>
+        <v>9.772579768879452e-42</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1821892721390338</v>
+        <v>0.0009098400857304116</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="B154" t="b">
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.466918703111465</v>
+        <v>0.7547186094081157</v>
       </c>
       <c r="F154" t="n">
-        <v>0.03810255222779355</v>
+        <v>1.217082753198539e-26</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4949787446607414</v>
+        <v>0.2452813905918843</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="B155" t="b">
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>0.8008300724911409</v>
+        <v>0.1838311522543357</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0001064577492247359</v>
+        <v>6.658659982715771e-25</v>
       </c>
       <c r="G155" t="n">
-        <v>0.1990634697596344</v>
+        <v>0.8161688477456642</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="B156" t="b">
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
-        <v>0.7954438461175067</v>
+        <v>0.02506234101054056</v>
       </c>
       <c r="F156" t="n">
-        <v>0.003291379818965802</v>
+        <v>2.078357192906699e-27</v>
       </c>
       <c r="G156" t="n">
-        <v>0.2012647740635276</v>
+        <v>0.9749376589894594</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="B157" t="b">
@@ -4356,44 +4356,44 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0.9345959647178207</v>
+        <v>0.9938919868529841</v>
       </c>
       <c r="F157" t="n">
-        <v>0.004092743180453339</v>
+        <v>1.310247251356744e-33</v>
       </c>
       <c r="G157" t="n">
-        <v>0.06131129210172608</v>
+        <v>0.00610801314701604</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="B158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>0.7302343920852582</v>
+        <v>1.325332742514092e-05</v>
       </c>
       <c r="F158" t="n">
-        <v>0.001481074934505133</v>
+        <v>3.058869075280296e-15</v>
       </c>
       <c r="G158" t="n">
-        <v>0.2682845329802366</v>
+        <v>0.9999867466725718</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="B159" t="b">
@@ -4406,69 +4406,69 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0.874163837037774</v>
+        <v>0.987233255533198</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0002569620831863645</v>
+        <v>9.590385907899026e-32</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1255792008790398</v>
+        <v>0.01276674446680206</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="B160" t="b">
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" t="n">
-        <v>0.6737763238957317</v>
+        <v>5.418694743454724e-05</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0001775729586833939</v>
+        <v>7.615423360838159e-23</v>
       </c>
       <c r="G160" t="n">
-        <v>0.326046103145585</v>
+        <v>0.9999458130525655</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="B161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4207278417688977</v>
+        <v>0.9947211000671732</v>
       </c>
       <c r="F161" t="n">
-        <v>0.5276328216873344</v>
+        <v>1.338834132059464e-34</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05163933654376802</v>
+        <v>0.00527889993282676</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="B162" t="b">
@@ -4481,48 +4481,48 @@
         <v>3</v>
       </c>
       <c r="E162" t="n">
-        <v>0.3035732780716192</v>
+        <v>0.01657480900672981</v>
       </c>
       <c r="F162" t="n">
-        <v>0.001125546693024915</v>
+        <v>8.015582548576291e-26</v>
       </c>
       <c r="G162" t="n">
-        <v>0.6953011752353558</v>
+        <v>0.9834251909932702</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="B163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163" t="n">
-        <v>0.8044505191968531</v>
+        <v>5.867535793209345e-09</v>
       </c>
       <c r="F163" t="n">
-        <v>6.259176395381748e-06</v>
+        <v>1.710577555841343e-06</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1955432216267514</v>
+        <v>0.9999982835549083</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="B164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -4531,19 +4531,19 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>0.8666066385420147</v>
+        <v>0.9759746431716307</v>
       </c>
       <c r="F164" t="n">
-        <v>4.267764210714554e-05</v>
+        <v>3.533652164361491e-33</v>
       </c>
       <c r="G164" t="n">
-        <v>0.1333506838158781</v>
+        <v>0.02402535682836921</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B165" t="b">
@@ -4556,23 +4556,23 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>0.538036927816307</v>
+        <v>0.9999999380549177</v>
       </c>
       <c r="F165" t="n">
-        <v>0.4616581032382059</v>
+        <v>7.72240952885317e-54</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0003049689454870772</v>
+        <v>6.194508239638056e-08</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="B166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -4581,19 +4581,19 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>0.8898392027966718</v>
+        <v>0.9381559233148186</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0002559406055330316</v>
+        <v>1.494039333245218e-33</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1099048565977951</v>
+        <v>0.06184407668518152</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="B167" t="b">
@@ -4606,19 +4606,19 @@
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>0.9573382189759132</v>
+        <v>0.9999997151308088</v>
       </c>
       <c r="F167" t="n">
-        <v>0.003433107786749069</v>
+        <v>4.223393352364206e-53</v>
       </c>
       <c r="G167" t="n">
-        <v>0.03922867323733763</v>
+        <v>2.848691912861464e-07</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="B168" t="b">
@@ -4631,23 +4631,23 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>0.5832091686127627</v>
+        <v>0.9999987951468647</v>
       </c>
       <c r="F168" t="n">
-        <v>6.694010686568399e-07</v>
+        <v>2.592459250560562e-52</v>
       </c>
       <c r="G168" t="n">
-        <v>0.4167901619861688</v>
+        <v>1.204853135264769e-06</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="B169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -4656,73 +4656,73 @@
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>0.9847790517853618</v>
+        <v>0.9999988518128516</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0002630302995705633</v>
+        <v>4.038703219663834e-54</v>
       </c>
       <c r="G169" t="n">
-        <v>0.01495791791506759</v>
+        <v>1.148187148370419e-06</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="B170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4265403856791288</v>
+        <v>0.9999993697650464</v>
       </c>
       <c r="F170" t="n">
-        <v>1.916154167729947e-08</v>
+        <v>1.662053165561007e-54</v>
       </c>
       <c r="G170" t="n">
-        <v>0.5734595951593294</v>
+        <v>6.302349535798508e-07</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="B171" t="b">
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" t="n">
-        <v>0.6584710928288917</v>
+        <v>0.0956925135353804</v>
       </c>
       <c r="F171" t="n">
-        <v>8.644008244493457e-05</v>
+        <v>5.272871811598946e-34</v>
       </c>
       <c r="G171" t="n">
-        <v>0.3414424670886634</v>
+        <v>0.9043074864646196</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="B172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -4731,23 +4731,23 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.6320740459198534</v>
+        <v>0.9998418696545247</v>
       </c>
       <c r="F172" t="n">
-        <v>5.913042043695691e-07</v>
+        <v>1.870205822447664e-42</v>
       </c>
       <c r="G172" t="n">
-        <v>0.3679253627759423</v>
+        <v>0.0001581303454753133</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -4756,144 +4756,144 @@
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0.688595472134667</v>
+        <v>0.9986240600373683</v>
       </c>
       <c r="F173" t="n">
-        <v>1.264104573029356e-06</v>
+        <v>6.498313980531245e-42</v>
       </c>
       <c r="G173" t="n">
-        <v>0.3114032637607601</v>
+        <v>0.001375939962631704</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="B174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>0.6619306471382498</v>
+        <v>0.0838066262237719</v>
       </c>
       <c r="F174" t="n">
-        <v>9.07001518158315e-07</v>
+        <v>2.537679122865766e-29</v>
       </c>
       <c r="G174" t="n">
-        <v>0.338068445860232</v>
+        <v>0.9161933737762282</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="B175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E175" t="n">
-        <v>0.5153704661804788</v>
+        <v>0.0520159915070911</v>
       </c>
       <c r="F175" t="n">
-        <v>2.47845269835088e-06</v>
+        <v>9.420067481767867e-29</v>
       </c>
       <c r="G175" t="n">
-        <v>0.4846270553668228</v>
+        <v>0.9479840084929089</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="B176" t="b">
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E176" t="n">
-        <v>0.6970096389741627</v>
+        <v>0.0108699594585798</v>
       </c>
       <c r="F176" t="n">
-        <v>0.00395675892879174</v>
+        <v>1.539044190471868e-27</v>
       </c>
       <c r="G176" t="n">
-        <v>0.2990336020970456</v>
+        <v>0.9891300405414203</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="B177" t="b">
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>0.279655906750887</v>
+        <v>0.9131347381894971</v>
       </c>
       <c r="F177" t="n">
-        <v>0.399368606530322</v>
+        <v>1.157616784474396e-38</v>
       </c>
       <c r="G177" t="n">
-        <v>0.3209754867187909</v>
+        <v>0.08686526181050287</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="B178" t="b">
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E178" t="n">
-        <v>0.08533376741706411</v>
+        <v>0.0060390829882241</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7618642402284707</v>
+        <v>2.027643412441402e-18</v>
       </c>
       <c r="G178" t="n">
-        <v>0.1528019923544654</v>
+        <v>0.9939609170117759</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="B179" t="b">
@@ -4906,69 +4906,69 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>0.8280400172331654</v>
+        <v>0.9771245795377483</v>
       </c>
       <c r="F179" t="n">
-        <v>1.292851181285524e-05</v>
+        <v>2.387869104306827e-32</v>
       </c>
       <c r="G179" t="n">
-        <v>0.1719470542550215</v>
+        <v>0.0228754204622517</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="B180" t="b">
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E180" t="n">
-        <v>0.7515731043039493</v>
+        <v>0.02563044441899236</v>
       </c>
       <c r="F180" t="n">
-        <v>1.042400898757185e-05</v>
+        <v>3.402606422805539e-21</v>
       </c>
       <c r="G180" t="n">
-        <v>0.2484164716870632</v>
+        <v>0.9743695555810076</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="B181" t="b">
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181" t="n">
-        <v>0.01337374245781599</v>
+        <v>1.644235502501923e-05</v>
       </c>
       <c r="F181" t="n">
-        <v>0.9663050975106422</v>
+        <v>7.853675500125839e-15</v>
       </c>
       <c r="G181" t="n">
-        <v>0.02032116003154184</v>
+        <v>0.9999835576449672</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="B182" t="b">
@@ -4981,19 +4981,19 @@
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>0.7344600535868271</v>
+        <v>0.9999495709075994</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0006601650670439066</v>
+        <v>2.387547220093458e-44</v>
       </c>
       <c r="G182" t="n">
-        <v>0.2648797813461291</v>
+        <v>5.042909240064547e-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="B183" t="b">
@@ -5006,19 +5006,19 @@
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6929902450193141</v>
+        <v>0.9998627951940025</v>
       </c>
       <c r="F183" t="n">
-        <v>2.947269787692045e-07</v>
+        <v>2.001094803758021e-43</v>
       </c>
       <c r="G183" t="n">
-        <v>0.3070094602537072</v>
+        <v>0.0001372048059975265</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="B184" t="b">
@@ -5031,198 +5031,198 @@
         <v>3</v>
       </c>
       <c r="E184" t="n">
-        <v>0.4927140785534693</v>
+        <v>0.00138137503047828</v>
       </c>
       <c r="F184" t="n">
-        <v>0.008000642511736352</v>
+        <v>8.796290272980963e-28</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4992852789347943</v>
+        <v>0.9986186249695217</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="B185" t="b">
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E185" t="n">
-        <v>0.5472514365051516</v>
+        <v>0.005888310829821579</v>
       </c>
       <c r="F185" t="n">
-        <v>0.007063412098672736</v>
+        <v>3.185020140560221e-23</v>
       </c>
       <c r="G185" t="n">
-        <v>0.4456851513961756</v>
+        <v>0.9941116891701783</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="B186" t="b">
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>0.4917929153501449</v>
+        <v>5.030591498182119e-16</v>
       </c>
       <c r="F186" t="n">
-        <v>0.06826179682831629</v>
+        <v>0.9972577640922242</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4399452878215389</v>
+        <v>0.002742235907775363</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="B187" t="b">
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E187" t="n">
-        <v>0.8636045497073548</v>
+        <v>5.393356813403808e-06</v>
       </c>
       <c r="F187" t="n">
-        <v>1.278537303564346e-05</v>
+        <v>1.731896292829554e-14</v>
       </c>
       <c r="G187" t="n">
-        <v>0.1363826649196096</v>
+        <v>0.9999946066431693</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="B188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E188" t="n">
-        <v>0.6992980302945337</v>
+        <v>4.829862766125752e-08</v>
       </c>
       <c r="F188" t="n">
-        <v>1.204305131126426e-05</v>
+        <v>2.509522019364148e-11</v>
       </c>
       <c r="G188" t="n">
-        <v>0.3006899266541549</v>
+        <v>0.9999999516762771</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="B189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>0.6876575289748045</v>
+        <v>0.08201920611506472</v>
       </c>
       <c r="F189" t="n">
-        <v>7.449283679858349e-07</v>
+        <v>2.895081183784522e-28</v>
       </c>
       <c r="G189" t="n">
-        <v>0.3123417260968276</v>
+        <v>0.9179807938849354</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="B190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>0.4753416092332927</v>
+        <v>0.8002117833790351</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0003194532995355824</v>
+        <v>1.207578998052599e-25</v>
       </c>
       <c r="G190" t="n">
-        <v>0.5243389374671716</v>
+        <v>0.199788216620965</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="B191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
         <v>3</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2751104507008352</v>
+        <v>0.4899987520103565</v>
       </c>
       <c r="F191" t="n">
-        <v>3.775102224497596e-08</v>
+        <v>8.822533219918034e-24</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7248895115481426</v>
+        <v>0.5100012479896435</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
         <v>3</v>
@@ -5231,44 +5231,44 @@
         <v>3</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3911552665643847</v>
+        <v>0.1044657488692495</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0001405052704865593</v>
+        <v>1.625748658161323e-26</v>
       </c>
       <c r="G192" t="n">
-        <v>0.6087042281651288</v>
+        <v>0.8955342511307505</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="B193" t="b">
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E193" t="n">
-        <v>0.5054275722514101</v>
+        <v>5.88710181601631e-05</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0004491099869438113</v>
+        <v>1.338866174574467e-18</v>
       </c>
       <c r="G193" t="n">
-        <v>0.4941233177616461</v>
+        <v>0.9999411289818398</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="B194" t="b">
@@ -5281,19 +5281,19 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.7327368981830172</v>
+        <v>0.9888546505098462</v>
       </c>
       <c r="F194" t="n">
-        <v>0.00166126322949124</v>
+        <v>9.481216376202971e-34</v>
       </c>
       <c r="G194" t="n">
-        <v>0.2656018385874915</v>
+        <v>0.01114534949015363</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="B195" t="b">
@@ -5306,144 +5306,144 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.7162015348103044</v>
+        <v>0.9999997103588365</v>
       </c>
       <c r="F195" t="n">
-        <v>0.02824649745412232</v>
+        <v>2.64030613225526e-50</v>
       </c>
       <c r="G195" t="n">
-        <v>0.2555519677355734</v>
+        <v>2.896411635029605e-07</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="B196" t="b">
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3698602654299104</v>
+        <v>0.99796149596221</v>
       </c>
       <c r="F196" t="n">
-        <v>0.4240060504384537</v>
+        <v>8.211913119637986e-37</v>
       </c>
       <c r="G196" t="n">
-        <v>0.206133684131636</v>
+        <v>0.002038504037789992</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B197" t="b">
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2754863345768983</v>
+        <v>0.9999995903877069</v>
       </c>
       <c r="F197" t="n">
-        <v>0.0382063898756233</v>
+        <v>7.403018827718476e-45</v>
       </c>
       <c r="G197" t="n">
-        <v>0.6863072755474784</v>
+        <v>4.096122929923492e-07</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="B198" t="b">
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E198" t="n">
-        <v>0.5122565550473214</v>
+        <v>1.460482147929197e-08</v>
       </c>
       <c r="F198" t="n">
-        <v>0.001259989903934685</v>
+        <v>4.176409154016236e-14</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4864834550487439</v>
+        <v>0.9999999853951367</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="B199" t="b">
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E199" t="n">
-        <v>0.5353860172025606</v>
+        <v>9.717045298878466e-21</v>
       </c>
       <c r="F199" t="n">
-        <v>0.007403420323761994</v>
+        <v>0.9999998805376403</v>
       </c>
       <c r="G199" t="n">
-        <v>0.4572105624736774</v>
+        <v>1.194623597571923e-07</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B200" t="b">
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E200" t="n">
-        <v>0.5703947709470355</v>
+        <v>0.03240459204212467</v>
       </c>
       <c r="F200" t="n">
-        <v>0.03648145168547499</v>
+        <v>1.781411558852759e-26</v>
       </c>
       <c r="G200" t="n">
-        <v>0.3931237773674895</v>
+        <v>0.9675954079578752</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B201" t="b">
@@ -5456,148 +5456,148 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.6065022903604003</v>
+        <v>0.8912828642297379</v>
       </c>
       <c r="F201" t="n">
-        <v>0.01063297723861587</v>
+        <v>2.422686984079438e-33</v>
       </c>
       <c r="G201" t="n">
-        <v>0.3828647324009838</v>
+        <v>0.1087171357702621</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="B202" t="b">
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E202" t="n">
-        <v>0.8167497734404846</v>
+        <v>0.001618139404267785</v>
       </c>
       <c r="F202" t="n">
-        <v>0.003711951703503272</v>
+        <v>2.334978250333416e-17</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1795382748560122</v>
+        <v>0.9983818605957321</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E203" t="n">
-        <v>0.6513411500357786</v>
+        <v>0.1517702304848304</v>
       </c>
       <c r="F203" t="n">
-        <v>1.791000138026305e-06</v>
+        <v>1.178660021392198e-19</v>
       </c>
       <c r="G203" t="n">
-        <v>0.3486570589640833</v>
+        <v>0.8482297695151696</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="B204" t="b">
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E204" t="n">
-        <v>0.5610416520107844</v>
+        <v>0.0001367019009460997</v>
       </c>
       <c r="F204" t="n">
-        <v>9.029431314024567e-06</v>
+        <v>1.333878921881157e-15</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4389493185579015</v>
+        <v>0.9998632980990525</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="B205" t="b">
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E205" t="n">
-        <v>0.6074781933775235</v>
+        <v>6.971666372794395e-09</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0001565333188126893</v>
+        <v>7.575480578697133e-14</v>
       </c>
       <c r="G205" t="n">
-        <v>0.3923652733036638</v>
+        <v>0.9999999930282579</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0.4471216976598495</v>
+        <v>0.9998962976373398</v>
       </c>
       <c r="F206" t="n">
-        <v>8.443979460062699e-06</v>
+        <v>2.124781701632662e-52</v>
       </c>
       <c r="G206" t="n">
-        <v>0.5528698583606906</v>
+        <v>0.000103702362660273</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="B207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207" t="n">
         <v>3</v>
@@ -5606,48 +5606,48 @@
         <v>3</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3220774164611825</v>
+        <v>4.114796880617452e-07</v>
       </c>
       <c r="F207" t="n">
-        <v>3.442844559751224e-08</v>
+        <v>7.545664656486468e-18</v>
       </c>
       <c r="G207" t="n">
-        <v>0.6779225491103719</v>
+        <v>0.999999588520312</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="B208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
-        <v>0.4943312453440981</v>
+        <v>2.715012222207521e-29</v>
       </c>
       <c r="F208" t="n">
-        <v>0.0008420106970950544</v>
+        <v>0.9999999999857581</v>
       </c>
       <c r="G208" t="n">
-        <v>0.5048267439588069</v>
+        <v>1.424185243473324e-11</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="B209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209" t="n">
         <v>3</v>
@@ -5656,44 +5656,44 @@
         <v>3</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3705987670689433</v>
+        <v>0.001771073641986717</v>
       </c>
       <c r="F209" t="n">
-        <v>1.425658837052478e-05</v>
+        <v>1.0922297473796e-19</v>
       </c>
       <c r="G209" t="n">
-        <v>0.6293869763426861</v>
+        <v>0.9982289263580133</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="B210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C210" t="n">
         <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E210" t="n">
-        <v>0.5524346515423602</v>
+        <v>8.489884780140636e-09</v>
       </c>
       <c r="F210" t="n">
-        <v>0.001643330312096585</v>
+        <v>1.016741135242514e-07</v>
       </c>
       <c r="G210" t="n">
-        <v>0.4459220181455434</v>
+        <v>0.9999998898360017</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="B211" t="b">
@@ -5706,23 +5706,23 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>0.8246672025936668</v>
+        <v>0.5212778425327972</v>
       </c>
       <c r="F211" t="n">
-        <v>0.03137177992200769</v>
+        <v>1.197356966508994e-27</v>
       </c>
       <c r="G211" t="n">
-        <v>0.1439610174843255</v>
+        <v>0.4787221574672029</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -5731,23 +5731,23 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>0.7867170917005086</v>
+        <v>0.9999996339048992</v>
       </c>
       <c r="F212" t="n">
-        <v>0.003182176260204515</v>
+        <v>7.480235954265385e-62</v>
       </c>
       <c r="G212" t="n">
-        <v>0.2101007320392868</v>
+        <v>3.660951008290679e-07</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="B213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -5756,48 +5756,48 @@
         <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>0.6897568403512964</v>
+        <v>0.9999082533288718</v>
       </c>
       <c r="F213" t="n">
-        <v>3.260956432677119e-05</v>
+        <v>3.740349392319402e-42</v>
       </c>
       <c r="G213" t="n">
-        <v>0.3102105500843769</v>
+        <v>9.174667112813313e-05</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="B214" t="b">
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4454997093370942</v>
+        <v>0.999608459685056</v>
       </c>
       <c r="F214" t="n">
-        <v>0.5086408919983213</v>
+        <v>2.798525788210362e-40</v>
       </c>
       <c r="G214" t="n">
-        <v>0.04585939866458453</v>
+        <v>0.0003915403149440348</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="B215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -5806,19 +5806,19 @@
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>0.9372751070725218</v>
+        <v>0.9999774042706211</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0004370803562206253</v>
+        <v>1.678616605808493e-44</v>
       </c>
       <c r="G215" t="n">
-        <v>0.06228781257125761</v>
+        <v>2.259572937887526e-05</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="B216" t="b">
@@ -5831,44 +5831,44 @@
         <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>0.8947260763235598</v>
+        <v>0.9975204928923559</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0006657019055000782</v>
+        <v>1.633921738917813e-35</v>
       </c>
       <c r="G216" t="n">
-        <v>0.10460822177094</v>
+        <v>0.002479507107644136</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="B217" t="b">
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E217" t="n">
-        <v>6.732205339595648e-06</v>
+        <v>0.0413936596864084</v>
       </c>
       <c r="F217" t="n">
-        <v>0.9999926736580962</v>
+        <v>1.58773258024779e-32</v>
       </c>
       <c r="G217" t="n">
-        <v>5.941365643320883e-07</v>
+        <v>0.9586063403135916</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="B218" t="b">
@@ -5881,94 +5881,94 @@
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>0.9895719578995754</v>
+        <v>0.9999111662938153</v>
       </c>
       <c r="F218" t="n">
-        <v>0.003274105700193829</v>
+        <v>3.489839835551912e-43</v>
       </c>
       <c r="G218" t="n">
-        <v>0.007153936400230643</v>
+        <v>8.883370618476572e-05</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="B219" t="b">
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E219" t="n">
-        <v>0.7962766391811822</v>
+        <v>5.15475726246204e-06</v>
       </c>
       <c r="F219" t="n">
-        <v>0.1492148209950559</v>
+        <v>2.152737289674116e-20</v>
       </c>
       <c r="G219" t="n">
-        <v>0.05450853982376188</v>
+        <v>0.9999948452427374</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="B220" t="b">
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>1.473205051428971e-05</v>
+        <v>0.6955614485672968</v>
       </c>
       <c r="F220" t="n">
-        <v>0.9999845748071973</v>
+        <v>1.470269549981756e-30</v>
       </c>
       <c r="G220" t="n">
-        <v>6.931422882425132e-07</v>
+        <v>0.3044385514327032</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="B221" t="b">
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E221" t="n">
-        <v>0.03660957707887492</v>
+        <v>0.0001078846109778446</v>
       </c>
       <c r="F221" t="n">
-        <v>0.9587579451962409</v>
+        <v>3.072528604465431e-17</v>
       </c>
       <c r="G221" t="n">
-        <v>0.004632477724884137</v>
+        <v>0.9998921153890221</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="B222" t="b">
@@ -5981,44 +5981,44 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>0.564574846931448</v>
+        <v>0.999938377043043</v>
       </c>
       <c r="F222" t="n">
-        <v>0.01199445828137632</v>
+        <v>5.52386635123357e-44</v>
       </c>
       <c r="G222" t="n">
-        <v>0.4234306947871755</v>
+        <v>6.162295695700293e-05</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B223" t="b">
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E223" t="n">
-        <v>0.002481094474045339</v>
+        <v>0.004835581297689611</v>
       </c>
       <c r="F223" t="n">
-        <v>0.997259998279124</v>
+        <v>2.152498354540545e-24</v>
       </c>
       <c r="G223" t="n">
-        <v>0.000258907246830792</v>
+        <v>0.9951644187023104</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B224" t="b">
@@ -6031,69 +6031,69 @@
         <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>0.9639299570017952</v>
+        <v>0.9181546323588633</v>
       </c>
       <c r="F224" t="n">
-        <v>0.00020799747780156</v>
+        <v>3.237225634764065e-32</v>
       </c>
       <c r="G224" t="n">
-        <v>0.03586204552040333</v>
+        <v>0.08184536764113669</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E225" t="n">
-        <v>0.9687729101410842</v>
+        <v>0.001473973451602997</v>
       </c>
       <c r="F225" t="n">
-        <v>0.0001837883012809572</v>
+        <v>1.166376182036637e-21</v>
       </c>
       <c r="G225" t="n">
-        <v>0.03104330155763486</v>
+        <v>0.9985260265483971</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B226" t="b">
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E226" t="n">
-        <v>0.0002586164319764972</v>
+        <v>2.54894926290638e-09</v>
       </c>
       <c r="F226" t="n">
-        <v>0.9997045225784467</v>
+        <v>5.740271832383451e-05</v>
       </c>
       <c r="G226" t="n">
-        <v>3.68609895767474e-05</v>
+        <v>0.9999425947327268</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B227" t="b">
@@ -6106,44 +6106,44 @@
         <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5613310781946106</v>
+        <v>0.9999999999980993</v>
       </c>
       <c r="F227" t="n">
-        <v>4.182834601356295e-07</v>
+        <v>2.459292022266274e-62</v>
       </c>
       <c r="G227" t="n">
-        <v>0.4386685035219293</v>
+        <v>1.900638071646845e-12</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B228" t="b">
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8445283649212669</v>
+        <v>0.3383294231383869</v>
       </c>
       <c r="F228" t="n">
-        <v>3.870316058996864e-05</v>
+        <v>2.213598762596805e-29</v>
       </c>
       <c r="G228" t="n">
-        <v>0.1554329319181433</v>
+        <v>0.6616705768616131</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B229" t="b">
@@ -6156,19 +6156,19 @@
         <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>0.9831864300472439</v>
+        <v>0.9997981592442535</v>
       </c>
       <c r="F229" t="n">
-        <v>2.532158338494706e-05</v>
+        <v>2.160808266721066e-36</v>
       </c>
       <c r="G229" t="n">
-        <v>0.0167882483693712</v>
+        <v>0.0002018407557463978</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B230" t="b">
@@ -6181,19 +6181,19 @@
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>0.7827094103368046</v>
+        <v>0.9999999999998308</v>
       </c>
       <c r="F230" t="n">
-        <v>7.329641413188417e-06</v>
+        <v>4.813105345036381e-70</v>
       </c>
       <c r="G230" t="n">
-        <v>0.2172832600217823</v>
+        <v>1.691407619938403e-13</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B231" t="b">
@@ -6206,19 +6206,19 @@
         <v>3</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3849221214670574</v>
+        <v>3.844463197295467e-08</v>
       </c>
       <c r="F231" t="n">
-        <v>6.868151523914532e-09</v>
+        <v>1.677024592386758e-11</v>
       </c>
       <c r="G231" t="n">
-        <v>0.615077871664791</v>
+        <v>0.9999999615385978</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B232" t="b">
@@ -6231,19 +6231,19 @@
         <v>3</v>
       </c>
       <c r="E232" t="n">
-        <v>0.4810137190931283</v>
+        <v>0.1817923521007524</v>
       </c>
       <c r="F232" t="n">
-        <v>1.836940141246471e-08</v>
+        <v>1.181560912387329e-28</v>
       </c>
       <c r="G232" t="n">
-        <v>0.5189862625374702</v>
+        <v>0.8182076478992476</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B233" t="b">
@@ -6256,19 +6256,19 @@
         <v>3</v>
       </c>
       <c r="E233" t="n">
-        <v>0.4725689349784083</v>
+        <v>0.02651583218129693</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0001715963303868841</v>
+        <v>8.143573813522776e-24</v>
       </c>
       <c r="G233" t="n">
-        <v>0.5272594686912049</v>
+        <v>0.973484167818703</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B234" t="b">
@@ -6281,13 +6281,1938 @@
         <v>1</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5783580727174458</v>
+        <v>0.999999999858479</v>
       </c>
       <c r="F234" t="n">
-        <v>8.804990003511908e-08</v>
+        <v>7.334337982309767e-57</v>
       </c>
       <c r="G234" t="n">
-        <v>0.4216418392326543</v>
+        <v>1.415209642846558e-10</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B235" t="b">
+        <v>0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.000973570071988631</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1.884017073273921e-21</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.9990264299280114</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B236" t="b">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0.9999999999997662</v>
+      </c>
+      <c r="F236" t="n">
+        <v>8.349938843540793e-68</v>
+      </c>
+      <c r="G236" t="n">
+        <v>2.337122063737881e-13</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B237" t="b">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.8682652512166414</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1.304045933370081e-32</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.1317347487833585</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>LSC-14</t>
+        </is>
+      </c>
+      <c r="B238" t="b">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3</v>
+      </c>
+      <c r="D238" t="n">
+        <v>3</v>
+      </c>
+      <c r="E238" t="n">
+        <v>3.279974155102559e-07</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.8134028059414e-09</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.9999996701891818</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="B239" t="b">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" t="n">
+        <v>3</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.436736233479349e-09</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1.313301712513713e-10</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.9999999984319337</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>LSC-16</t>
+        </is>
+      </c>
+      <c r="B240" t="b">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.9999541864067618</v>
+      </c>
+      <c r="F240" t="n">
+        <v>5.522984145907315e-43</v>
+      </c>
+      <c r="G240" t="n">
+        <v>4.581359323815356e-05</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>LSC-17</t>
+        </is>
+      </c>
+      <c r="B241" t="b">
+        <v>1</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="n">
+        <v>3</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.100788981938709</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.388523814739045e-26</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.899211018061291</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>LSC-18</t>
+        </is>
+      </c>
+      <c r="B242" t="b">
+        <v>0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1.762576643155634e-13</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.9999515714195404</v>
+      </c>
+      <c r="G242" t="n">
+        <v>4.842858028322997e-05</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>LSC-19</t>
+        </is>
+      </c>
+      <c r="B243" t="b">
+        <v>0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.01736053135516948</v>
+      </c>
+      <c r="F243" t="n">
+        <v>7.554296986154411e-23</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0.9826394686448305</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>LSC-20</t>
+        </is>
+      </c>
+      <c r="B244" t="b">
+        <v>0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.01871604386135573</v>
+      </c>
+      <c r="F244" t="n">
+        <v>9.820327856056327e-23</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0.9812839561386442</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="B245" t="b">
+        <v>0</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.04760533710968624</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.016493615173269e-29</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0.9523946628903138</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>LSC-22</t>
+        </is>
+      </c>
+      <c r="B246" t="b">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.08189809849598505</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1.185593883459653e-21</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0.9181019015040149</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>LSC-23</t>
+        </is>
+      </c>
+      <c r="B247" t="b">
+        <v>0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.8816146094874469</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1.231809806556619e-36</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0.1183853905125532</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>SCR-05</t>
+        </is>
+      </c>
+      <c r="B248" t="b">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.938323146861433</v>
+      </c>
+      <c r="F248" t="n">
+        <v>2.765514827542879e-33</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0.061676853138567</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>LSC-24</t>
+        </is>
+      </c>
+      <c r="B249" t="b">
+        <v>1</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.9938703069845746</v>
+      </c>
+      <c r="F249" t="n">
+        <v>5.893127491478644e-39</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0.006129693015425484</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>LSC-25</t>
+        </is>
+      </c>
+      <c r="B250" t="b">
+        <v>0</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.9977969200093701</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1.789053461295778e-39</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0.002203079990629939</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>LSC-26</t>
+        </is>
+      </c>
+      <c r="B251" t="b">
+        <v>0</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.9991987411930573</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1.206056566286365e-40</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.0008012588069427731</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>LSC-27</t>
+        </is>
+      </c>
+      <c r="B252" t="b">
+        <v>0</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.6066147530059379</v>
+      </c>
+      <c r="F252" t="n">
+        <v>4.636494393095663e-32</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.3933852469940621</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="B253" t="b">
+        <v>0</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3</v>
+      </c>
+      <c r="D253" t="n">
+        <v>3</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.01059809146738633</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1.956158904657223e-23</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0.9894019085326136</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="B254" t="b">
+        <v>0</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3</v>
+      </c>
+      <c r="E254" t="n">
+        <v>2.152172007182388e-12</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.1195852538928943</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0.8804147461049535</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="B255" t="b">
+        <v>0</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2</v>
+      </c>
+      <c r="E255" t="n">
+        <v>6.893313924764092e-17</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.9991222370695466</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0.0008777629304534548</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>LSC-30</t>
+        </is>
+      </c>
+      <c r="B256" t="b">
+        <v>0</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.007698056711547942</v>
+      </c>
+      <c r="F256" t="n">
+        <v>2.223868279993944e-26</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0.992301943288452</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>LSC-31</t>
+        </is>
+      </c>
+      <c r="B257" t="b">
+        <v>0</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.002737404382794862</v>
+      </c>
+      <c r="F257" t="n">
+        <v>5.496115118174016e-25</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0.9972625956172051</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="B258" t="b">
+        <v>0</v>
+      </c>
+      <c r="C258" t="n">
+        <v>2</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2</v>
+      </c>
+      <c r="E258" t="n">
+        <v>3.580721918993571e-16</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0.9975692705260121</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0.002430729473987385</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>LSC-33</t>
+        </is>
+      </c>
+      <c r="B259" t="b">
+        <v>0</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3</v>
+      </c>
+      <c r="E259" t="n">
+        <v>8.797954981786089e-07</v>
+      </c>
+      <c r="F259" t="n">
+        <v>6.483138222902876e-16</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0.9999991202045011</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>LSC-34</t>
+        </is>
+      </c>
+      <c r="B260" t="b">
+        <v>0</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.5113627022844083</v>
+      </c>
+      <c r="F260" t="n">
+        <v>8.128039932095475e-34</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0.4886372977155917</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>LSC-35</t>
+        </is>
+      </c>
+      <c r="B261" t="b">
+        <v>0</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1.177632430259274e-09</v>
+      </c>
+      <c r="F261" t="n">
+        <v>2.002636634782807e-09</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.9999999968197308</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>LSC-36</t>
+        </is>
+      </c>
+      <c r="B262" t="b">
+        <v>0</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1.800129107544499e-05</v>
+      </c>
+      <c r="F262" t="n">
+        <v>5.236965985232905e-18</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0.9999819987089247</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="B263" t="b">
+        <v>0</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3</v>
+      </c>
+      <c r="E263" t="n">
+        <v>2.9945726128416e-11</v>
+      </c>
+      <c r="F263" t="n">
+        <v>4.098444363485444e-05</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0.9999590155264194</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>SCR-07</t>
+        </is>
+      </c>
+      <c r="B264" t="b">
+        <v>0</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.01191408062119542</v>
+      </c>
+      <c r="F264" t="n">
+        <v>3.914252695954281e-25</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0.9880859193788045</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>LSC-38</t>
+        </is>
+      </c>
+      <c r="B265" t="b">
+        <v>0</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.6602429471312441</v>
+      </c>
+      <c r="F265" t="n">
+        <v>8.153036295261565e-32</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0.339757052868756</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>LSC-39</t>
+        </is>
+      </c>
+      <c r="B266" t="b">
+        <v>0</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.999685778823274</v>
+      </c>
+      <c r="F266" t="n">
+        <v>7.760841568720996e-42</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0.0003142211767259779</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>LSC-40</t>
+        </is>
+      </c>
+      <c r="B267" t="b">
+        <v>0</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.001063172405406924</v>
+      </c>
+      <c r="F267" t="n">
+        <v>6.699461368704255e-23</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0.9989368275945931</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>LSC-41</t>
+        </is>
+      </c>
+      <c r="B268" t="b">
+        <v>0</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.9997457687801306</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1.259921851364677e-45</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0.0002542312198695137</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>LSC-42</t>
+        </is>
+      </c>
+      <c r="B269" t="b">
+        <v>0</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3</v>
+      </c>
+      <c r="D269" t="n">
+        <v>3</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.0002616920273243704</v>
+      </c>
+      <c r="F269" t="n">
+        <v>4.171697000952332e-22</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0.9997383079726757</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="B270" t="b">
+        <v>0</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3</v>
+      </c>
+      <c r="D270" t="n">
+        <v>3</v>
+      </c>
+      <c r="E270" t="n">
+        <v>3.213853407524321e-05</v>
+      </c>
+      <c r="F270" t="n">
+        <v>5.325414804438009e-20</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0.9999678614659248</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>LSC-44</t>
+        </is>
+      </c>
+      <c r="B271" t="b">
+        <v>0</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3</v>
+      </c>
+      <c r="D271" t="n">
+        <v>3</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.000324121811101687</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1.64037336005604e-20</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0.9996758781888982</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B272" t="b">
+        <v>0</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3</v>
+      </c>
+      <c r="E272" t="n">
+        <v>3.433282198896874e-11</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.0004855510288444942</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0.9995144489368226</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>LSC-46</t>
+        </is>
+      </c>
+      <c r="B273" t="b">
+        <v>0</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3</v>
+      </c>
+      <c r="D273" t="n">
+        <v>3</v>
+      </c>
+      <c r="E273" t="n">
+        <v>6.019917381314734e-11</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.001426045232730693</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.9985739547070702</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B274" t="b">
+        <v>0</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3</v>
+      </c>
+      <c r="D274" t="n">
+        <v>3</v>
+      </c>
+      <c r="E274" t="n">
+        <v>8.111046702048509e-14</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.4060544925720898</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.593945507427829</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B275" t="b">
+        <v>0</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3</v>
+      </c>
+      <c r="D275" t="n">
+        <v>3</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1.87646255250041e-10</v>
+      </c>
+      <c r="F275" t="n">
+        <v>8.197919315077676e-08</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0.9999999178331606</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>LSC-49</t>
+        </is>
+      </c>
+      <c r="B276" t="b">
+        <v>0</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3</v>
+      </c>
+      <c r="D276" t="n">
+        <v>3</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1.495800896865028e-11</v>
+      </c>
+      <c r="F276" t="n">
+        <v>8.113394668072963e-05</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.9999188660383612</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>LSC-50</t>
+        </is>
+      </c>
+      <c r="B277" t="b">
+        <v>0</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3</v>
+      </c>
+      <c r="D277" t="n">
+        <v>3</v>
+      </c>
+      <c r="E277" t="n">
+        <v>2.155145166290903e-09</v>
+      </c>
+      <c r="F277" t="n">
+        <v>5.762054913025704e-09</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.9999999920827999</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>LSC-51</t>
+        </is>
+      </c>
+      <c r="B278" t="b">
+        <v>0</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3</v>
+      </c>
+      <c r="D278" t="n">
+        <v>3</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.002026640190389209</v>
+      </c>
+      <c r="F278" t="n">
+        <v>3.566748801922342e-22</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0.9979733598096108</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>LSC-52</t>
+        </is>
+      </c>
+      <c r="B279" t="b">
+        <v>0</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0.9999999997679165</v>
+      </c>
+      <c r="F279" t="n">
+        <v>7.886824801655651e-58</v>
+      </c>
+      <c r="G279" t="n">
+        <v>2.320834809465731e-10</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B280" t="b">
+        <v>1</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.9921625352196256</v>
+      </c>
+      <c r="F280" t="n">
+        <v>2.810641108415308e-37</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0.007837464780374458</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>LSC-54</t>
+        </is>
+      </c>
+      <c r="B281" t="b">
+        <v>0</v>
+      </c>
+      <c r="C281" t="n">
+        <v>1</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.7272745145713013</v>
+      </c>
+      <c r="F281" t="n">
+        <v>1.190927851874059e-33</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0.2727254854286987</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B282" t="b">
+        <v>0</v>
+      </c>
+      <c r="C282" t="n">
+        <v>3</v>
+      </c>
+      <c r="D282" t="n">
+        <v>3</v>
+      </c>
+      <c r="E282" t="n">
+        <v>2.369875468593249e-06</v>
+      </c>
+      <c r="F282" t="n">
+        <v>1.495244186420027e-17</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0.9999976301245314</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B283" t="b">
+        <v>0</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3</v>
+      </c>
+      <c r="D283" t="n">
+        <v>3</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.005572051047711145</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1.254599330355979e-26</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0.9944279489522888</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B284" t="b">
+        <v>0</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.9994154258552613</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1.638140246144911e-45</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0.0005845741447387961</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B285" t="b">
+        <v>0</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.01977728477273527</v>
+      </c>
+      <c r="F285" t="n">
+        <v>2.240580534705122e-25</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0.9802227152272647</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B286" t="b">
+        <v>0</v>
+      </c>
+      <c r="C286" t="n">
+        <v>1</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.9968678558562892</v>
+      </c>
+      <c r="F286" t="n">
+        <v>5.701211931724273e-40</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0.003132144143710733</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B287" t="b">
+        <v>0</v>
+      </c>
+      <c r="C287" t="n">
+        <v>3</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3</v>
+      </c>
+      <c r="E287" t="n">
+        <v>2.909827658061603e-06</v>
+      </c>
+      <c r="F287" t="n">
+        <v>1.058547702071358e-16</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.9999970901723417</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>LSC-61</t>
+        </is>
+      </c>
+      <c r="B288" t="b">
+        <v>0</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3</v>
+      </c>
+      <c r="D288" t="n">
+        <v>3</v>
+      </c>
+      <c r="E288" t="n">
+        <v>8.559378663863343e-10</v>
+      </c>
+      <c r="F288" t="n">
+        <v>2.166145450531793e-06</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0.9999978329986116</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B289" t="b">
+        <v>0</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3</v>
+      </c>
+      <c r="D289" t="n">
+        <v>3</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.002848292670818651</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3.813065029422325e-21</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0.9971517073291815</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B290" t="b">
+        <v>0</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.1872529666457595</v>
+      </c>
+      <c r="F290" t="n">
+        <v>4.48853772568646e-28</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0.8127470333542405</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>LSC-63</t>
+        </is>
+      </c>
+      <c r="B291" t="b">
+        <v>0</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3</v>
+      </c>
+      <c r="D291" t="n">
+        <v>3</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1.508508664928894e-08</v>
+      </c>
+      <c r="F291" t="n">
+        <v>1.015358038642906e-06</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0.9999989695568747</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B292" t="b">
+        <v>1</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.9999999999605622</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1.64577733998495e-58</v>
+      </c>
+      <c r="G292" t="n">
+        <v>3.943772620685546e-11</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B293" t="b">
+        <v>0</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3</v>
+      </c>
+      <c r="D293" t="n">
+        <v>3</v>
+      </c>
+      <c r="E293" t="n">
+        <v>0.3495898136424769</v>
+      </c>
+      <c r="F293" t="n">
+        <v>7.517622453527572e-26</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0.650410186357523</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>DR-146</t>
+        </is>
+      </c>
+      <c r="B294" t="b">
+        <v>0</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3</v>
+      </c>
+      <c r="D294" t="n">
+        <v>3</v>
+      </c>
+      <c r="E294" t="n">
+        <v>9.196166308689432e-05</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1.28530750457627e-09</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0.9999080370516056</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>DR-147</t>
+        </is>
+      </c>
+      <c r="B295" t="b">
+        <v>0</v>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.9531773723428593</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1.212777018932982e-29</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0.04682262765714058</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>DR-148</t>
+        </is>
+      </c>
+      <c r="B296" t="b">
+        <v>0</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1.128155025203961e-07</v>
+      </c>
+      <c r="F296" t="n">
+        <v>6.808068339256836e-10</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0.9999998865036905</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>DR-149</t>
+        </is>
+      </c>
+      <c r="B297" t="b">
+        <v>0</v>
+      </c>
+      <c r="C297" t="n">
+        <v>3</v>
+      </c>
+      <c r="D297" t="n">
+        <v>3</v>
+      </c>
+      <c r="E297" t="n">
+        <v>5.687531120734105e-06</v>
+      </c>
+      <c r="F297" t="n">
+        <v>3.830944453148865e-07</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0.999993929374434</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>DR-150</t>
+        </is>
+      </c>
+      <c r="B298" t="b">
+        <v>0</v>
+      </c>
+      <c r="C298" t="n">
+        <v>2</v>
+      </c>
+      <c r="D298" t="n">
+        <v>2</v>
+      </c>
+      <c r="E298" t="n">
+        <v>3.157429120638231e-19</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.9999955973727481</v>
+      </c>
+      <c r="G298" t="n">
+        <v>4.402627251842001e-06</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B299" t="b">
+        <v>0</v>
+      </c>
+      <c r="C299" t="n">
+        <v>3</v>
+      </c>
+      <c r="D299" t="n">
+        <v>3</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1.112384426951539e-06</v>
+      </c>
+      <c r="F299" t="n">
+        <v>2.300545329107072e-14</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0.9999988876155501</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>DR-151</t>
+        </is>
+      </c>
+      <c r="B300" t="b">
+        <v>0</v>
+      </c>
+      <c r="C300" t="n">
+        <v>3</v>
+      </c>
+      <c r="D300" t="n">
+        <v>3</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.05156094017344572</v>
+      </c>
+      <c r="F300" t="n">
+        <v>2.411996714175075e-18</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0.9484390598265543</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>DR-152</t>
+        </is>
+      </c>
+      <c r="B301" t="b">
+        <v>0</v>
+      </c>
+      <c r="C301" t="n">
+        <v>1</v>
+      </c>
+      <c r="D301" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.9999915562857961</v>
+      </c>
+      <c r="F301" t="n">
+        <v>3.622736204711302e-43</v>
+      </c>
+      <c r="G301" t="n">
+        <v>8.443714203960048e-06</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>DR-154</t>
+        </is>
+      </c>
+      <c r="B302" t="b">
+        <v>0</v>
+      </c>
+      <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.7325076112933611</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1.828515937385743e-29</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0.2674923887066389</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>DR-155</t>
+        </is>
+      </c>
+      <c r="B303" t="b">
+        <v>0</v>
+      </c>
+      <c r="C303" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" t="n">
+        <v>2</v>
+      </c>
+      <c r="E303" t="n">
+        <v>2.011226996628609e-17</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.9999977043732314</v>
+      </c>
+      <c r="G303" t="n">
+        <v>2.295626768438919e-06</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B304" t="b">
+        <v>0</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.9998583256430906</v>
+      </c>
+      <c r="F304" t="n">
+        <v>5.545242085541379e-44</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0.0001416743569093358</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B305" t="b">
+        <v>1</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" t="n">
+        <v>3</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.4133489369190837</v>
+      </c>
+      <c r="F305" t="n">
+        <v>5.143367635951179e-28</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0.5866510630809163</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>DR-158</t>
+        </is>
+      </c>
+      <c r="B306" t="b">
+        <v>0</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0.01833111369758912</v>
+      </c>
+      <c r="F306" t="n">
+        <v>8.694945228062813e-26</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0.9816688863024109</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B307" t="b">
+        <v>0</v>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.9999999999999991</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1.74798627420778e-77</v>
+      </c>
+      <c r="G307" t="n">
+        <v>9.157178065411441e-16</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="B308" t="b">
+        <v>0</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.9856538617896731</v>
+      </c>
+      <c r="F308" t="n">
+        <v>6.761546241632487e-42</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0.01434613821032687</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>LSC-65</t>
+        </is>
+      </c>
+      <c r="B309" t="b">
+        <v>0</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.9324584860554527</v>
+      </c>
+      <c r="F309" t="n">
+        <v>9.478871782851233e-39</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0.06754151394454742</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="B310" t="b">
+        <v>0</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3</v>
+      </c>
+      <c r="D310" t="n">
+        <v>3</v>
+      </c>
+      <c r="E310" t="n">
+        <v>3.953443266808728e-05</v>
+      </c>
+      <c r="F310" t="n">
+        <v>9.197015235686526e-21</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0.9999604655673319</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="B311" t="b">
+        <v>0</v>
+      </c>
+      <c r="C311" t="n">
+        <v>3</v>
+      </c>
+      <c r="D311" t="n">
+        <v>3</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.0002487349002032935</v>
+      </c>
+      <c r="F311" t="n">
+        <v>5.147676483388388e-26</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0.9997512650997966</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
@@ -475,19 +475,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.087407458217597e-07</v>
+        <v>0.9974498653622463</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004454550784634666</v>
+        <v>0.002550134637753637</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9995542361807908</v>
+        <v>1.467033863945152e-18</v>
       </c>
     </row>
     <row r="3">
@@ -503,16 +503,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4914004173276788</v>
+        <v>0.998752729442381</v>
       </c>
       <c r="F3" t="n">
-        <v>1.76298911609951e-21</v>
+        <v>0.001247270557618951</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5085995826723212</v>
+        <v>9.474796039594086e-27</v>
       </c>
     </row>
     <row r="4">
@@ -531,13 +531,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9923109997065596</v>
+        <v>0.9999820623591859</v>
       </c>
       <c r="F4" t="n">
-        <v>3.164110014493942e-31</v>
+        <v>1.793764081405901e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007689000293440389</v>
+        <v>2.639156918384471e-19</v>
       </c>
     </row>
     <row r="5">
@@ -550,19 +550,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>5.591281972096291e-41</v>
+        <v>0.8881088149931345</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.1118911850068655</v>
       </c>
       <c r="G5" t="n">
-        <v>1.802842715030217e-22</v>
+        <v>2.335917809268925e-34</v>
       </c>
     </row>
     <row r="6">
@@ -581,13 +581,13 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999832426546784</v>
+        <v>0.9636676644647262</v>
       </c>
       <c r="F6" t="n">
-        <v>1.306677823309202e-38</v>
+        <v>0.03633233553527394</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67573453217262e-05</v>
+        <v>1.187879582126876e-39</v>
       </c>
     </row>
     <row r="7">
@@ -600,19 +600,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009466166955558028</v>
+        <v>0.9990209261705724</v>
       </c>
       <c r="F7" t="n">
-        <v>1.044460087014875e-17</v>
+        <v>0.0009790738294276837</v>
       </c>
       <c r="G7" t="n">
-        <v>0.990533833044442</v>
+        <v>7.981688091680475e-29</v>
       </c>
     </row>
     <row r="8">
@@ -631,13 +631,13 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8398950809379471</v>
+        <v>0.9963421466445079</v>
       </c>
       <c r="F8" t="n">
-        <v>1.578134166518372e-33</v>
+        <v>0.003657852194654749</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1601049190620529</v>
+        <v>1.160837427454919e-09</v>
       </c>
     </row>
     <row r="9">
@@ -647,22 +647,22 @@
         </is>
       </c>
       <c r="B9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>4.098311769095971e-08</v>
+        <v>0.772986580653004</v>
       </c>
       <c r="F9" t="n">
-        <v>1.389305986185035e-13</v>
+        <v>0.2270134193469959</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9999999590167433</v>
+        <v>1.547904749260524e-19</v>
       </c>
     </row>
     <row r="10">
@@ -681,13 +681,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9997911998552943</v>
+        <v>0.9218083795222423</v>
       </c>
       <c r="F10" t="n">
-        <v>5.202797010085763e-46</v>
+        <v>0.07819162047775782</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002088001447057823</v>
+        <v>3.154206650942864e-34</v>
       </c>
     </row>
     <row r="11">
@@ -706,13 +706,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9969974431840656</v>
+        <v>0.9944989068750124</v>
       </c>
       <c r="F11" t="n">
-        <v>7.199514498689118e-42</v>
+        <v>0.005501093124987577</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00300255681593442</v>
+        <v>1.588017514333789e-26</v>
       </c>
     </row>
     <row r="12">
@@ -725,19 +725,19 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2.611832215504022e-11</v>
+        <v>0.2465991431001034</v>
       </c>
       <c r="F12" t="n">
-        <v>3.501167734718652e-05</v>
+        <v>0.7534008568998967</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9999649882965345</v>
+        <v>1.178079781245579e-18</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="B13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2.010106612071253e-06</v>
+        <v>0.9384714537499251</v>
       </c>
       <c r="F13" t="n">
-        <v>1.548740374912976e-16</v>
+        <v>0.06152488859827776</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9999979898933877</v>
+        <v>3.657651797018479e-06</v>
       </c>
     </row>
     <row r="14">
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8080806095201328</v>
+        <v>0.9999903414547487</v>
       </c>
       <c r="F14" t="n">
-        <v>2.574192200577748e-30</v>
+        <v>9.656150967323422e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1919193904798671</v>
+        <v>2.394283841227986e-09</v>
       </c>
     </row>
     <row r="15">
@@ -800,19 +800,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004567424675958377</v>
+        <v>0.9809454280924567</v>
       </c>
       <c r="F15" t="n">
-        <v>1.307425154089226e-26</v>
+        <v>0.01905457190754335</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9954325753240416</v>
+        <v>4.498797628168144e-24</v>
       </c>
     </row>
     <row r="16">
@@ -825,19 +825,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>7.032263721216192e-49</v>
+        <v>3.124375667252805e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.418377383863167e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>1.330922383340078e-27</v>
+        <v>0.9999954572469488</v>
       </c>
     </row>
     <row r="17">
@@ -850,19 +850,19 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.928582176072454e-06</v>
+        <v>0.9984913654478864</v>
       </c>
       <c r="F17" t="n">
-        <v>1.502098810388144e-16</v>
+        <v>0.001508634552113599</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9999970714178238</v>
+        <v>1.378911087055579e-20</v>
       </c>
     </row>
     <row r="18">
@@ -875,19 +875,19 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>4.550041318435578e-33</v>
+        <v>8.701810171668019e-18</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>1.73289644088277e-18</v>
       </c>
       <c r="G18" t="n">
-        <v>9.738331216437072e-17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -906,13 +906,13 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>7.541212149956982e-52</v>
+        <v>0.3988116546943388</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.6011883453055894</v>
       </c>
       <c r="G19" t="n">
-        <v>2.658079960030139e-29</v>
+        <v>7.192701504395306e-14</v>
       </c>
     </row>
     <row r="20">
@@ -925,19 +925,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005432446568790727</v>
+        <v>0.9999896704916958</v>
       </c>
       <c r="F20" t="n">
-        <v>2.712763681233794e-23</v>
+        <v>1.032950830413329e-05</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9945675534312093</v>
+        <v>6.380929209401282e-17</v>
       </c>
     </row>
     <row r="21">
@@ -950,19 +950,19 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>9.530089124385959e-15</v>
+        <v>0.6369431262158399</v>
       </c>
       <c r="F21" t="n">
-        <v>0.878740970287779</v>
+        <v>0.3630568737819351</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1212590297122116</v>
+        <v>2.225042520060694e-12</v>
       </c>
     </row>
     <row r="22">
@@ -975,19 +975,19 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1.947223043681752e-07</v>
+        <v>0.9999874062888694</v>
       </c>
       <c r="F22" t="n">
-        <v>3.702775517301102e-15</v>
+        <v>1.259371113060668e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9999998052776919</v>
+        <v>1.703919512633276e-24</v>
       </c>
     </row>
     <row r="23">
@@ -1000,19 +1000,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>1.214525477926596e-14</v>
+        <v>6.95075596628408e-19</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9980637300967947</v>
+        <v>9.23806991212004e-22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001936269903193108</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1031,13 +1031,13 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.866588397325232e-79</v>
+        <v>0.2240663132706526</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.7759336867293475</v>
       </c>
       <c r="G24" t="n">
-        <v>2.516254454230679e-51</v>
+        <v>4.686895349388496e-53</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -1056,13 +1056,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>8.661513651670974e-32</v>
+        <v>0.4576909110867951</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.542309088913205</v>
       </c>
       <c r="G25" t="n">
-        <v>3.271755151167421e-17</v>
+        <v>1.74450989391711e-34</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -1081,13 +1081,13 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4.188245128938946e-42</v>
+        <v>0.2803859731094322</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.7196140268876227</v>
       </c>
       <c r="G26" t="n">
-        <v>5.765329706443533e-24</v>
+        <v>2.945006065023606e-12</v>
       </c>
     </row>
     <row r="27">
@@ -1100,19 +1100,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1.821732616404615e-57</v>
+        <v>2.43092219663653e-27</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>1.312771402995716e-30</v>
       </c>
       <c r="G27" t="n">
-        <v>1.560970380667772e-37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="B28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.552559975159302e-29</v>
+        <v>0.1532082812487736</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9999999999999027</v>
+        <v>0.0007260021743408798</v>
       </c>
       <c r="G28" t="n">
-        <v>9.733214621016334e-14</v>
+        <v>0.8460657165768855</v>
       </c>
     </row>
     <row r="29">
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="B29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>2.741206003103437e-38</v>
+        <v>4.150956638193203e-129</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>5.606193087830236e-138</v>
       </c>
       <c r="G29" t="n">
-        <v>6.813549918722915e-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1175,19 +1175,19 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>1.854326531038739e-22</v>
+        <v>3.008155015899652e-56</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9999999997533553</v>
+        <v>2.910855129134498e-59</v>
       </c>
       <c r="G30" t="n">
-        <v>2.466447232439013e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1200,19 +1200,19 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>4.750234082104595e-44</v>
+        <v>0.6717665684721295</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.3282334315278629</v>
       </c>
       <c r="G31" t="n">
-        <v>8.243439691575271e-24</v>
+        <v>7.563093153151979e-15</v>
       </c>
     </row>
     <row r="32">
@@ -1231,13 +1231,13 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>4.612486712971901e-57</v>
+        <v>0.009632252489449114</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.9903677475101794</v>
       </c>
       <c r="G32" t="n">
-        <v>7.894664766377426e-33</v>
+        <v>3.714466380308182e-13</v>
       </c>
     </row>
     <row r="33">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="B33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>6.712395074666319e-31</v>
+        <v>2.66232254093986e-43</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9999999999999725</v>
+        <v>1.11266761474873e-50</v>
       </c>
       <c r="G33" t="n">
-        <v>2.743268276460132e-14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1275,19 +1275,19 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.449532166197732e-73</v>
+        <v>0.04333350049406969</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.06057350193081879</v>
       </c>
       <c r="G34" t="n">
-        <v>7.416023577513104e-45</v>
+        <v>0.8960929975751115</v>
       </c>
     </row>
     <row r="35">
@@ -1300,19 +1300,19 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0005415236098069511</v>
+        <v>0.999927598101092</v>
       </c>
       <c r="F35" t="n">
-        <v>3.249461217081503e-16</v>
+        <v>7.24018989079139e-05</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9994584763901927</v>
+        <v>4.916197345101366e-35</v>
       </c>
     </row>
     <row r="36">
@@ -1325,19 +1325,19 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>2.116637667430632e-07</v>
+        <v>0.9999802646698374</v>
       </c>
       <c r="F36" t="n">
-        <v>1.138747628527472e-08</v>
+        <v>1.973533016264458e-05</v>
       </c>
       <c r="G36" t="n">
-        <v>0.999999776948757</v>
+        <v>1.724801526153289e-29</v>
       </c>
     </row>
     <row r="37">
@@ -1350,19 +1350,19 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.496750149940891e-52</v>
+        <v>0.006416975032948294</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>1.906443616440184e-05</v>
       </c>
       <c r="G37" t="n">
-        <v>7.317863530130667e-32</v>
+        <v>0.9935639605308874</v>
       </c>
     </row>
     <row r="38">
@@ -1381,13 +1381,13 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>3.912093025267857e-38</v>
+        <v>0.09498466112074938</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.9050153388792506</v>
       </c>
       <c r="G38" t="n">
-        <v>6.994537947584044e-21</v>
+        <v>7.050015049737664e-32</v>
       </c>
     </row>
     <row r="39">
@@ -1400,19 +1400,19 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>9.244763094430002e-71</v>
+        <v>0.0005388038213686952</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>1.516545682472353e-05</v>
       </c>
       <c r="G39" t="n">
-        <v>5.601077577127239e-46</v>
+        <v>0.9994460307218066</v>
       </c>
     </row>
     <row r="40">
@@ -1425,19 +1425,19 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.736727069363971e-14</v>
+        <v>1.495612522761132e-26</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9995190353988762</v>
+        <v>2.596358540080893e-31</v>
       </c>
       <c r="G40" t="n">
-        <v>0.000480964601066419</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1450,19 +1450,19 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>9.231325602973444e-34</v>
+        <v>0.9999006813955612</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>9.931839703670421e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>4.376575301819715e-17</v>
+        <v>2.074020662935571e-10</v>
       </c>
     </row>
     <row r="42">
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>6.686264696723161e-22</v>
+        <v>0.7499714127064112</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9999999997206745</v>
+        <v>0.250026080215792</v>
       </c>
       <c r="G42" t="n">
-        <v>2.793255549220871e-10</v>
+        <v>2.507077796712183e-06</v>
       </c>
     </row>
     <row r="43">
@@ -1500,19 +1500,19 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>4.64346560390073e-38</v>
+        <v>0.9290654203917926</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0.07092911285065778</v>
       </c>
       <c r="G43" t="n">
-        <v>3.530453362548754e-21</v>
+        <v>5.466757549642126e-06</v>
       </c>
     </row>
     <row r="44">
@@ -1525,19 +1525,19 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.850466482091454e-25</v>
+        <v>0.6569798047148179</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9999999999890814</v>
+        <v>0.3430201952851822</v>
       </c>
       <c r="G44" t="n">
-        <v>1.091856927324187e-11</v>
+        <v>1.611510792553359e-35</v>
       </c>
     </row>
     <row r="45">
@@ -1550,19 +1550,19 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>2.409930092011533e-08</v>
+        <v>0.9997693669121318</v>
       </c>
       <c r="F45" t="n">
-        <v>2.242707565813235e-08</v>
+        <v>0.0002306330878681958</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9999999534736234</v>
+        <v>8.811591974323307e-51</v>
       </c>
     </row>
     <row r="46">
@@ -1575,19 +1575,19 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>4.662958791025905e-11</v>
+        <v>0.9952511476158195</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9773731871994982</v>
+        <v>0.004475958960352145</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02262681275387213</v>
+        <v>0.0002728934238284575</v>
       </c>
     </row>
     <row r="47">
@@ -1606,13 +1606,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8360529835718359</v>
+        <v>0.9983108016548048</v>
       </c>
       <c r="F47" t="n">
-        <v>6.684541515823535e-35</v>
+        <v>0.001689198344133037</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1639470164281642</v>
+        <v>1.062138385548015e-12</v>
       </c>
     </row>
     <row r="48">
@@ -1631,13 +1631,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9756114387067848</v>
+        <v>0.9108208495833645</v>
       </c>
       <c r="F48" t="n">
-        <v>3.009361454726731e-38</v>
+        <v>0.08917915041663542</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02438856129321522</v>
+        <v>2.022888951985608e-38</v>
       </c>
     </row>
     <row r="49">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1656,13 +1656,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9995526880205594</v>
+        <v>0.9350327730969752</v>
       </c>
       <c r="F49" t="n">
-        <v>6.905400780465352e-45</v>
+        <v>0.06496722690302491</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000447311979440594</v>
+        <v>1.527786265356812e-30</v>
       </c>
     </row>
     <row r="50">
@@ -1675,19 +1675,19 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0001097655519664342</v>
+        <v>0.9999360502509059</v>
       </c>
       <c r="F50" t="n">
-        <v>5.056432567670912e-22</v>
+        <v>6.394974909314845e-05</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9998902344480335</v>
+        <v>9.561284120974118e-16</v>
       </c>
     </row>
     <row r="51">
@@ -1697,22 +1697,22 @@
         </is>
       </c>
       <c r="B51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>2.242107158608158e-08</v>
+        <v>0.6229944085308912</v>
       </c>
       <c r="F51" t="n">
-        <v>6.625979709576053e-11</v>
+        <v>0.3770055914691088</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9999999775126686</v>
+        <v>9.907824469792886e-21</v>
       </c>
     </row>
     <row r="52">
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5435522104524301</v>
+        <v>0.9944182469771469</v>
       </c>
       <c r="F52" t="n">
-        <v>1.245777059550773e-33</v>
+        <v>0.005581753022853109</v>
       </c>
       <c r="G52" t="n">
-        <v>0.45644778954757</v>
+        <v>2.005702454277184e-27</v>
       </c>
     </row>
     <row r="53">
@@ -1750,19 +1750,19 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0009960660605856984</v>
+        <v>0.9999133405720879</v>
       </c>
       <c r="F53" t="n">
-        <v>7.85149837273157e-25</v>
+        <v>8.66594279122167e-05</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9990039339394142</v>
+        <v>1.059624237892311e-18</v>
       </c>
     </row>
     <row r="54">
@@ -1781,13 +1781,13 @@
         <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>3.82586783687399e-06</v>
+        <v>2.004943502035567e-14</v>
       </c>
       <c r="F54" t="n">
-        <v>1.214665132238641e-12</v>
+        <v>3.322913471479718e-14</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9999961741309483</v>
+        <v>0.9999999999999467</v>
       </c>
     </row>
     <row r="55">
@@ -1806,13 +1806,13 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0.999983015933076</v>
+        <v>0.9564962365211082</v>
       </c>
       <c r="F55" t="n">
-        <v>3.054583183313724e-48</v>
+        <v>0.04350376347889199</v>
       </c>
       <c r="G55" t="n">
-        <v>1.698406692397459e-05</v>
+        <v>3.032732997552055e-31</v>
       </c>
     </row>
     <row r="56">
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="B56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.061297653740543e-05</v>
+        <v>0.638536766897436</v>
       </c>
       <c r="F56" t="n">
-        <v>2.487595470297807e-16</v>
+        <v>0.3614589038808997</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9999693870234623</v>
+        <v>4.329221664260327e-06</v>
       </c>
     </row>
     <row r="57">
@@ -1856,13 +1856,13 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8033121004772862</v>
+        <v>0.9979730436751713</v>
       </c>
       <c r="F57" t="n">
-        <v>3.166693409134696e-33</v>
+        <v>0.002026956324822479</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1966878995227138</v>
+        <v>6.512314248976573e-15</v>
       </c>
     </row>
     <row r="58">
@@ -1872,22 +1872,22 @@
         </is>
       </c>
       <c r="B58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>5.173938765476805e-07</v>
+        <v>0.9195842620582673</v>
       </c>
       <c r="F58" t="n">
-        <v>1.34074020420173e-14</v>
+        <v>0.08041573793860067</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9999994826061099</v>
+        <v>3.131948992312367e-12</v>
       </c>
     </row>
     <row r="59">
@@ -1897,22 +1897,22 @@
         </is>
       </c>
       <c r="B59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0004766501040335004</v>
+        <v>0.9922004723671815</v>
       </c>
       <c r="F59" t="n">
-        <v>9.499084300941895e-24</v>
+        <v>0.0077995276315212</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9995233498959665</v>
+        <v>1.297101432264194e-12</v>
       </c>
     </row>
     <row r="60">
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>1.039839269974045e-16</v>
+        <v>3.732099145639373e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9992839879545359</v>
+        <v>3.250615407559886e-07</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0007160120454640274</v>
+        <v>0.9999623539470027</v>
       </c>
     </row>
     <row r="61">
@@ -1947,22 +1947,22 @@
         </is>
       </c>
       <c r="B61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9999829829335232</v>
+        <v>0.9705459698079257</v>
       </c>
       <c r="F61" t="n">
-        <v>1.460641766532878e-48</v>
+        <v>0.02945403019207438</v>
       </c>
       <c r="G61" t="n">
-        <v>1.701706647690897e-05</v>
+        <v>9.484674457049457e-31</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="B62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
         <v>3</v>
@@ -1981,13 +1981,13 @@
         <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>6.090220025578483e-06</v>
+        <v>3.295002152091984e-07</v>
       </c>
       <c r="F62" t="n">
-        <v>2.819620327627155e-20</v>
+        <v>1.366018203794167e-13</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9999939097799744</v>
+        <v>0.9999996704996481</v>
       </c>
     </row>
     <row r="63">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
         <v>3</v>
@@ -2006,13 +2006,13 @@
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004537031833414897</v>
+        <v>0.08927038467129274</v>
       </c>
       <c r="F63" t="n">
-        <v>6.399441533796586e-24</v>
+        <v>1.261260288793052e-08</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9995462968166585</v>
+        <v>0.9107296027161044</v>
       </c>
     </row>
     <row r="64">
@@ -2025,19 +2025,19 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.08231868989932635</v>
+        <v>0.8762125933602762</v>
       </c>
       <c r="F64" t="n">
-        <v>1.615892381075924e-20</v>
+        <v>0.1237874066397238</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9176813101006738</v>
+        <v>3.408474282215384e-57</v>
       </c>
     </row>
     <row r="65">
@@ -2050,19 +2050,19 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.511345487142944e-12</v>
+        <v>0.9999959937670201</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9375361035892245</v>
+        <v>4.006232979961294e-06</v>
       </c>
       <c r="G65" t="n">
-        <v>0.06246389640426421</v>
+        <v>1.576692438306417e-29</v>
       </c>
     </row>
     <row r="66">
@@ -2075,19 +2075,19 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>2.076738695538381e-32</v>
+        <v>0.9875301449467805</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0.01240070546251824</v>
       </c>
       <c r="G66" t="n">
-        <v>7.076261280490595e-18</v>
+        <v>6.91495907013125e-05</v>
       </c>
     </row>
     <row r="67">
@@ -2100,19 +2100,19 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>1.69893924574503e-06</v>
+        <v>0.9999960554273716</v>
       </c>
       <c r="F67" t="n">
-        <v>4.246651756084691e-10</v>
+        <v>3.944572628390219e-06</v>
       </c>
       <c r="G67" t="n">
-        <v>0.999998300636089</v>
+        <v>2.864153847845084e-25</v>
       </c>
     </row>
     <row r="68">
@@ -2125,19 +2125,19 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>6.509050868844883e-07</v>
+        <v>0.9999669789922229</v>
       </c>
       <c r="F68" t="n">
-        <v>8.915521145545311e-08</v>
+        <v>3.302100777716364e-05</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9999992599397017</v>
+        <v>1.930936588715053e-33</v>
       </c>
     </row>
     <row r="69">
@@ -2150,19 +2150,19 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1.499554926941969e-06</v>
+        <v>0.9999632945799031</v>
       </c>
       <c r="F69" t="n">
-        <v>1.478246291271676e-08</v>
+        <v>3.670542009705244e-05</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9999984856626103</v>
+        <v>4.697481973403386e-33</v>
       </c>
     </row>
     <row r="70">
@@ -2181,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>1.070463232524215e-36</v>
+        <v>0.002458855404762359</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0.9975411445952377</v>
       </c>
       <c r="G70" t="n">
-        <v>1.01490891292299e-20</v>
+        <v>2.406250744078365e-46</v>
       </c>
     </row>
     <row r="71">
@@ -2200,19 +2200,19 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.809032252351955e-07</v>
+        <v>0.9999987822540598</v>
       </c>
       <c r="F71" t="n">
-        <v>1.889492028984095e-07</v>
+        <v>1.217745940199271e-06</v>
       </c>
       <c r="G71" t="n">
-        <v>0.999999430147572</v>
+        <v>3.303265697648755e-22</v>
       </c>
     </row>
     <row r="72">
@@ -2231,13 +2231,13 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.332162093615787e-23</v>
+        <v>0.0002482543454250794</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9999999999931404</v>
+        <v>0.999751745654575</v>
       </c>
       <c r="G72" t="n">
-        <v>6.859644616125063e-12</v>
+        <v>8.488936488665015e-48</v>
       </c>
     </row>
     <row r="73">
@@ -2250,19 +2250,19 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0005404850378843065</v>
+        <v>0.9999948139210582</v>
       </c>
       <c r="F73" t="n">
-        <v>3.111546525476096e-16</v>
+        <v>5.125899779179261e-06</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9994595149621154</v>
+        <v>6.017916271040533e-08</v>
       </c>
     </row>
     <row r="74">
@@ -2275,19 +2275,19 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.448752294323436e-05</v>
+        <v>0.9999449407018309</v>
       </c>
       <c r="F74" t="n">
-        <v>2.297234455560046e-14</v>
+        <v>5.505929816906266e-05</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9999455124770338</v>
+        <v>6.833587995480438e-29</v>
       </c>
     </row>
     <row r="75">
@@ -2300,19 +2300,19 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7540090075931345</v>
+        <v>0.01098498864690647</v>
       </c>
       <c r="F75" t="n">
-        <v>2.564504534703931e-28</v>
+        <v>0.9890150113530936</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2459909924068655</v>
+        <v>5.66899518812121e-54</v>
       </c>
     </row>
     <row r="76">
@@ -2325,19 +2325,19 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2911907455286852</v>
+        <v>0.1442436633302083</v>
       </c>
       <c r="F76" t="n">
-        <v>5.919258866282412e-18</v>
+        <v>0.8557563366697917</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7088092544713148</v>
+        <v>7.023418906444119e-45</v>
       </c>
     </row>
     <row r="77">
@@ -2350,19 +2350,19 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.008041753323046859</v>
+        <v>0.9999417445798559</v>
       </c>
       <c r="F77" t="n">
-        <v>9.847088980091378e-21</v>
+        <v>5.825542014420381e-05</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9919582466769531</v>
+        <v>5.51696116189423e-35</v>
       </c>
     </row>
     <row r="78">
@@ -2375,19 +2375,19 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>1.370962407278819e-07</v>
+        <v>0.9999717728844356</v>
       </c>
       <c r="F78" t="n">
-        <v>2.646776667457095e-08</v>
+        <v>2.822711556440757e-05</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9999998364359927</v>
+        <v>1.321304559678692e-34</v>
       </c>
     </row>
     <row r="79">
@@ -2400,19 +2400,19 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1863344487229622</v>
+        <v>0.9635710096324143</v>
       </c>
       <c r="F79" t="n">
-        <v>1.111579768986998e-20</v>
+        <v>0.03642899036758569</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8136655512770379</v>
+        <v>3.410378636784788e-52</v>
       </c>
     </row>
     <row r="80">
@@ -2425,19 +2425,19 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.485460179297859e-27</v>
+        <v>0.9908313495555527</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9999999999990239</v>
+        <v>0.009168650444447188</v>
       </c>
       <c r="G80" t="n">
-        <v>9.760144507991976e-13</v>
+        <v>2.073313315216523e-31</v>
       </c>
     </row>
     <row r="81">
@@ -2450,19 +2450,19 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0002919310404194629</v>
+        <v>0.9999854122081221</v>
       </c>
       <c r="F81" t="n">
-        <v>2.452888329343602e-15</v>
+        <v>1.458779187791298e-05</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9997080689595781</v>
+        <v>1.00696922245563e-22</v>
       </c>
     </row>
     <row r="82">
@@ -2475,19 +2475,19 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>6.465432783197535e-06</v>
+        <v>0.999966910781521</v>
       </c>
       <c r="F82" t="n">
-        <v>1.448131979287122e-11</v>
+        <v>3.308921847890679e-05</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9999935345527354</v>
+        <v>1.41010689307958e-30</v>
       </c>
     </row>
     <row r="83">
@@ -2500,19 +2500,19 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>9.378264415970747e-05</v>
+        <v>0.9999696298656593</v>
       </c>
       <c r="F83" t="n">
-        <v>1.639093629470576e-16</v>
+        <v>3.037013434060333e-05</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9999062173558402</v>
+        <v>4.065163661332865e-25</v>
       </c>
     </row>
     <row r="84">
@@ -2531,13 +2531,13 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9999700030151101</v>
+        <v>0.9998328595992477</v>
       </c>
       <c r="F84" t="n">
-        <v>6.840333330053895e-40</v>
+        <v>0.0001671404007521673</v>
       </c>
       <c r="G84" t="n">
-        <v>2.999698488987039e-05</v>
+        <v>1.120452697030819e-20</v>
       </c>
     </row>
     <row r="85">
@@ -2550,19 +2550,19 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.008816815158721828</v>
+        <v>0.999945265017957</v>
       </c>
       <c r="F85" t="n">
-        <v>2.112859645551748e-19</v>
+        <v>5.473498204297656e-05</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9911831848412781</v>
+        <v>1.684015033355128e-34</v>
       </c>
     </row>
     <row r="86">
@@ -2575,19 +2575,19 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.937150495322335e-08</v>
+        <v>0.9963689107218756</v>
       </c>
       <c r="F86" t="n">
-        <v>5.225455912077447e-09</v>
+        <v>0.003630522840004884</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9999999554030392</v>
+        <v>5.664381195102757e-07</v>
       </c>
     </row>
     <row r="87">
@@ -2600,19 +2600,19 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1.504606661244661e-08</v>
+        <v>0.9999775486987587</v>
       </c>
       <c r="F87" t="n">
-        <v>9.518957474908841e-11</v>
+        <v>2.245130124139129e-05</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9999999848587438</v>
+        <v>5.71619455600599e-18</v>
       </c>
     </row>
     <row r="88">
@@ -2625,19 +2625,19 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>2.43576425308378e-07</v>
+        <v>0.9889930612421522</v>
       </c>
       <c r="F88" t="n">
-        <v>4.032627471506166e-15</v>
+        <v>0.01100693875784772</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9999997564235705</v>
+        <v>5.891602868157833e-38</v>
       </c>
     </row>
     <row r="89">
@@ -2650,19 +2650,19 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>3.892226183128858e-07</v>
+        <v>0.9999320233050427</v>
       </c>
       <c r="F89" t="n">
-        <v>4.3181631310833e-15</v>
+        <v>6.79766949572144e-05</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9999996107773773</v>
+        <v>1.786640236678842e-20</v>
       </c>
     </row>
     <row r="90">
@@ -2675,19 +2675,19 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>4.208423940005464e-05</v>
+        <v>0.9999057318964706</v>
       </c>
       <c r="F90" t="n">
-        <v>1.235115760372905e-20</v>
+        <v>9.426805359779769e-05</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9999579157605999</v>
+        <v>4.99314744653177e-11</v>
       </c>
     </row>
     <row r="91">
@@ -2700,19 +2700,19 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>0.006908100178166612</v>
+        <v>0.9997824195959727</v>
       </c>
       <c r="F91" t="n">
-        <v>1.348444969893505e-22</v>
+        <v>0.0002175804040099458</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9930918998218333</v>
+        <v>1.723061962502887e-14</v>
       </c>
     </row>
     <row r="92">
@@ -2731,13 +2731,13 @@
         <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>8.225942999573415e-05</v>
+        <v>9.922175724617697e-12</v>
       </c>
       <c r="F92" t="n">
-        <v>8.956827761626626e-17</v>
+        <v>1.720321286510475e-15</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9999177405700043</v>
+        <v>0.9999999999900762</v>
       </c>
     </row>
     <row r="93">
@@ -2747,22 +2747,22 @@
         </is>
       </c>
       <c r="B93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0006132722338878922</v>
+        <v>0.9999817585885391</v>
       </c>
       <c r="F93" t="n">
-        <v>2.10242000719677e-22</v>
+        <v>1.824141146086042e-05</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9993867277661121</v>
+        <v>8.414690157788287e-20</v>
       </c>
     </row>
     <row r="94">
@@ -2781,13 +2781,13 @@
         <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>3.421276814224403e-06</v>
+        <v>7.158030310885373e-09</v>
       </c>
       <c r="F94" t="n">
-        <v>1.162136828010865e-13</v>
+        <v>2.096809049643013e-13</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9999965787230697</v>
+        <v>0.99999999284176</v>
       </c>
     </row>
     <row r="95">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="B95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
         <v>3</v>
@@ -2806,13 +2806,13 @@
         <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>4.452045330423855e-09</v>
+        <v>0.008340321990449071</v>
       </c>
       <c r="F95" t="n">
-        <v>3.624817801607503e-07</v>
+        <v>8.810204922876148e-07</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9999996330661746</v>
+        <v>0.9916587969890586</v>
       </c>
     </row>
     <row r="96">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="B96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2831,13 +2831,13 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9811234885426894</v>
+        <v>0.9989851142932532</v>
       </c>
       <c r="F96" t="n">
-        <v>1.898841446727086e-36</v>
+        <v>0.001014885706746842</v>
       </c>
       <c r="G96" t="n">
-        <v>0.01887651145731052</v>
+        <v>3.57593542919148e-28</v>
       </c>
     </row>
     <row r="97">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="B97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
         <v>3</v>
@@ -2856,13 +2856,13 @@
         <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3652250162064756</v>
+        <v>0.0003714143748977118</v>
       </c>
       <c r="F97" t="n">
-        <v>1.171446580014517e-26</v>
+        <v>5.76928097841936e-09</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6347749837935245</v>
+        <v>0.9996285798558214</v>
       </c>
     </row>
     <row r="98">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="B98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
         <v>3</v>
@@ -2881,13 +2881,13 @@
         <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0002779462404193438</v>
+        <v>4.438234330609455e-10</v>
       </c>
       <c r="F98" t="n">
-        <v>1.750992354023995e-17</v>
+        <v>2.678640621388119e-14</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9997220537595806</v>
+        <v>0.9999999995561497</v>
       </c>
     </row>
     <row r="99">
@@ -2906,13 +2906,13 @@
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>6.986347374622582e-07</v>
+        <v>2.863426211223333e-17</v>
       </c>
       <c r="F99" t="n">
-        <v>5.443774449246546e-11</v>
+        <v>1.455850193617012e-21</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9999993013108247</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,22 +2922,22 @@
         </is>
       </c>
       <c r="B100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>8.408178932678543e-07</v>
+        <v>0.9999504570118481</v>
       </c>
       <c r="F100" t="n">
-        <v>2.045946738789998e-14</v>
+        <v>4.954298815189554e-05</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9999991591820863</v>
+        <v>2.398769228291588e-21</v>
       </c>
     </row>
     <row r="101">
@@ -2956,13 +2956,13 @@
         <v>3</v>
       </c>
       <c r="E101" t="n">
-        <v>3.947032061178055e-09</v>
+        <v>1.678561179612068e-11</v>
       </c>
       <c r="F101" t="n">
-        <v>0.003447184961849877</v>
+        <v>1.803643974750925e-18</v>
       </c>
       <c r="G101" t="n">
-        <v>0.9965528110911182</v>
+        <v>0.9999999999832143</v>
       </c>
     </row>
     <row r="102">
@@ -2981,13 +2981,13 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9989912442312248</v>
+        <v>0.99994670333769</v>
       </c>
       <c r="F102" t="n">
-        <v>5.370997515783539e-34</v>
+        <v>5.329666230993446e-05</v>
       </c>
       <c r="G102" t="n">
-        <v>0.00100875576877532</v>
+        <v>9.850804292476601e-20</v>
       </c>
     </row>
     <row r="103">
@@ -3000,19 +3000,19 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>2.969168772378235e-27</v>
+        <v>0.9998819610713157</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9999999999984774</v>
+        <v>0.0001180389262787494</v>
       </c>
       <c r="G103" t="n">
-        <v>1.522476298896751e-12</v>
+        <v>2.405642277144721e-12</v>
       </c>
     </row>
     <row r="104">
@@ -3025,19 +3025,19 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>2.171599363668507e-19</v>
+        <v>0.9987424151626896</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9999993645949151</v>
+        <v>0.001257584837310572</v>
       </c>
       <c r="G104" t="n">
-        <v>6.354050848383377e-07</v>
+        <v>7.760326291667794e-26</v>
       </c>
     </row>
     <row r="105">
@@ -3050,19 +3050,19 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>8.452909580111206e-16</v>
+        <v>0.8482686270221487</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9999581598692833</v>
+        <v>0.1517313729778513</v>
       </c>
       <c r="G105" t="n">
-        <v>4.184013071597197e-05</v>
+        <v>7.52560199499016e-24</v>
       </c>
     </row>
     <row r="106">
@@ -3075,19 +3075,19 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>3.357671205001748e-05</v>
+        <v>0.9854785063521261</v>
       </c>
       <c r="F106" t="n">
-        <v>6.010226630720555e-17</v>
+        <v>0.0145214936478739</v>
       </c>
       <c r="G106" t="n">
-        <v>0.9999664232879499</v>
+        <v>4.857068663952198e-48</v>
       </c>
     </row>
     <row r="107">
@@ -3100,19 +3100,19 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>9.165848869863005e-09</v>
+        <v>0.999872098475392</v>
       </c>
       <c r="F107" t="n">
-        <v>5.856024199799487e-07</v>
+        <v>0.000127901524607978</v>
       </c>
       <c r="G107" t="n">
-        <v>0.9999994052317311</v>
+        <v>2.126624483654823e-20</v>
       </c>
     </row>
     <row r="108">
@@ -3131,13 +3131,13 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9534278568402272</v>
+        <v>0.9994453357909996</v>
       </c>
       <c r="F108" t="n">
-        <v>2.772670887587876e-34</v>
+        <v>0.000554664209000366</v>
       </c>
       <c r="G108" t="n">
-        <v>0.04657214315977284</v>
+        <v>4.216516236110956e-28</v>
       </c>
     </row>
     <row r="109">
@@ -3156,13 +3156,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.998480221182793</v>
+        <v>0.9977202859796401</v>
       </c>
       <c r="F109" t="n">
-        <v>4.320547022829381e-36</v>
+        <v>0.002279714020359775</v>
       </c>
       <c r="G109" t="n">
-        <v>0.001519778817207079</v>
+        <v>5.099772218030908e-17</v>
       </c>
     </row>
     <row r="110">
@@ -3181,13 +3181,13 @@
         <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>4.278190880381659e-07</v>
+        <v>7.870656135538957e-33</v>
       </c>
       <c r="F110" t="n">
-        <v>3.923720026817798e-07</v>
+        <v>1.578478699517768e-35</v>
       </c>
       <c r="G110" t="n">
-        <v>0.9999991798089093</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3200,19 +3200,19 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.01263193767943844</v>
+        <v>0.9947406791137487</v>
       </c>
       <c r="F111" t="n">
-        <v>1.26557879698727e-24</v>
+        <v>0.005259320886251244</v>
       </c>
       <c r="G111" t="n">
-        <v>0.9873680623205616</v>
+        <v>7.587332497573636e-32</v>
       </c>
     </row>
     <row r="112">
@@ -3225,19 +3225,19 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>7.326642612633931e-06</v>
+        <v>0.9863451403303135</v>
       </c>
       <c r="F112" t="n">
-        <v>4.18752062000309e-16</v>
+        <v>0.01365485966968641</v>
       </c>
       <c r="G112" t="n">
-        <v>0.9999926733573868</v>
+        <v>5.356982499517082e-30</v>
       </c>
     </row>
     <row r="113">
@@ -3256,13 +3256,13 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9999312169214921</v>
+        <v>0.9999386794079174</v>
       </c>
       <c r="F113" t="n">
-        <v>1.025134081291806e-37</v>
+        <v>6.132059208263986e-05</v>
       </c>
       <c r="G113" t="n">
-        <v>6.878307850779439e-05</v>
+        <v>1.470221119072497e-22</v>
       </c>
     </row>
     <row r="114">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="B114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -3281,13 +3281,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.999999599309811</v>
+        <v>0.8302587659044659</v>
       </c>
       <c r="F114" t="n">
-        <v>2.433602805658487e-51</v>
+        <v>0.1697412340955341</v>
       </c>
       <c r="G114" t="n">
-        <v>4.006901890331989e-07</v>
+        <v>1.2118754674781e-32</v>
       </c>
     </row>
     <row r="115">
@@ -3306,13 +3306,13 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9999951401063114</v>
+        <v>0.9998946443583365</v>
       </c>
       <c r="F115" t="n">
-        <v>7.513971801629144e-47</v>
+        <v>0.0001053552284476002</v>
       </c>
       <c r="G115" t="n">
-        <v>4.859893688471918e-06</v>
+        <v>4.132159137837432e-10</v>
       </c>
     </row>
     <row r="116">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="B116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -3331,13 +3331,13 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9434858434122564</v>
+        <v>0.9993870255902225</v>
       </c>
       <c r="F116" t="n">
-        <v>3.4861163351444e-32</v>
+        <v>0.0006129744097775943</v>
       </c>
       <c r="G116" t="n">
-        <v>0.05651415658774357</v>
+        <v>2.627560919132533e-28</v>
       </c>
     </row>
     <row r="117">
@@ -3356,13 +3356,13 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9999999866719735</v>
+        <v>0.8981323618924694</v>
       </c>
       <c r="F117" t="n">
-        <v>4.468683222689963e-59</v>
+        <v>0.1018676381075307</v>
       </c>
       <c r="G117" t="n">
-        <v>1.332802660620859e-08</v>
+        <v>4.991825316075436e-27</v>
       </c>
     </row>
     <row r="118">
@@ -3375,19 +3375,19 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>0.999999999853433</v>
+        <v>0.0904790638313272</v>
       </c>
       <c r="F118" t="n">
-        <v>5.579149018947006e-70</v>
+        <v>0.9095209361686727</v>
       </c>
       <c r="G118" t="n">
-        <v>1.465670515033747e-10</v>
+        <v>2.665458416715137e-42</v>
       </c>
     </row>
     <row r="119">
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="B119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>0.07829304867839018</v>
+        <v>0.9962667022678233</v>
       </c>
       <c r="F119" t="n">
-        <v>1.097069786508977e-28</v>
+        <v>0.003733297732176656</v>
       </c>
       <c r="G119" t="n">
-        <v>0.9217069513216098</v>
+        <v>2.589045718651061e-23</v>
       </c>
     </row>
     <row r="120">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="B120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -3431,13 +3431,13 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.9994961593998823</v>
+        <v>0.9984752108333114</v>
       </c>
       <c r="F120" t="n">
-        <v>5.507451050981829e-41</v>
+        <v>0.001524789166688551</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0005038406001176753</v>
+        <v>1.154711976995953e-22</v>
       </c>
     </row>
     <row r="121">
@@ -3456,13 +3456,13 @@
         <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>3.419107936208321e-05</v>
+        <v>4.456802047971459e-22</v>
       </c>
       <c r="F121" t="n">
-        <v>2.212399207610356e-15</v>
+        <v>7.704778265151464e-25</v>
       </c>
       <c r="G121" t="n">
-        <v>0.9999658089206357</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3475,19 +3475,19 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0.02269945981505498</v>
+        <v>0.9926625636157923</v>
       </c>
       <c r="F122" t="n">
-        <v>1.793865781821426e-25</v>
+        <v>0.007337436384207632</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9773005401849452</v>
+        <v>2.304299978866069e-30</v>
       </c>
     </row>
     <row r="123">
@@ -3497,22 +3497,22 @@
         </is>
       </c>
       <c r="B123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0008733383837855163</v>
+        <v>0.9994706978164697</v>
       </c>
       <c r="F123" t="n">
-        <v>2.789955739355438e-22</v>
+        <v>0.0005293021668323604</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9991266616162144</v>
+        <v>1.669806604574665e-11</v>
       </c>
     </row>
     <row r="124">
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="B124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -3531,13 +3531,13 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9098973748970235</v>
+        <v>0.9989237210793824</v>
       </c>
       <c r="F124" t="n">
-        <v>6.443919329298773e-33</v>
+        <v>0.001076278920617657</v>
       </c>
       <c r="G124" t="n">
-        <v>0.09010262510297665</v>
+        <v>5.282938634209598e-29</v>
       </c>
     </row>
     <row r="125">
@@ -3547,22 +3547,22 @@
         </is>
       </c>
       <c r="B125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>0.05670444379523303</v>
+        <v>0.9968396904306176</v>
       </c>
       <c r="F125" t="n">
-        <v>2.884218623747994e-25</v>
+        <v>0.003160309569382291</v>
       </c>
       <c r="G125" t="n">
-        <v>0.943295556204767</v>
+        <v>4.457879328874208e-28</v>
       </c>
     </row>
     <row r="126">
@@ -3572,22 +3572,22 @@
         </is>
       </c>
       <c r="B126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>4.922783384216739e-05</v>
+        <v>0.9946201489338129</v>
       </c>
       <c r="F126" t="n">
-        <v>2.497697121293739e-17</v>
+        <v>0.005379851066187162</v>
       </c>
       <c r="G126" t="n">
-        <v>0.9999507721661578</v>
+        <v>3.109979883142864e-18</v>
       </c>
     </row>
     <row r="127">
@@ -3606,13 +3606,13 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>0.9900153712257058</v>
+        <v>0.9995504256778375</v>
       </c>
       <c r="F127" t="n">
-        <v>8.697754234004185e-34</v>
+        <v>0.0004495694851761768</v>
       </c>
       <c r="G127" t="n">
-        <v>0.009984628774294322</v>
+        <v>4.836986459412392e-09</v>
       </c>
     </row>
     <row r="128">
@@ -3622,22 +3622,22 @@
         </is>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>0.002690981243843975</v>
+        <v>0.99975266101438</v>
       </c>
       <c r="F128" t="n">
-        <v>5.35945526971653e-22</v>
+        <v>0.0002473373246424556</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9973090187561561</v>
+        <v>1.660977567300842e-09</v>
       </c>
     </row>
     <row r="129">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="B129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
         <v>3</v>
@@ -3656,13 +3656,13 @@
         <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0001916344552161711</v>
+        <v>1.899576214836721e-14</v>
       </c>
       <c r="F129" t="n">
-        <v>9.342885039606009e-26</v>
+        <v>4.628389982582935e-20</v>
       </c>
       <c r="G129" t="n">
-        <v>0.9998083655447838</v>
+        <v>0.9999999999999809</v>
       </c>
     </row>
     <row r="130">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="B130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -3681,13 +3681,13 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8703391515563766</v>
+        <v>0.998093312200735</v>
       </c>
       <c r="F130" t="n">
-        <v>6.080854167637393e-31</v>
+        <v>0.001906029443386023</v>
       </c>
       <c r="G130" t="n">
-        <v>0.1296608484436232</v>
+        <v>6.583558788791796e-07</v>
       </c>
     </row>
     <row r="131">
@@ -3706,13 +3706,13 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5536712317137564</v>
+        <v>0.9971856557705454</v>
       </c>
       <c r="F131" t="n">
-        <v>9.993692981832124e-33</v>
+        <v>0.002814344229454629</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4463287682862435</v>
+        <v>9.409291967695316e-35</v>
       </c>
     </row>
     <row r="132">
@@ -3731,13 +3731,13 @@
         <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>0.002075128929846473</v>
+        <v>3.884446486122541e-13</v>
       </c>
       <c r="F132" t="n">
-        <v>1.925805346176193e-19</v>
+        <v>5.409269156614729e-18</v>
       </c>
       <c r="G132" t="n">
-        <v>0.9979248710701536</v>
+        <v>0.9999999999996116</v>
       </c>
     </row>
     <row r="133">
@@ -3747,22 +3747,22 @@
         </is>
       </c>
       <c r="B133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>9.657027928612704e-07</v>
+        <v>0.9982473050442552</v>
       </c>
       <c r="F133" t="n">
-        <v>7.661194044044215e-14</v>
+        <v>0.001752694955641257</v>
       </c>
       <c r="G133" t="n">
-        <v>0.9999990342971306</v>
+        <v>1.034615193599074e-13</v>
       </c>
     </row>
     <row r="134">
@@ -3781,13 +3781,13 @@
         <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>3.133727728663439e-07</v>
+        <v>2.892416773177278e-53</v>
       </c>
       <c r="F134" t="n">
-        <v>3.556465042415595e-12</v>
+        <v>4.996417949562336e-60</v>
       </c>
       <c r="G134" t="n">
-        <v>0.9999996866236708</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3800,19 +3800,19 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>1.665002364563145e-08</v>
+        <v>0.9997194443635227</v>
       </c>
       <c r="F135" t="n">
-        <v>1.690752536018941e-10</v>
+        <v>0.0002805556364773963</v>
       </c>
       <c r="G135" t="n">
-        <v>0.9999999831809011</v>
+        <v>1.448860787081434e-25</v>
       </c>
     </row>
     <row r="136">
@@ -3831,13 +3831,13 @@
         <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>5.792081635845467e-08</v>
+        <v>1.945159048303669e-35</v>
       </c>
       <c r="F136" t="n">
-        <v>9.091925841177132e-08</v>
+        <v>2.870909376751626e-40</v>
       </c>
       <c r="G136" t="n">
-        <v>0.9999998511599253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -3850,19 +3850,19 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="n">
-        <v>7.209544904401512e-23</v>
+        <v>2.674780488989943e-66</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9999999735839713</v>
+        <v>1.367217038306943e-71</v>
       </c>
       <c r="G137" t="n">
-        <v>2.641602875615632e-08</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3875,19 +3875,19 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" t="n">
-        <v>0.9476240752768248</v>
+        <v>8.156969462301038e-46</v>
       </c>
       <c r="F138" t="n">
-        <v>1.625917603939927e-29</v>
+        <v>3.8777132516483e-53</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0523759247231752</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3906,13 +3906,13 @@
         <v>3</v>
       </c>
       <c r="E139" t="n">
-        <v>2.160838781000729e-10</v>
+        <v>3.686232532778001e-09</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0003389388781093649</v>
+        <v>6.40064993112299e-15</v>
       </c>
       <c r="G139" t="n">
-        <v>0.9996610609058069</v>
+        <v>0.9999999963137611</v>
       </c>
     </row>
     <row r="140">
@@ -3931,13 +3931,13 @@
         <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>0.00264799344413942</v>
+        <v>1.603148442798741e-27</v>
       </c>
       <c r="F140" t="n">
-        <v>1.851261994769127e-22</v>
+        <v>3.920188830791756e-33</v>
       </c>
       <c r="G140" t="n">
-        <v>0.9973520065558605</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3950,19 +3950,19 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>2.353217640338208e-14</v>
+        <v>1.792303109280076e-05</v>
       </c>
       <c r="F141" t="n">
-        <v>0.8412017471052515</v>
+        <v>1.418460525361744e-07</v>
       </c>
       <c r="G141" t="n">
-        <v>0.158798252894725</v>
+        <v>0.9999819351228546</v>
       </c>
     </row>
     <row r="142">
@@ -3975,19 +3975,19 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E142" t="n">
-        <v>1.325622090378949e-18</v>
+        <v>6.587654924963972e-63</v>
       </c>
       <c r="F142" t="n">
-        <v>0.9999704162799889</v>
+        <v>1.794309607721464e-71</v>
       </c>
       <c r="G142" t="n">
-        <v>2.958372001111805e-05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -4000,19 +4000,19 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>3.109297949319793e-12</v>
+        <v>8.176920197762366e-57</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9743135682898272</v>
+        <v>3.324640954546813e-61</v>
       </c>
       <c r="G143" t="n">
-        <v>0.02568643170706353</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -4025,19 +4025,19 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0.02589980405187923</v>
+        <v>0.9284079747686683</v>
       </c>
       <c r="F144" t="n">
-        <v>1.046402424892478e-22</v>
+        <v>0.07159173726627974</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9741001959481208</v>
+        <v>2.879650520893045e-07</v>
       </c>
     </row>
     <row r="145">
@@ -4050,19 +4050,19 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>7.017040473794504e-14</v>
+        <v>1.514671214912772e-08</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7256973074075096</v>
+        <v>7.888669458918179e-10</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2743026925924202</v>
+        <v>0.9999999840644209</v>
       </c>
     </row>
     <row r="146">
@@ -4081,13 +4081,13 @@
         <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>0.01766368211083314</v>
+        <v>3.103533102536889e-12</v>
       </c>
       <c r="F146" t="n">
-        <v>6.05845811699154e-22</v>
+        <v>7.804244206114689e-17</v>
       </c>
       <c r="G146" t="n">
-        <v>0.9823363178891668</v>
+        <v>0.9999999999968965</v>
       </c>
     </row>
     <row r="147">
@@ -4106,13 +4106,13 @@
         <v>3</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1020699810307639</v>
+        <v>7.827422744916965e-29</v>
       </c>
       <c r="F147" t="n">
-        <v>9.79812599775795e-28</v>
+        <v>1.645925330552953e-34</v>
       </c>
       <c r="G147" t="n">
-        <v>0.8979300189692362</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4131,13 +4131,13 @@
         <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0001322374340553959</v>
+        <v>5.062908702487437e-40</v>
       </c>
       <c r="F148" t="n">
-        <v>4.707431257708982e-23</v>
+        <v>3.227407029978285e-44</v>
       </c>
       <c r="G148" t="n">
-        <v>0.9998677625659446</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4150,19 +4150,19 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
-        <v>0.9385329584819204</v>
+        <v>6.992905335495158e-36</v>
       </c>
       <c r="F149" t="n">
-        <v>1.820755595022802e-34</v>
+        <v>1.48176933966868e-41</v>
       </c>
       <c r="G149" t="n">
-        <v>0.06146704151807955</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4175,19 +4175,19 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
-        <v>0.9999821680822918</v>
+        <v>5.752029423075814e-11</v>
       </c>
       <c r="F150" t="n">
-        <v>6.655762820535641e-51</v>
+        <v>1.051330019661266e-15</v>
       </c>
       <c r="G150" t="n">
-        <v>1.783191770817292e-05</v>
+        <v>0.9999999999424787</v>
       </c>
     </row>
     <row r="151">
@@ -4200,19 +4200,19 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0004964626181906184</v>
+        <v>0.9979026860181356</v>
       </c>
       <c r="F151" t="n">
-        <v>4.328374861081873e-25</v>
+        <v>0.002097313975193188</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9995035373818093</v>
+        <v>6.671052238618433e-12</v>
       </c>
     </row>
     <row r="152">
@@ -4231,13 +4231,13 @@
         <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0002068178427265421</v>
+        <v>1.397932342949231e-23</v>
       </c>
       <c r="F152" t="n">
-        <v>3.25638883288533e-18</v>
+        <v>9.606288143067756e-29</v>
       </c>
       <c r="G152" t="n">
-        <v>0.9997931821572734</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4250,19 +4250,19 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153" t="n">
-        <v>0.9990901599142695</v>
+        <v>1.241649939710985e-21</v>
       </c>
       <c r="F153" t="n">
-        <v>9.772579768879452e-42</v>
+        <v>3.245574328748688e-27</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0009098400857304116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4275,19 +4275,19 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E154" t="n">
-        <v>0.7547186094081157</v>
+        <v>3.46519847520965e-11</v>
       </c>
       <c r="F154" t="n">
-        <v>1.217082753198539e-26</v>
+        <v>1.861174104740867e-15</v>
       </c>
       <c r="G154" t="n">
-        <v>0.2452813905918843</v>
+        <v>0.9999999999653462</v>
       </c>
     </row>
     <row r="155">
@@ -4306,13 +4306,13 @@
         <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>0.1838311522543357</v>
+        <v>1.313856895574915e-12</v>
       </c>
       <c r="F155" t="n">
-        <v>6.658659982715771e-25</v>
+        <v>4.361707862449598e-19</v>
       </c>
       <c r="G155" t="n">
-        <v>0.8161688477456642</v>
+        <v>0.9999999999986862</v>
       </c>
     </row>
     <row r="156">
@@ -4325,19 +4325,19 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>0.02506234101054056</v>
+        <v>0.1091261530161097</v>
       </c>
       <c r="F156" t="n">
-        <v>2.078357192906699e-27</v>
+        <v>0.8537364864318115</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9749376589894594</v>
+        <v>0.03713736055207868</v>
       </c>
     </row>
     <row r="157">
@@ -4350,19 +4350,19 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" t="n">
-        <v>0.9938919868529841</v>
+        <v>7.620436187909726e-15</v>
       </c>
       <c r="F157" t="n">
-        <v>1.310247251356744e-33</v>
+        <v>5.840556397654362e-22</v>
       </c>
       <c r="G157" t="n">
-        <v>0.00610801314701604</v>
+        <v>0.9999999999999925</v>
       </c>
     </row>
     <row r="158">
@@ -4381,13 +4381,13 @@
         <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>1.325332742514092e-05</v>
+        <v>9.363939300424779e-24</v>
       </c>
       <c r="F158" t="n">
-        <v>3.058869075280296e-15</v>
+        <v>1.286779490700112e-30</v>
       </c>
       <c r="G158" t="n">
-        <v>0.9999867466725718</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -4406,13 +4406,13 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0.987233255533198</v>
+        <v>0.9994273810221117</v>
       </c>
       <c r="F159" t="n">
-        <v>9.590385907899026e-32</v>
+        <v>0.0005726189066266033</v>
       </c>
       <c r="G159" t="n">
-        <v>0.01276674446680206</v>
+        <v>7.126174937233559e-11</v>
       </c>
     </row>
     <row r="160">
@@ -4431,13 +4431,13 @@
         <v>3</v>
       </c>
       <c r="E160" t="n">
-        <v>5.418694743454724e-05</v>
+        <v>8.753582209305526e-18</v>
       </c>
       <c r="F160" t="n">
-        <v>7.615423360838159e-23</v>
+        <v>7.68764749953448e-22</v>
       </c>
       <c r="G160" t="n">
-        <v>0.9999458130525655</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -4450,19 +4450,19 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E161" t="n">
-        <v>0.9947211000671732</v>
+        <v>7.524559322128178e-06</v>
       </c>
       <c r="F161" t="n">
-        <v>1.338834132059464e-34</v>
+        <v>8.500023256826748e-09</v>
       </c>
       <c r="G161" t="n">
-        <v>0.00527889993282676</v>
+        <v>0.9999924669406547</v>
       </c>
     </row>
     <row r="162">
@@ -4475,19 +4475,19 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.01657480900672981</v>
+        <v>0.9999851000969864</v>
       </c>
       <c r="F162" t="n">
-        <v>8.015582548576291e-26</v>
+        <v>1.485948349826435e-05</v>
       </c>
       <c r="G162" t="n">
-        <v>0.9834251909932702</v>
+        <v>4.041951551779744e-08</v>
       </c>
     </row>
     <row r="163">
@@ -4506,13 +4506,13 @@
         <v>3</v>
       </c>
       <c r="E163" t="n">
-        <v>5.867535793209345e-09</v>
+        <v>8.334816257094361e-23</v>
       </c>
       <c r="F163" t="n">
-        <v>1.710577555841343e-06</v>
+        <v>1.931386815251301e-25</v>
       </c>
       <c r="G163" t="n">
-        <v>0.9999982835549083</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -4525,19 +4525,19 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>0.9759746431716307</v>
+        <v>5.342967907377972e-05</v>
       </c>
       <c r="F164" t="n">
-        <v>3.533652164361491e-33</v>
+        <v>2.892395573113681e-09</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02402535682836921</v>
+        <v>0.9999465674285306</v>
       </c>
     </row>
     <row r="165">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -4556,13 +4556,13 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>0.9999999380549177</v>
+        <v>0.8704088668453721</v>
       </c>
       <c r="F165" t="n">
-        <v>7.72240952885317e-54</v>
+        <v>0.0001944975811842939</v>
       </c>
       <c r="G165" t="n">
-        <v>6.194508239638056e-08</v>
+        <v>0.1293966355734435</v>
       </c>
     </row>
     <row r="166">
@@ -4575,19 +4575,19 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E166" t="n">
-        <v>0.9381559233148186</v>
+        <v>0.02815372051686455</v>
       </c>
       <c r="F166" t="n">
-        <v>1.494039333245218e-33</v>
+        <v>1.584515690680049e-06</v>
       </c>
       <c r="G166" t="n">
-        <v>0.06184407668518152</v>
+        <v>0.9718446949674447</v>
       </c>
     </row>
     <row r="167">
@@ -4600,19 +4600,19 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E167" t="n">
-        <v>0.9999997151308088</v>
+        <v>6.277391314335143e-21</v>
       </c>
       <c r="F167" t="n">
-        <v>4.223393352364206e-53</v>
+        <v>7.835706329093476e-24</v>
       </c>
       <c r="G167" t="n">
-        <v>2.848691912861464e-07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -4625,19 +4625,19 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" t="n">
-        <v>0.9999987951468647</v>
+        <v>1.177449725891353e-14</v>
       </c>
       <c r="F168" t="n">
-        <v>2.592459250560562e-52</v>
+        <v>2.419425239247891e-18</v>
       </c>
       <c r="G168" t="n">
-        <v>1.204853135264769e-06</v>
+        <v>0.9999999999999882</v>
       </c>
     </row>
     <row r="169">
@@ -4650,19 +4650,19 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>0.9999988518128516</v>
+        <v>0.172215447721334</v>
       </c>
       <c r="F169" t="n">
-        <v>4.038703219663834e-54</v>
+        <v>0.8277845522786659</v>
       </c>
       <c r="G169" t="n">
-        <v>1.148187148370419e-06</v>
+        <v>1.29931904475297e-35</v>
       </c>
     </row>
     <row r="170">
@@ -4675,19 +4675,19 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" t="n">
-        <v>0.9999993697650464</v>
+        <v>1.230366211360548e-16</v>
       </c>
       <c r="F170" t="n">
-        <v>1.662053165561007e-54</v>
+        <v>3.245304591470334e-20</v>
       </c>
       <c r="G170" t="n">
-        <v>6.302349535798508e-07</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="171">
@@ -4700,19 +4700,19 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0956925135353804</v>
+        <v>0.99908297630243</v>
       </c>
       <c r="F171" t="n">
-        <v>5.272871811598946e-34</v>
+        <v>0.0009170233340248365</v>
       </c>
       <c r="G171" t="n">
-        <v>0.9043074864646196</v>
+        <v>3.635450297770159e-10</v>
       </c>
     </row>
     <row r="172">
@@ -4731,13 +4731,13 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.9998418696545247</v>
+        <v>0.861290805132672</v>
       </c>
       <c r="F172" t="n">
-        <v>1.870205822447664e-42</v>
+        <v>8.330692879644624e-05</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0001581303454753133</v>
+        <v>0.1386258879385315</v>
       </c>
     </row>
     <row r="173">
@@ -4747,22 +4747,22 @@
         </is>
       </c>
       <c r="B173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E173" t="n">
-        <v>0.9986240600373683</v>
+        <v>0.0003761675276060683</v>
       </c>
       <c r="F173" t="n">
-        <v>6.498313980531245e-42</v>
+        <v>1.937770785980285e-06</v>
       </c>
       <c r="G173" t="n">
-        <v>0.001375939962631704</v>
+        <v>0.9996218947016079</v>
       </c>
     </row>
     <row r="174">
@@ -4781,13 +4781,13 @@
         <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0838066262237719</v>
+        <v>0.002409872894059108</v>
       </c>
       <c r="F174" t="n">
-        <v>2.537679122865766e-29</v>
+        <v>6.54552369131632e-05</v>
       </c>
       <c r="G174" t="n">
-        <v>0.9161933737762282</v>
+        <v>0.9975246718690278</v>
       </c>
     </row>
     <row r="175">
@@ -4806,13 +4806,13 @@
         <v>3</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0520159915070911</v>
+        <v>3.492154735004326e-23</v>
       </c>
       <c r="F175" t="n">
-        <v>9.420067481767867e-29</v>
+        <v>2.056305524972748e-27</v>
       </c>
       <c r="G175" t="n">
-        <v>0.9479840084929089</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4831,13 +4831,13 @@
         <v>3</v>
       </c>
       <c r="E176" t="n">
-        <v>0.0108699594585798</v>
+        <v>6.128073366687651e-13</v>
       </c>
       <c r="F176" t="n">
-        <v>1.539044190471868e-27</v>
+        <v>1.545037638558703e-16</v>
       </c>
       <c r="G176" t="n">
-        <v>0.9891300405414203</v>
+        <v>0.9999999999993869</v>
       </c>
     </row>
     <row r="177">
@@ -4856,13 +4856,13 @@
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>0.9131347381894971</v>
+        <v>0.9936063791507063</v>
       </c>
       <c r="F177" t="n">
-        <v>1.157616784474396e-38</v>
+        <v>0.006393620817793746</v>
       </c>
       <c r="G177" t="n">
-        <v>0.08686526181050287</v>
+        <v>3.149984621632717e-11</v>
       </c>
     </row>
     <row r="178">
@@ -4881,13 +4881,13 @@
         <v>3</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0060390829882241</v>
+        <v>0.0001036251859386742</v>
       </c>
       <c r="F178" t="n">
-        <v>2.027643412441402e-18</v>
+        <v>4.071264304106994e-12</v>
       </c>
       <c r="G178" t="n">
-        <v>0.9939609170117759</v>
+        <v>0.9998963748099902</v>
       </c>
     </row>
     <row r="179">
@@ -4906,13 +4906,13 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>0.9771245795377483</v>
+        <v>0.9280894592419763</v>
       </c>
       <c r="F179" t="n">
-        <v>2.387869104306827e-32</v>
+        <v>2.985017040282939e-05</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0228754204622517</v>
+        <v>0.07188069058762095</v>
       </c>
     </row>
     <row r="180">
@@ -4931,13 +4931,13 @@
         <v>3</v>
       </c>
       <c r="E180" t="n">
-        <v>0.02563044441899236</v>
+        <v>1.596486065828927e-42</v>
       </c>
       <c r="F180" t="n">
-        <v>3.402606422805539e-21</v>
+        <v>9.688750143493451e-51</v>
       </c>
       <c r="G180" t="n">
-        <v>0.9743695555810076</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -4950,19 +4950,19 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>1.644235502501923e-05</v>
+        <v>0.9996310380313496</v>
       </c>
       <c r="F181" t="n">
-        <v>7.853675500125839e-15</v>
+        <v>0.0003689619686502433</v>
       </c>
       <c r="G181" t="n">
-        <v>0.9999835576449672</v>
+        <v>2.210500928040214e-16</v>
       </c>
     </row>
     <row r="182">
@@ -4975,19 +4975,19 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E182" t="n">
-        <v>0.9999495709075994</v>
+        <v>0.003615855403871552</v>
       </c>
       <c r="F182" t="n">
-        <v>2.387547220093458e-44</v>
+        <v>1.828249048324477e-07</v>
       </c>
       <c r="G182" t="n">
-        <v>5.042909240064547e-05</v>
+        <v>0.9963839617712236</v>
       </c>
     </row>
     <row r="183">
@@ -5000,19 +5000,19 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" t="n">
-        <v>0.9998627951940025</v>
+        <v>1.214354562361737e-09</v>
       </c>
       <c r="F183" t="n">
-        <v>2.001094803758021e-43</v>
+        <v>1.717376865871008e-14</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0001372048059975265</v>
+        <v>0.9999999987856283</v>
       </c>
     </row>
     <row r="184">
@@ -5025,19 +5025,19 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>0.00138137503047828</v>
+        <v>0.07044377238697187</v>
       </c>
       <c r="F184" t="n">
-        <v>8.796290272980963e-28</v>
+        <v>0.9295562276130281</v>
       </c>
       <c r="G184" t="n">
-        <v>0.9986186249695217</v>
+        <v>2.174566288917771e-19</v>
       </c>
     </row>
     <row r="185">
@@ -5056,13 +5056,13 @@
         <v>3</v>
       </c>
       <c r="E185" t="n">
-        <v>0.005888310829821579</v>
+        <v>4.61676328594808e-11</v>
       </c>
       <c r="F185" t="n">
-        <v>3.185020140560221e-23</v>
+        <v>2.107603360356048e-16</v>
       </c>
       <c r="G185" t="n">
-        <v>0.9941116891701783</v>
+        <v>0.9999999999538323</v>
       </c>
     </row>
     <row r="186">
@@ -5075,19 +5075,19 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
-        <v>5.030591498182119e-16</v>
+        <v>3.137150263653287e-17</v>
       </c>
       <c r="F186" t="n">
-        <v>0.9972577640922242</v>
+        <v>2.811252094735606e-22</v>
       </c>
       <c r="G186" t="n">
-        <v>0.002742235907775363</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5106,13 +5106,13 @@
         <v>3</v>
       </c>
       <c r="E187" t="n">
-        <v>5.393356813403808e-06</v>
+        <v>3.517813961156545e-05</v>
       </c>
       <c r="F187" t="n">
-        <v>1.731896292829554e-14</v>
+        <v>1.014452830881122e-10</v>
       </c>
       <c r="G187" t="n">
-        <v>0.9999946066431693</v>
+        <v>0.9999648217589431</v>
       </c>
     </row>
     <row r="188">
@@ -5131,13 +5131,13 @@
         <v>3</v>
       </c>
       <c r="E188" t="n">
-        <v>4.829862766125752e-08</v>
+        <v>1.014673624042187e-16</v>
       </c>
       <c r="F188" t="n">
-        <v>2.509522019364148e-11</v>
+        <v>7.81425476329462e-21</v>
       </c>
       <c r="G188" t="n">
-        <v>0.9999999516762771</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -5156,13 +5156,13 @@
         <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>0.08201920611506472</v>
+        <v>4.155098803469096e-35</v>
       </c>
       <c r="F189" t="n">
-        <v>2.895081183784522e-28</v>
+        <v>2.52949084277402e-39</v>
       </c>
       <c r="G189" t="n">
-        <v>0.9179807938849354</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -5175,19 +5175,19 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E190" t="n">
-        <v>0.8002117833790351</v>
+        <v>3.427508792046227e-31</v>
       </c>
       <c r="F190" t="n">
-        <v>1.207578998052599e-25</v>
+        <v>1.851043181526799e-34</v>
       </c>
       <c r="G190" t="n">
-        <v>0.199788216620965</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -5200,19 +5200,19 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>0.4899987520103565</v>
+        <v>0.9960586730750471</v>
       </c>
       <c r="F191" t="n">
-        <v>8.822533219918034e-24</v>
+        <v>0.003941326924831311</v>
       </c>
       <c r="G191" t="n">
-        <v>0.5100012479896435</v>
+        <v>1.213632096838554e-13</v>
       </c>
     </row>
     <row r="192">
@@ -5222,22 +5222,22 @@
         </is>
       </c>
       <c r="B192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>0.1044657488692495</v>
+        <v>0.9964455835682403</v>
       </c>
       <c r="F192" t="n">
-        <v>1.625748658161323e-26</v>
+        <v>0.003554416431759609</v>
       </c>
       <c r="G192" t="n">
-        <v>0.8955342511307505</v>
+        <v>2.055349579375182e-32</v>
       </c>
     </row>
     <row r="193">
@@ -5250,19 +5250,19 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>5.88710181601631e-05</v>
+        <v>0.9792939731397984</v>
       </c>
       <c r="F193" t="n">
-        <v>1.338866174574467e-18</v>
+        <v>0.02070602686020175</v>
       </c>
       <c r="G193" t="n">
-        <v>0.9999411289818398</v>
+        <v>7.636074033959563e-37</v>
       </c>
     </row>
     <row r="194">
@@ -5281,13 +5281,13 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.9888546505098462</v>
+        <v>0.999407102821206</v>
       </c>
       <c r="F194" t="n">
-        <v>9.481216376202971e-34</v>
+        <v>0.0005928971787939031</v>
       </c>
       <c r="G194" t="n">
-        <v>0.01114534949015363</v>
+        <v>6.511980881050138e-29</v>
       </c>
     </row>
     <row r="195">
@@ -5306,13 +5306,13 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.9999997103588365</v>
+        <v>0.9141361465791881</v>
       </c>
       <c r="F195" t="n">
-        <v>2.64030613225526e-50</v>
+        <v>0.08586385342081193</v>
       </c>
       <c r="G195" t="n">
-        <v>2.896411635029605e-07</v>
+        <v>3.308392945809581e-43</v>
       </c>
     </row>
     <row r="196">
@@ -5331,13 +5331,13 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.99796149596221</v>
+        <v>0.9962693186222243</v>
       </c>
       <c r="F196" t="n">
-        <v>8.211913119637986e-37</v>
+        <v>7.445219828720182e-06</v>
       </c>
       <c r="G196" t="n">
-        <v>0.002038504037789992</v>
+        <v>0.003723236157946741</v>
       </c>
     </row>
     <row r="197">
@@ -5347,22 +5347,22 @@
         </is>
       </c>
       <c r="B197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" t="n">
-        <v>0.9999995903877069</v>
+        <v>2.124234677395084e-34</v>
       </c>
       <c r="F197" t="n">
-        <v>7.403018827718476e-45</v>
+        <v>1.106606378344374e-38</v>
       </c>
       <c r="G197" t="n">
-        <v>4.096122929923492e-07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5375,19 +5375,19 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>1.460482147929197e-08</v>
+        <v>0.829472558284012</v>
       </c>
       <c r="F198" t="n">
-        <v>4.176409154016236e-14</v>
+        <v>0.170527441715988</v>
       </c>
       <c r="G198" t="n">
-        <v>0.9999999853951367</v>
+        <v>8.234967928428704e-26</v>
       </c>
     </row>
     <row r="199">
@@ -5400,19 +5400,19 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>9.717045298878466e-21</v>
+        <v>0.8662191333346366</v>
       </c>
       <c r="F199" t="n">
-        <v>0.9999998805376403</v>
+        <v>0.1337808666653633</v>
       </c>
       <c r="G199" t="n">
-        <v>1.194623597571923e-07</v>
+        <v>1.113353498248052e-39</v>
       </c>
     </row>
     <row r="200">
@@ -5425,19 +5425,19 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.03240459204212467</v>
+        <v>0.9997865654786324</v>
       </c>
       <c r="F200" t="n">
-        <v>1.781411558852759e-26</v>
+        <v>0.000213434521367667</v>
       </c>
       <c r="G200" t="n">
-        <v>0.9675954079578752</v>
+        <v>1.578328539596711e-18</v>
       </c>
     </row>
     <row r="201">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="B201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -5456,13 +5456,13 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.8912828642297379</v>
+        <v>0.9386343260964012</v>
       </c>
       <c r="F201" t="n">
-        <v>2.422686984079438e-33</v>
+        <v>0.06136567390359882</v>
       </c>
       <c r="G201" t="n">
-        <v>0.1087171357702621</v>
+        <v>2.843174666881501e-31</v>
       </c>
     </row>
     <row r="202">
@@ -5475,19 +5475,19 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.001618139404267785</v>
+        <v>0.9821549923608862</v>
       </c>
       <c r="F202" t="n">
-        <v>2.334978250333416e-17</v>
+        <v>8.202373494953408e-05</v>
       </c>
       <c r="G202" t="n">
-        <v>0.9983818605957321</v>
+        <v>0.01776298390416427</v>
       </c>
     </row>
     <row r="203">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C203" t="n">
         <v>3</v>
@@ -5506,13 +5506,13 @@
         <v>3</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1517702304848304</v>
+        <v>1.178100880455004e-14</v>
       </c>
       <c r="F203" t="n">
-        <v>1.178660021392198e-19</v>
+        <v>9.306263433931688e-19</v>
       </c>
       <c r="G203" t="n">
-        <v>0.8482297695151696</v>
+        <v>0.9999999999999882</v>
       </c>
     </row>
     <row r="204">
@@ -5525,19 +5525,19 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0001367019009460997</v>
+        <v>0.9787621031044127</v>
       </c>
       <c r="F204" t="n">
-        <v>1.333878921881157e-15</v>
+        <v>0.02123789689542238</v>
       </c>
       <c r="G204" t="n">
-        <v>0.9998632980990525</v>
+        <v>1.648968693469638e-13</v>
       </c>
     </row>
     <row r="205">
@@ -5550,19 +5550,19 @@
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>6.971666372794395e-09</v>
+        <v>0.9933904297553344</v>
       </c>
       <c r="F205" t="n">
-        <v>7.575480578697133e-14</v>
+        <v>0.00660957024466557</v>
       </c>
       <c r="G205" t="n">
-        <v>0.9999999930282579</v>
+        <v>1.719768407769154e-18</v>
       </c>
     </row>
     <row r="206">
@@ -5578,16 +5578,16 @@
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206" t="n">
-        <v>0.9998962976373398</v>
+        <v>1.015638210643479e-07</v>
       </c>
       <c r="F206" t="n">
-        <v>2.124781701632662e-52</v>
+        <v>6.221921825830707e-11</v>
       </c>
       <c r="G206" t="n">
-        <v>0.000103702362660273</v>
+        <v>0.9999998983739596</v>
       </c>
     </row>
     <row r="207">
@@ -5606,13 +5606,13 @@
         <v>3</v>
       </c>
       <c r="E207" t="n">
-        <v>4.114796880617452e-07</v>
+        <v>0.01278511794368981</v>
       </c>
       <c r="F207" t="n">
-        <v>7.545664656486468e-18</v>
+        <v>7.22200598869848e-07</v>
       </c>
       <c r="G207" t="n">
-        <v>0.999999588520312</v>
+        <v>0.9872141598557113</v>
       </c>
     </row>
     <row r="208">
@@ -5631,13 +5631,13 @@
         <v>2</v>
       </c>
       <c r="E208" t="n">
-        <v>2.715012222207521e-29</v>
+        <v>0.1487337389709831</v>
       </c>
       <c r="F208" t="n">
-        <v>0.9999999999857581</v>
+        <v>0.8512662610290168</v>
       </c>
       <c r="G208" t="n">
-        <v>1.424185243473324e-11</v>
+        <v>1.818516605447594e-17</v>
       </c>
     </row>
     <row r="209">
@@ -5650,19 +5650,19 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>0.001771073641986717</v>
+        <v>0.9440503020679697</v>
       </c>
       <c r="F209" t="n">
-        <v>1.0922297473796e-19</v>
+        <v>6.865795848592631e-05</v>
       </c>
       <c r="G209" t="n">
-        <v>0.9982289263580133</v>
+        <v>0.05588103997354437</v>
       </c>
     </row>
     <row r="210">
@@ -5681,13 +5681,13 @@
         <v>3</v>
       </c>
       <c r="E210" t="n">
-        <v>8.489884780140636e-09</v>
+        <v>2.459713651521691e-17</v>
       </c>
       <c r="F210" t="n">
-        <v>1.016741135242514e-07</v>
+        <v>1.855782281965734e-20</v>
       </c>
       <c r="G210" t="n">
-        <v>0.9999998898360017</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -5700,19 +5700,19 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5212778425327972</v>
+        <v>2.390248872779615e-08</v>
       </c>
       <c r="F211" t="n">
-        <v>1.197356966508994e-27</v>
+        <v>1.027049572362561e-14</v>
       </c>
       <c r="G211" t="n">
-        <v>0.4787221574672029</v>
+        <v>0.999999976097501</v>
       </c>
     </row>
     <row r="212">
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="B212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -5731,13 +5731,13 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>0.9999996339048992</v>
+        <v>0.9932125113745492</v>
       </c>
       <c r="F212" t="n">
-        <v>7.480235954265385e-62</v>
+        <v>0.006787488625450535</v>
       </c>
       <c r="G212" t="n">
-        <v>3.660951008290679e-07</v>
+        <v>2.805908824159893e-16</v>
       </c>
     </row>
     <row r="213">
@@ -5750,19 +5750,19 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E213" t="n">
-        <v>0.9999082533288718</v>
+        <v>5.205298818720101e-10</v>
       </c>
       <c r="F213" t="n">
-        <v>3.740349392319402e-42</v>
+        <v>1.440257984345567e-14</v>
       </c>
       <c r="G213" t="n">
-        <v>9.174667112813313e-05</v>
+        <v>0.9999999994794557</v>
       </c>
     </row>
     <row r="214">
@@ -5781,13 +5781,13 @@
         <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>0.999608459685056</v>
+        <v>0.9998813272691779</v>
       </c>
       <c r="F214" t="n">
-        <v>2.798525788210362e-40</v>
+        <v>0.0001133592887608296</v>
       </c>
       <c r="G214" t="n">
-        <v>0.0003915403149440348</v>
+        <v>5.313442061309378e-06</v>
       </c>
     </row>
     <row r="215">
@@ -5806,13 +5806,13 @@
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>0.9999774042706211</v>
+        <v>0.9966707043391699</v>
       </c>
       <c r="F215" t="n">
-        <v>1.678616605808493e-44</v>
+        <v>0.003329295660829935</v>
       </c>
       <c r="G215" t="n">
-        <v>2.259572937887526e-05</v>
+        <v>6.479673633601073e-22</v>
       </c>
     </row>
     <row r="216">
@@ -5825,19 +5825,19 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E216" t="n">
-        <v>0.9975204928923559</v>
+        <v>6.652417957940076e-15</v>
       </c>
       <c r="F216" t="n">
-        <v>1.633921738917813e-35</v>
+        <v>7.374416576838135e-20</v>
       </c>
       <c r="G216" t="n">
-        <v>0.002479507107644136</v>
+        <v>0.9999999999999933</v>
       </c>
     </row>
     <row r="217">
@@ -5850,19 +5850,19 @@
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0413936596864084</v>
+        <v>0.9963995412247291</v>
       </c>
       <c r="F217" t="n">
-        <v>1.58773258024779e-32</v>
+        <v>0.0036004586531497</v>
       </c>
       <c r="G217" t="n">
-        <v>0.9586063403135916</v>
+        <v>1.22121287104827e-10</v>
       </c>
     </row>
     <row r="218">
@@ -5881,13 +5881,13 @@
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>0.9999111662938153</v>
+        <v>0.9996184025070135</v>
       </c>
       <c r="F218" t="n">
-        <v>3.489839835551912e-43</v>
+        <v>0.0003760239111856786</v>
       </c>
       <c r="G218" t="n">
-        <v>8.883370618476572e-05</v>
+        <v>5.573581800820326e-06</v>
       </c>
     </row>
     <row r="219">
@@ -5900,19 +5900,19 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>5.15475726246204e-06</v>
+        <v>0.9997723344099404</v>
       </c>
       <c r="F219" t="n">
-        <v>2.152737289674116e-20</v>
+        <v>0.0002276460918833892</v>
       </c>
       <c r="G219" t="n">
-        <v>0.9999948452427374</v>
+        <v>1.949817624198253e-08</v>
       </c>
     </row>
     <row r="220">
@@ -5925,19 +5925,19 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E220" t="n">
-        <v>0.6955614485672968</v>
+        <v>1.353933363738241e-11</v>
       </c>
       <c r="F220" t="n">
-        <v>1.470269549981756e-30</v>
+        <v>5.613169476204184e-17</v>
       </c>
       <c r="G220" t="n">
-        <v>0.3044385514327032</v>
+        <v>0.9999999999864606</v>
       </c>
     </row>
     <row r="221">
@@ -5956,13 +5956,13 @@
         <v>3</v>
       </c>
       <c r="E221" t="n">
-        <v>0.0001078846109778446</v>
+        <v>2.051112895143067e-36</v>
       </c>
       <c r="F221" t="n">
-        <v>3.072528604465431e-17</v>
+        <v>6.261604756359285e-42</v>
       </c>
       <c r="G221" t="n">
-        <v>0.9998921153890221</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -5981,13 +5981,13 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>0.999938377043043</v>
+        <v>0.9998277688142136</v>
       </c>
       <c r="F222" t="n">
-        <v>5.52386635123357e-44</v>
+        <v>0.0001719285089474133</v>
       </c>
       <c r="G222" t="n">
-        <v>6.162295695700293e-05</v>
+        <v>3.026768390207801e-07</v>
       </c>
     </row>
     <row r="223">
@@ -5997,22 +5997,22 @@
         </is>
       </c>
       <c r="B223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>0.004835581297689611</v>
+        <v>0.5564807001718851</v>
       </c>
       <c r="F223" t="n">
-        <v>2.152498354540545e-24</v>
+        <v>0.4435192998281149</v>
       </c>
       <c r="G223" t="n">
-        <v>0.9951644187023104</v>
+        <v>4.801381504122917e-34</v>
       </c>
     </row>
     <row r="224">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="B224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -6031,13 +6031,13 @@
         <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>0.9181546323588633</v>
+        <v>0.9927384464683222</v>
       </c>
       <c r="F224" t="n">
-        <v>3.237225634764065e-32</v>
+        <v>0.007261553531677714</v>
       </c>
       <c r="G224" t="n">
-        <v>0.08184536764113669</v>
+        <v>5.722586475372274e-39</v>
       </c>
     </row>
     <row r="225">
@@ -6047,22 +6047,22 @@
         </is>
       </c>
       <c r="B225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E225" t="n">
-        <v>0.001473973451602997</v>
+        <v>0.9979941495470832</v>
       </c>
       <c r="F225" t="n">
-        <v>1.166376182036637e-21</v>
+        <v>0.002005850452916702</v>
       </c>
       <c r="G225" t="n">
-        <v>0.9985260265483971</v>
+        <v>8.98422224087827e-27</v>
       </c>
     </row>
     <row r="226">
@@ -6072,22 +6072,22 @@
         </is>
       </c>
       <c r="B226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" t="n">
         <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>2.54894926290638e-09</v>
+        <v>0.8144072128536445</v>
       </c>
       <c r="F226" t="n">
-        <v>5.740271832383451e-05</v>
+        <v>0.1855927871463556</v>
       </c>
       <c r="G226" t="n">
-        <v>0.9999425947327268</v>
+        <v>2.750203486991994e-22</v>
       </c>
     </row>
     <row r="227">
@@ -6097,22 +6097,22 @@
         </is>
       </c>
       <c r="B227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E227" t="n">
-        <v>0.9999999999980993</v>
+        <v>1.384935410666222e-18</v>
       </c>
       <c r="F227" t="n">
-        <v>2.459292022266274e-62</v>
+        <v>7.699292622681426e-24</v>
       </c>
       <c r="G227" t="n">
-        <v>1.900638071646845e-12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -6122,22 +6122,22 @@
         </is>
       </c>
       <c r="B228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>0.3383294231383869</v>
+        <v>0.9994141993509844</v>
       </c>
       <c r="F228" t="n">
-        <v>2.213598762596805e-29</v>
+        <v>0.0005858006490154728</v>
       </c>
       <c r="G228" t="n">
-        <v>0.6616705768616131</v>
+        <v>1.04066055875601e-28</v>
       </c>
     </row>
     <row r="229">
@@ -6150,19 +6150,19 @@
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E229" t="n">
-        <v>0.9997981592442535</v>
+        <v>5.844785858942106e-30</v>
       </c>
       <c r="F229" t="n">
-        <v>2.160808266721066e-36</v>
+        <v>2.679198177281848e-33</v>
       </c>
       <c r="G229" t="n">
-        <v>0.0002018407557463978</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -6175,19 +6175,19 @@
         <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9999999999998308</v>
+        <v>7.469342326656154e-13</v>
       </c>
       <c r="F230" t="n">
-        <v>4.813105345036381e-70</v>
+        <v>2.998350931058425e-17</v>
       </c>
       <c r="G230" t="n">
-        <v>1.691407619938403e-13</v>
+        <v>0.999999999999253</v>
       </c>
     </row>
     <row r="231">
@@ -6197,22 +6197,22 @@
         </is>
       </c>
       <c r="B231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>3.844463197295467e-08</v>
+        <v>0.2686349931789204</v>
       </c>
       <c r="F231" t="n">
-        <v>1.677024592386758e-11</v>
+        <v>0.7313650068210796</v>
       </c>
       <c r="G231" t="n">
-        <v>0.9999999615385978</v>
+        <v>3.95524463373581e-32</v>
       </c>
     </row>
     <row r="232">
@@ -6225,19 +6225,19 @@
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>0.1817923521007524</v>
+        <v>0.9698788191598549</v>
       </c>
       <c r="F232" t="n">
-        <v>1.181560912387329e-28</v>
+        <v>0.03012118084014518</v>
       </c>
       <c r="G232" t="n">
-        <v>0.8182076478992476</v>
+        <v>6.579138042772044e-27</v>
       </c>
     </row>
     <row r="233">
@@ -6250,19 +6250,19 @@
         <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>0.02651583218129693</v>
+        <v>0.8893480618340152</v>
       </c>
       <c r="F233" t="n">
-        <v>8.143573813522776e-24</v>
+        <v>0.1106519381659848</v>
       </c>
       <c r="G233" t="n">
-        <v>0.973484167818703</v>
+        <v>1.919912913185403e-31</v>
       </c>
     </row>
     <row r="234">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E234" t="n">
-        <v>0.999999999858479</v>
+        <v>6.171165691474373e-25</v>
       </c>
       <c r="F234" t="n">
-        <v>7.334337982309767e-57</v>
+        <v>2.204585651314021e-29</v>
       </c>
       <c r="G234" t="n">
-        <v>1.415209642846558e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -6297,22 +6297,22 @@
         </is>
       </c>
       <c r="B235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E235" t="n">
-        <v>0.000973570071988631</v>
+        <v>0.7828238470897687</v>
       </c>
       <c r="F235" t="n">
-        <v>1.884017073273921e-21</v>
+        <v>0.2171761529102314</v>
       </c>
       <c r="G235" t="n">
-        <v>0.9990264299280114</v>
+        <v>8.852378618564675e-38</v>
       </c>
     </row>
     <row r="236">
@@ -6322,22 +6322,22 @@
         </is>
       </c>
       <c r="B236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E236" t="n">
-        <v>0.9999999999997662</v>
+        <v>6.514406329158804e-32</v>
       </c>
       <c r="F236" t="n">
-        <v>8.349938843540793e-68</v>
+        <v>1.008193000469149e-36</v>
       </c>
       <c r="G236" t="n">
-        <v>2.337122063737881e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="B237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -6356,13 +6356,13 @@
         <v>1</v>
       </c>
       <c r="E237" t="n">
-        <v>0.8682652512166414</v>
+        <v>0.9324216841645221</v>
       </c>
       <c r="F237" t="n">
-        <v>1.304045933370081e-32</v>
+        <v>0.06757831583547791</v>
       </c>
       <c r="G237" t="n">
-        <v>0.1317347487833585</v>
+        <v>1.750332447628084e-22</v>
       </c>
     </row>
     <row r="238">
@@ -6372,22 +6372,22 @@
         </is>
       </c>
       <c r="B238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>3.279974155102559e-07</v>
+        <v>0.9079011008008311</v>
       </c>
       <c r="F238" t="n">
-        <v>1.8134028059414e-09</v>
+        <v>0.09209889919916886</v>
       </c>
       <c r="G238" t="n">
-        <v>0.9999996701891818</v>
+        <v>3.841795911905917e-25</v>
       </c>
     </row>
     <row r="239">
@@ -6397,22 +6397,22 @@
         </is>
       </c>
       <c r="B239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C239" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>1.436736233479349e-09</v>
+        <v>0.9812250301269169</v>
       </c>
       <c r="F239" t="n">
-        <v>1.313301712513713e-10</v>
+        <v>0.01877496987174898</v>
       </c>
       <c r="G239" t="n">
-        <v>0.9999999984319337</v>
+        <v>1.334128842077602e-12</v>
       </c>
     </row>
     <row r="240">
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="B240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -6431,13 +6431,13 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9999541864067618</v>
+        <v>0.9976631683622095</v>
       </c>
       <c r="F240" t="n">
-        <v>5.522984145907315e-43</v>
+        <v>0.002336831637790527</v>
       </c>
       <c r="G240" t="n">
-        <v>4.581359323815356e-05</v>
+        <v>5.604936139623648e-31</v>
       </c>
     </row>
     <row r="241">
@@ -6453,16 +6453,16 @@
         <v>1</v>
       </c>
       <c r="D241" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0.100788981938709</v>
+        <v>0.9965227762286866</v>
       </c>
       <c r="F241" t="n">
-        <v>1.388523814739045e-26</v>
+        <v>0.003477223771313482</v>
       </c>
       <c r="G241" t="n">
-        <v>0.899211018061291</v>
+        <v>5.535327606021869e-35</v>
       </c>
     </row>
     <row r="242">
@@ -6472,22 +6472,22 @@
         </is>
       </c>
       <c r="B242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>1.762576643155634e-13</v>
+        <v>0.9999942000004347</v>
       </c>
       <c r="F242" t="n">
-        <v>0.9999515714195404</v>
+        <v>5.799999565323212e-06</v>
       </c>
       <c r="G242" t="n">
-        <v>4.842858028322997e-05</v>
+        <v>6.17960879420007e-56</v>
       </c>
     </row>
     <row r="243">
@@ -6497,22 +6497,22 @@
         </is>
       </c>
       <c r="B243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.01736053135516948</v>
+        <v>0.9908467521783334</v>
       </c>
       <c r="F243" t="n">
-        <v>7.554296986154411e-23</v>
+        <v>0.009153247821666674</v>
       </c>
       <c r="G243" t="n">
-        <v>0.9826394686448305</v>
+        <v>5.439767626469993e-44</v>
       </c>
     </row>
     <row r="244">
@@ -6525,19 +6525,19 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.01871604386135573</v>
+        <v>0.9898059896370828</v>
       </c>
       <c r="F244" t="n">
-        <v>9.820327856056327e-23</v>
+        <v>0.01019401036291718</v>
       </c>
       <c r="G244" t="n">
-        <v>0.9812839561386442</v>
+        <v>1.630885507967255e-27</v>
       </c>
     </row>
     <row r="245">
@@ -6550,19 +6550,19 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.04760533710968624</v>
+        <v>0.9999271265097378</v>
       </c>
       <c r="F245" t="n">
-        <v>1.016493615173269e-29</v>
+        <v>7.287325626063288e-05</v>
       </c>
       <c r="G245" t="n">
-        <v>0.9523946628903138</v>
+        <v>2.340014843627983e-10</v>
       </c>
     </row>
     <row r="246">
@@ -6572,22 +6572,22 @@
         </is>
       </c>
       <c r="B246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.08189809849598505</v>
+        <v>0.9999468217984029</v>
       </c>
       <c r="F246" t="n">
-        <v>1.185593883459653e-21</v>
+        <v>5.317820159724976e-05</v>
       </c>
       <c r="G246" t="n">
-        <v>0.9181019015040149</v>
+        <v>2.156390026592585e-39</v>
       </c>
     </row>
     <row r="247">
@@ -6597,22 +6597,22 @@
         </is>
       </c>
       <c r="B247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247" t="n">
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8816146094874469</v>
+        <v>0.9999767168786988</v>
       </c>
       <c r="F247" t="n">
-        <v>1.231809806556619e-36</v>
+        <v>2.32831212574836e-05</v>
       </c>
       <c r="G247" t="n">
-        <v>0.1183853905125532</v>
+        <v>4.370191390194611e-14</v>
       </c>
     </row>
     <row r="248">
@@ -6631,13 +6631,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.938323146861433</v>
+        <v>0.9522342373844825</v>
       </c>
       <c r="F248" t="n">
-        <v>2.765514827542879e-33</v>
+        <v>0.04776576261551745</v>
       </c>
       <c r="G248" t="n">
-        <v>0.061676853138567</v>
+        <v>1.07735987957441e-28</v>
       </c>
     </row>
     <row r="249">
@@ -6656,13 +6656,13 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>0.9938703069845746</v>
+        <v>0.9914373619450524</v>
       </c>
       <c r="F249" t="n">
-        <v>5.893127491478644e-39</v>
+        <v>0.008562638054947593</v>
       </c>
       <c r="G249" t="n">
-        <v>0.006129693015425484</v>
+        <v>1.869073835460701e-36</v>
       </c>
     </row>
     <row r="250">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="B250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -6681,13 +6681,13 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.9977969200093701</v>
+        <v>0.9931130852752955</v>
       </c>
       <c r="F250" t="n">
-        <v>1.789053461295778e-39</v>
+        <v>0.006886914724704428</v>
       </c>
       <c r="G250" t="n">
-        <v>0.002203079990629939</v>
+        <v>1.764600210286172e-36</v>
       </c>
     </row>
     <row r="251">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="B251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -6706,13 +6706,13 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9991987411930573</v>
+        <v>0.9922950453301113</v>
       </c>
       <c r="F251" t="n">
-        <v>1.206056566286365e-40</v>
+        <v>0.007704954669888721</v>
       </c>
       <c r="G251" t="n">
-        <v>0.0008012588069427731</v>
+        <v>3.726178815735047e-40</v>
       </c>
     </row>
     <row r="252">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="B252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
@@ -6731,13 +6731,13 @@
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6066147530059379</v>
+        <v>0.9916268338029839</v>
       </c>
       <c r="F252" t="n">
-        <v>4.636494393095663e-32</v>
+        <v>0.008373166197016214</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3933852469940621</v>
+        <v>2.604814110555107e-32</v>
       </c>
     </row>
     <row r="253">
@@ -6747,22 +6747,22 @@
         </is>
       </c>
       <c r="B253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0.01059809146738633</v>
+        <v>0.9220594925296278</v>
       </c>
       <c r="F253" t="n">
-        <v>1.956158904657223e-23</v>
+        <v>0.0779405074703723</v>
       </c>
       <c r="G253" t="n">
-        <v>0.9894019085326136</v>
+        <v>9.649062903675408e-23</v>
       </c>
     </row>
     <row r="254">
@@ -6775,19 +6775,19 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E254" t="n">
-        <v>2.152172007182388e-12</v>
+        <v>0.09251859979419982</v>
       </c>
       <c r="F254" t="n">
-        <v>0.1195852538928943</v>
+        <v>0.9074814002058003</v>
       </c>
       <c r="G254" t="n">
-        <v>0.8804147461049535</v>
+        <v>8.472149642891397e-32</v>
       </c>
     </row>
     <row r="255">
@@ -6806,13 +6806,13 @@
         <v>2</v>
       </c>
       <c r="E255" t="n">
-        <v>6.893313924764092e-17</v>
+        <v>0.01479058136081872</v>
       </c>
       <c r="F255" t="n">
-        <v>0.9991222370695466</v>
+        <v>0.9852094186391813</v>
       </c>
       <c r="G255" t="n">
-        <v>0.0008777629304534548</v>
+        <v>1.450400060345938e-36</v>
       </c>
     </row>
     <row r="256">
@@ -6822,22 +6822,22 @@
         </is>
       </c>
       <c r="B256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.007698056711547942</v>
+        <v>0.9941010473697466</v>
       </c>
       <c r="F256" t="n">
-        <v>2.223868279993944e-26</v>
+        <v>0.005898952630253456</v>
       </c>
       <c r="G256" t="n">
-        <v>0.992301943288452</v>
+        <v>3.61365446238452e-30</v>
       </c>
     </row>
     <row r="257">
@@ -6850,19 +6850,19 @@
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.002737404382794862</v>
+        <v>0.9897240153167656</v>
       </c>
       <c r="F257" t="n">
-        <v>5.496115118174016e-25</v>
+        <v>0.0102759846832343</v>
       </c>
       <c r="G257" t="n">
-        <v>0.9972625956172051</v>
+        <v>8.710887820178603e-38</v>
       </c>
     </row>
     <row r="258">
@@ -6872,22 +6872,22 @@
         </is>
       </c>
       <c r="B258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D258" t="n">
         <v>2</v>
       </c>
       <c r="E258" t="n">
-        <v>3.580721918993571e-16</v>
+        <v>0.002702766393568608</v>
       </c>
       <c r="F258" t="n">
-        <v>0.9975692705260121</v>
+        <v>0.9972972336064313</v>
       </c>
       <c r="G258" t="n">
-        <v>0.002430729473987385</v>
+        <v>4.339816498880127e-31</v>
       </c>
     </row>
     <row r="259">
@@ -6900,19 +6900,19 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>8.797954981786089e-07</v>
+        <v>0.9357212790306125</v>
       </c>
       <c r="F259" t="n">
-        <v>6.483138222902876e-16</v>
+        <v>0.06427872096938736</v>
       </c>
       <c r="G259" t="n">
-        <v>0.9999991202045011</v>
+        <v>4.905847598017339e-34</v>
       </c>
     </row>
     <row r="260">
@@ -6931,13 +6931,13 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.5113627022844083</v>
+        <v>0.9745651838538226</v>
       </c>
       <c r="F260" t="n">
-        <v>8.128039932095475e-34</v>
+        <v>0.0254348161461774</v>
       </c>
       <c r="G260" t="n">
-        <v>0.4886372977155917</v>
+        <v>1.162812383077263e-41</v>
       </c>
     </row>
     <row r="261">
@@ -6950,19 +6950,19 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E261" t="n">
-        <v>1.177632430259274e-09</v>
+        <v>0.4568239273715173</v>
       </c>
       <c r="F261" t="n">
-        <v>2.002636634782807e-09</v>
+        <v>0.5431760726284827</v>
       </c>
       <c r="G261" t="n">
-        <v>0.9999999968197308</v>
+        <v>1.309516386554037e-33</v>
       </c>
     </row>
     <row r="262">
@@ -6975,19 +6975,19 @@
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E262" t="n">
-        <v>1.800129107544499e-05</v>
+        <v>0.4592790459374463</v>
       </c>
       <c r="F262" t="n">
-        <v>5.236965985232905e-18</v>
+        <v>0.5407209540625536</v>
       </c>
       <c r="G262" t="n">
-        <v>0.9999819987089247</v>
+        <v>3.674673083795742e-31</v>
       </c>
     </row>
     <row r="263">
@@ -6997,22 +6997,22 @@
         </is>
       </c>
       <c r="B263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>2.9945726128416e-11</v>
+        <v>0.6424133429665312</v>
       </c>
       <c r="F263" t="n">
-        <v>4.098444363485444e-05</v>
+        <v>0.3575866570334688</v>
       </c>
       <c r="G263" t="n">
-        <v>0.9999590155264194</v>
+        <v>2.381993386855221e-22</v>
       </c>
     </row>
     <row r="264">
@@ -7025,19 +7025,19 @@
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.01191408062119542</v>
+        <v>0.99984739406044</v>
       </c>
       <c r="F264" t="n">
-        <v>3.914252695954281e-25</v>
+        <v>0.000152605939559959</v>
       </c>
       <c r="G264" t="n">
-        <v>0.9880859193788045</v>
+        <v>1.915011386973616e-23</v>
       </c>
     </row>
     <row r="265">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="B265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C265" t="n">
         <v>1</v>
@@ -7056,13 +7056,13 @@
         <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0.6602429471312441</v>
+        <v>0.9860409183750889</v>
       </c>
       <c r="F265" t="n">
-        <v>8.153036295261565e-32</v>
+        <v>0.01395908162491114</v>
       </c>
       <c r="G265" t="n">
-        <v>0.339757052868756</v>
+        <v>3.444560014487434e-30</v>
       </c>
     </row>
     <row r="266">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="B266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C266" t="n">
         <v>1</v>
@@ -7081,13 +7081,13 @@
         <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0.999685778823274</v>
+        <v>0.995909569682116</v>
       </c>
       <c r="F266" t="n">
-        <v>7.760841568720996e-42</v>
+        <v>0.004090430317884105</v>
       </c>
       <c r="G266" t="n">
-        <v>0.0003142211767259779</v>
+        <v>1.370873129315487e-38</v>
       </c>
     </row>
     <row r="267">
@@ -7097,22 +7097,22 @@
         </is>
       </c>
       <c r="B267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D267" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.001063172405406924</v>
+        <v>0.8794134971166455</v>
       </c>
       <c r="F267" t="n">
-        <v>6.699461368704255e-23</v>
+        <v>0.1205865028833544</v>
       </c>
       <c r="G267" t="n">
-        <v>0.9989368275945931</v>
+        <v>5.774297498596669e-30</v>
       </c>
     </row>
     <row r="268">
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C268" t="n">
         <v>1</v>
@@ -7131,13 +7131,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.9997457687801306</v>
+        <v>0.9858915970996538</v>
       </c>
       <c r="F268" t="n">
-        <v>1.259921851364677e-45</v>
+        <v>0.01410840290034625</v>
       </c>
       <c r="G268" t="n">
-        <v>0.0002542312198695137</v>
+        <v>2.858856496962257e-31</v>
       </c>
     </row>
     <row r="269">
@@ -7147,22 +7147,22 @@
         </is>
       </c>
       <c r="B269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.0002616920273243704</v>
+        <v>0.9330663222691633</v>
       </c>
       <c r="F269" t="n">
-        <v>4.171697000952332e-22</v>
+        <v>0.06693367773083669</v>
       </c>
       <c r="G269" t="n">
-        <v>0.9997383079726757</v>
+        <v>8.105350641213544e-28</v>
       </c>
     </row>
     <row r="270">
@@ -7172,22 +7172,22 @@
         </is>
       </c>
       <c r="B270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>3.213853407524321e-05</v>
+        <v>0.9308528032707329</v>
       </c>
       <c r="F270" t="n">
-        <v>5.325414804438009e-20</v>
+        <v>0.06914719672926693</v>
       </c>
       <c r="G270" t="n">
-        <v>0.9999678614659248</v>
+        <v>2.31658204927648e-24</v>
       </c>
     </row>
     <row r="271">
@@ -7200,19 +7200,19 @@
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.000324121811101687</v>
+        <v>0.996569074032493</v>
       </c>
       <c r="F271" t="n">
-        <v>1.64037336005604e-20</v>
+        <v>0.003430925965550857</v>
       </c>
       <c r="G271" t="n">
-        <v>0.9996758781888982</v>
+        <v>1.956122925593641e-12</v>
       </c>
     </row>
     <row r="272">
@@ -7222,22 +7222,22 @@
         </is>
       </c>
       <c r="B272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>3.433282198896874e-11</v>
+        <v>0.6499774665280567</v>
       </c>
       <c r="F272" t="n">
-        <v>0.0004855510288444942</v>
+        <v>0.3500225334719434</v>
       </c>
       <c r="G272" t="n">
-        <v>0.9995144489368226</v>
+        <v>4.664395687976026e-43</v>
       </c>
     </row>
     <row r="273">
@@ -7250,19 +7250,19 @@
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>6.019917381314734e-11</v>
+        <v>0.5110027174231291</v>
       </c>
       <c r="F273" t="n">
-        <v>0.001426045232730693</v>
+        <v>0.4889972825768709</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9985739547070702</v>
+        <v>2.338510623573212e-26</v>
       </c>
     </row>
     <row r="274">
@@ -7272,22 +7272,22 @@
         </is>
       </c>
       <c r="B274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E274" t="n">
-        <v>8.111046702048509e-14</v>
+        <v>0.03047746694880172</v>
       </c>
       <c r="F274" t="n">
-        <v>0.4060544925720898</v>
+        <v>0.9695225330511983</v>
       </c>
       <c r="G274" t="n">
-        <v>0.593945507427829</v>
+        <v>1.013467356756302e-42</v>
       </c>
     </row>
     <row r="275">
@@ -7297,22 +7297,22 @@
         </is>
       </c>
       <c r="B275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>1.87646255250041e-10</v>
+        <v>0.7450118025908699</v>
       </c>
       <c r="F275" t="n">
-        <v>8.197919315077676e-08</v>
+        <v>0.2549881974091301</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9999999178331606</v>
+        <v>3.004095904865443e-42</v>
       </c>
     </row>
     <row r="276">
@@ -7325,19 +7325,19 @@
         <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>1.495800896865028e-11</v>
+        <v>0.7795467064058303</v>
       </c>
       <c r="F276" t="n">
-        <v>8.113394668072963e-05</v>
+        <v>0.2204532935941697</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9999188660383612</v>
+        <v>1.093809530675285e-34</v>
       </c>
     </row>
     <row r="277">
@@ -7350,19 +7350,19 @@
         <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>2.155145166290903e-09</v>
+        <v>0.8923791214937214</v>
       </c>
       <c r="F277" t="n">
-        <v>5.762054913025704e-09</v>
+        <v>0.1076208785062787</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9999999920827999</v>
+        <v>7.530125204966352e-18</v>
       </c>
     </row>
     <row r="278">
@@ -7375,19 +7375,19 @@
         <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>0.002026640190389209</v>
+        <v>0.9796126272352909</v>
       </c>
       <c r="F278" t="n">
-        <v>3.566748801922342e-22</v>
+        <v>0.02005970697903846</v>
       </c>
       <c r="G278" t="n">
-        <v>0.9979733598096108</v>
+        <v>0.00032766578567086</v>
       </c>
     </row>
     <row r="279">
@@ -7400,19 +7400,19 @@
         <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E279" t="n">
-        <v>0.9999999997679165</v>
+        <v>2.294369900964399e-31</v>
       </c>
       <c r="F279" t="n">
-        <v>7.886824801655651e-58</v>
+        <v>3.686096110036996e-35</v>
       </c>
       <c r="G279" t="n">
-        <v>2.320834809465731e-10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -7431,13 +7431,13 @@
         <v>1</v>
       </c>
       <c r="E280" t="n">
-        <v>0.9921625352196256</v>
+        <v>0.994740692737531</v>
       </c>
       <c r="F280" t="n">
-        <v>2.810641108415308e-37</v>
+        <v>0.00525930726246916</v>
       </c>
       <c r="G280" t="n">
-        <v>0.007837464780374458</v>
+        <v>3.542956477287938e-36</v>
       </c>
     </row>
     <row r="281">
@@ -7456,13 +7456,13 @@
         <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>0.7272745145713013</v>
+        <v>0.6569797564650154</v>
       </c>
       <c r="F281" t="n">
-        <v>1.190927851874059e-33</v>
+        <v>0.3430202435349846</v>
       </c>
       <c r="G281" t="n">
-        <v>0.2727254854286987</v>
+        <v>2.192273221090858e-38</v>
       </c>
     </row>
     <row r="282">
@@ -7472,22 +7472,22 @@
         </is>
       </c>
       <c r="B282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E282" t="n">
-        <v>2.369875468593249e-06</v>
+        <v>0.8522487360710671</v>
       </c>
       <c r="F282" t="n">
-        <v>1.495244186420027e-17</v>
+        <v>0.147751263928933</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9999976301245314</v>
+        <v>7.383350965450501e-42</v>
       </c>
     </row>
     <row r="283">
@@ -7497,22 +7497,22 @@
         </is>
       </c>
       <c r="B283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E283" t="n">
-        <v>0.005572051047711145</v>
+        <v>0.9695368636876834</v>
       </c>
       <c r="F283" t="n">
-        <v>1.254599330355979e-26</v>
+        <v>0.0304631363123167</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9944279489522888</v>
+        <v>3.238116375935817e-31</v>
       </c>
     </row>
     <row r="284">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="B284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C284" t="n">
         <v>1</v>
@@ -7531,13 +7531,13 @@
         <v>1</v>
       </c>
       <c r="E284" t="n">
-        <v>0.9994154258552613</v>
+        <v>0.918986457535833</v>
       </c>
       <c r="F284" t="n">
-        <v>1.638140246144911e-45</v>
+        <v>0.08101354246416707</v>
       </c>
       <c r="G284" t="n">
-        <v>0.0005845741447387961</v>
+        <v>2.956104273265506e-36</v>
       </c>
     </row>
     <row r="285">
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="B285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E285" t="n">
-        <v>0.01977728477273527</v>
+        <v>0.5999093527367141</v>
       </c>
       <c r="F285" t="n">
-        <v>2.240580534705122e-25</v>
+        <v>0.400090647263286</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9802227152272647</v>
+        <v>1.605442850051178e-31</v>
       </c>
     </row>
     <row r="286">
@@ -7572,22 +7572,22 @@
         </is>
       </c>
       <c r="B286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E286" t="n">
-        <v>0.9968678558562892</v>
+        <v>0.399678313547528</v>
       </c>
       <c r="F286" t="n">
-        <v>5.701211931724273e-40</v>
+        <v>0.600321686452472</v>
       </c>
       <c r="G286" t="n">
-        <v>0.003132144143710733</v>
+        <v>3.237111742680726e-33</v>
       </c>
     </row>
     <row r="287">
@@ -7597,22 +7597,22 @@
         </is>
       </c>
       <c r="B287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E287" t="n">
-        <v>2.909827658061603e-06</v>
+        <v>0.8870339748969177</v>
       </c>
       <c r="F287" t="n">
-        <v>1.058547702071358e-16</v>
+        <v>0.1129660251030822</v>
       </c>
       <c r="G287" t="n">
-        <v>0.9999970901723417</v>
+        <v>1.845510896678766e-28</v>
       </c>
     </row>
     <row r="288">
@@ -7625,19 +7625,19 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>8.559378663863343e-10</v>
+        <v>0.9248742784189371</v>
       </c>
       <c r="F288" t="n">
-        <v>2.166145450531793e-06</v>
+        <v>0.07512572158106286</v>
       </c>
       <c r="G288" t="n">
-        <v>0.9999978329986116</v>
+        <v>2.981862459146728e-36</v>
       </c>
     </row>
     <row r="289">
@@ -7647,22 +7647,22 @@
         </is>
       </c>
       <c r="B289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>0.002848292670818651</v>
+        <v>0.9921407358770273</v>
       </c>
       <c r="F289" t="n">
-        <v>3.813065029422325e-21</v>
+        <v>0.007859264122972592</v>
       </c>
       <c r="G289" t="n">
-        <v>0.9971517073291815</v>
+        <v>2.280205109306539e-22</v>
       </c>
     </row>
     <row r="290">
@@ -7672,22 +7672,22 @@
         </is>
       </c>
       <c r="B290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C290" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>0.1872529666457595</v>
+        <v>0.9807749478333576</v>
       </c>
       <c r="F290" t="n">
-        <v>4.48853772568646e-28</v>
+        <v>0.01922505216664237</v>
       </c>
       <c r="G290" t="n">
-        <v>0.8127470333542405</v>
+        <v>1.278246593898778e-36</v>
       </c>
     </row>
     <row r="291">
@@ -7700,19 +7700,19 @@
         <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E291" t="n">
-        <v>1.508508664928894e-08</v>
+        <v>0.9653654294528493</v>
       </c>
       <c r="F291" t="n">
-        <v>1.015358038642906e-06</v>
+        <v>0.03463457054715068</v>
       </c>
       <c r="G291" t="n">
-        <v>0.9999989695568747</v>
+        <v>8.514103645516752e-22</v>
       </c>
     </row>
     <row r="292">
@@ -7728,16 +7728,16 @@
         <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E292" t="n">
-        <v>0.9999999999605622</v>
+        <v>8.05497874919727e-24</v>
       </c>
       <c r="F292" t="n">
-        <v>1.64577733998495e-58</v>
+        <v>1.513646066676685e-29</v>
       </c>
       <c r="G292" t="n">
-        <v>3.943772620685546e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -7747,22 +7747,22 @@
         </is>
       </c>
       <c r="B293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E293" t="n">
-        <v>0.3495898136424769</v>
+        <v>0.9962283222779791</v>
       </c>
       <c r="F293" t="n">
-        <v>7.517622453527572e-26</v>
+        <v>0.003771677722021046</v>
       </c>
       <c r="G293" t="n">
-        <v>0.650410186357523</v>
+        <v>1.206647137586476e-31</v>
       </c>
     </row>
     <row r="294">
@@ -7781,13 +7781,13 @@
         <v>3</v>
       </c>
       <c r="E294" t="n">
-        <v>9.196166308689432e-05</v>
+        <v>5.644381676269288e-41</v>
       </c>
       <c r="F294" t="n">
-        <v>1.28530750457627e-09</v>
+        <v>1.295927209617741e-42</v>
       </c>
       <c r="G294" t="n">
-        <v>0.9999080370516056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -7800,19 +7800,19 @@
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E295" t="n">
-        <v>0.9531773723428593</v>
+        <v>1.296071007042675e-06</v>
       </c>
       <c r="F295" t="n">
-        <v>1.212777018932982e-29</v>
+        <v>1.622814614517076e-11</v>
       </c>
       <c r="G295" t="n">
-        <v>0.04682262765714058</v>
+        <v>0.9999987039127648</v>
       </c>
     </row>
     <row r="296">
@@ -7825,19 +7825,19 @@
         <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>1.128155025203961e-07</v>
+        <v>0.9897744383890923</v>
       </c>
       <c r="F296" t="n">
-        <v>6.808068339256836e-10</v>
+        <v>0.01022556161090768</v>
       </c>
       <c r="G296" t="n">
-        <v>0.9999998865036905</v>
+        <v>8.284370407452495e-18</v>
       </c>
     </row>
     <row r="297">
@@ -7856,13 +7856,13 @@
         <v>3</v>
       </c>
       <c r="E297" t="n">
-        <v>5.687531120734105e-06</v>
+        <v>9.474473583511146e-39</v>
       </c>
       <c r="F297" t="n">
-        <v>3.830944453148865e-07</v>
+        <v>7.16993876433125e-41</v>
       </c>
       <c r="G297" t="n">
-        <v>0.999993929374434</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -7875,19 +7875,19 @@
         <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E298" t="n">
-        <v>3.157429120638231e-19</v>
+        <v>0.7167947278587867</v>
       </c>
       <c r="F298" t="n">
-        <v>0.9999955973727481</v>
+        <v>0.2832052721412133</v>
       </c>
       <c r="G298" t="n">
-        <v>4.402627251842001e-06</v>
+        <v>2.67665002856225e-19</v>
       </c>
     </row>
     <row r="299">
@@ -7897,22 +7897,22 @@
         </is>
       </c>
       <c r="B299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D299" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>1.112384426951539e-06</v>
+        <v>0.6036338423070458</v>
       </c>
       <c r="F299" t="n">
-        <v>2.300545329107072e-14</v>
+        <v>0.3963661576929542</v>
       </c>
       <c r="G299" t="n">
-        <v>0.9999988876155501</v>
+        <v>1.492633568152601e-34</v>
       </c>
     </row>
     <row r="300">
@@ -7931,13 +7931,13 @@
         <v>3</v>
       </c>
       <c r="E300" t="n">
-        <v>0.05156094017344572</v>
+        <v>4.61841004924574e-32</v>
       </c>
       <c r="F300" t="n">
-        <v>2.411996714175075e-18</v>
+        <v>1.540247816825955e-34</v>
       </c>
       <c r="G300" t="n">
-        <v>0.9484390598265543</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -7950,19 +7950,19 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E301" t="n">
-        <v>0.9999915562857961</v>
+        <v>0.007565113216882607</v>
       </c>
       <c r="F301" t="n">
-        <v>3.622736204711302e-43</v>
+        <v>2.303456409745842e-07</v>
       </c>
       <c r="G301" t="n">
-        <v>8.443714203960048e-06</v>
+        <v>0.9924346564374764</v>
       </c>
     </row>
     <row r="302">
@@ -7981,13 +7981,13 @@
         <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>0.7325076112933611</v>
+        <v>0.9998999059828615</v>
       </c>
       <c r="F302" t="n">
-        <v>1.828515937385743e-29</v>
+        <v>0.000100089650050934</v>
       </c>
       <c r="G302" t="n">
-        <v>0.2674923887066389</v>
+        <v>4.367087588692211e-09</v>
       </c>
     </row>
     <row r="303">
@@ -8000,19 +8000,19 @@
         <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E303" t="n">
-        <v>2.011226996628609e-17</v>
+        <v>2.358749523344202e-62</v>
       </c>
       <c r="F303" t="n">
-        <v>0.9999977043732314</v>
+        <v>1.580578209813729e-68</v>
       </c>
       <c r="G303" t="n">
-        <v>2.295626768438919e-06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="B304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C304" t="n">
         <v>1</v>
@@ -8031,13 +8031,13 @@
         <v>1</v>
       </c>
       <c r="E304" t="n">
-        <v>0.9998583256430906</v>
+        <v>0.9909751931236458</v>
       </c>
       <c r="F304" t="n">
-        <v>5.545242085541379e-44</v>
+        <v>0.009024806876354151</v>
       </c>
       <c r="G304" t="n">
-        <v>0.0001416743569093358</v>
+        <v>3.987718882843544e-36</v>
       </c>
     </row>
     <row r="305">
@@ -8053,16 +8053,16 @@
         <v>1</v>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E305" t="n">
-        <v>0.4133489369190837</v>
+        <v>0.9983342227881874</v>
       </c>
       <c r="F305" t="n">
-        <v>5.143367635951179e-28</v>
+        <v>0.001665777211812657</v>
       </c>
       <c r="G305" t="n">
-        <v>0.5866510630809163</v>
+        <v>1.933211459891826e-33</v>
       </c>
     </row>
     <row r="306">
@@ -8075,19 +8075,19 @@
         <v>0</v>
       </c>
       <c r="C306" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D306" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E306" t="n">
-        <v>0.01833111369758912</v>
+        <v>0.9998515911592036</v>
       </c>
       <c r="F306" t="n">
-        <v>8.694945228062813e-26</v>
+        <v>0.0001484088407965042</v>
       </c>
       <c r="G306" t="n">
-        <v>0.9816688863024109</v>
+        <v>8.045963798180108e-20</v>
       </c>
     </row>
     <row r="307">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="B307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C307" t="n">
         <v>1</v>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E307" t="n">
-        <v>0.9999999999999991</v>
+        <v>1.272057524040049e-18</v>
       </c>
       <c r="F307" t="n">
-        <v>1.74798627420778e-77</v>
+        <v>8.360190676480656e-23</v>
       </c>
       <c r="G307" t="n">
-        <v>9.157178065411441e-16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -8131,13 +8131,13 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>0.9856538617896731</v>
+        <v>0.9978512244967422</v>
       </c>
       <c r="F308" t="n">
-        <v>6.761546241632487e-42</v>
+        <v>0.002148775503257743</v>
       </c>
       <c r="G308" t="n">
-        <v>0.01434613821032687</v>
+        <v>1.558205630755049e-26</v>
       </c>
     </row>
     <row r="309">
@@ -8156,13 +8156,13 @@
         <v>1</v>
       </c>
       <c r="E309" t="n">
-        <v>0.9324584860554527</v>
+        <v>0.9998110993993856</v>
       </c>
       <c r="F309" t="n">
-        <v>9.478871782851233e-39</v>
+        <v>0.000188900600614106</v>
       </c>
       <c r="G309" t="n">
-        <v>0.06754151394454742</v>
+        <v>1.513639633224811e-16</v>
       </c>
     </row>
     <row r="310">
@@ -8175,19 +8175,19 @@
         <v>0</v>
       </c>
       <c r="C310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>3.953443266808728e-05</v>
+        <v>0.997259744430591</v>
       </c>
       <c r="F310" t="n">
-        <v>9.197015235686526e-21</v>
+        <v>0.001215144382507842</v>
       </c>
       <c r="G310" t="n">
-        <v>0.9999604655673319</v>
+        <v>0.001525111186901139</v>
       </c>
     </row>
     <row r="311">
@@ -8200,19 +8200,19 @@
         <v>0</v>
       </c>
       <c r="C311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E311" t="n">
-        <v>0.0002487349002032935</v>
+        <v>0.9999032019941132</v>
       </c>
       <c r="F311" t="n">
-        <v>5.147676483388388e-26</v>
+        <v>9.679800588677554e-05</v>
       </c>
       <c r="G311" t="n">
-        <v>0.9997512650997966</v>
+        <v>3.435874632320647e-22</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G311"/>
+  <dimension ref="A1:F311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,6 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Prob_Cluster 2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>Prob_Cluster 3</t>
         </is>
       </c>
@@ -481,13 +476,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9974498653622463</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002550134637753637</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.467033863945152e-18</v>
+        <v>1.577323370632145e-37</v>
       </c>
     </row>
     <row r="3">
@@ -506,13 +498,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.998752729442381</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001247270557618951</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9.474796039594086e-27</v>
+        <v>2.659608448613661e-44</v>
       </c>
     </row>
     <row r="4">
@@ -531,13 +520,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999820623591859</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.793764081405901e-05</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.639156918384471e-19</v>
+        <v>6.396275756989901e-41</v>
       </c>
     </row>
     <row r="5">
@@ -556,13 +542,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8881088149931345</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1118911850068655</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.335917809268925e-34</v>
+        <v>4.184700140099287e-106</v>
       </c>
     </row>
     <row r="6">
@@ -581,13 +564,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9636676644647262</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03633233553527394</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.187879582126876e-39</v>
+        <v>1.139548109503929e-56</v>
       </c>
     </row>
     <row r="7">
@@ -606,13 +586,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9990209261705724</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009790738294276837</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.981688091680475e-29</v>
+        <v>1.813599903472144e-58</v>
       </c>
     </row>
     <row r="8">
@@ -631,13 +608,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9963421466445079</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003657852194654749</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.160837427454919e-09</v>
+        <v>1.366398330948042e-40</v>
       </c>
     </row>
     <row r="9">
@@ -656,13 +630,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.772986580653004</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2270134193469959</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.547904749260524e-19</v>
+        <v>6.546577214714725e-74</v>
       </c>
     </row>
     <row r="10">
@@ -681,13 +652,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9218083795222423</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07819162047775782</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.154206650942864e-34</v>
+        <v>9.016568227907951e-86</v>
       </c>
     </row>
     <row r="11">
@@ -706,13 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9944989068750124</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005501093124987577</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.588017514333789e-26</v>
+        <v>1.9326987859514e-77</v>
       </c>
     </row>
     <row r="12">
@@ -725,19 +690,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2465991431001034</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7534008568998967</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.178079781245579e-18</v>
+        <v>1.601654070353406e-72</v>
       </c>
     </row>
     <row r="13">
@@ -756,13 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9384714537499251</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06152488859827776</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.657651797018479e-06</v>
+        <v>1.140009424704253e-41</v>
       </c>
     </row>
     <row r="14">
@@ -781,13 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999903414547487</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>9.656150967323422e-06</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.394283841227986e-09</v>
+        <v>7.89138125903788e-40</v>
       </c>
     </row>
     <row r="15">
@@ -806,13 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9809454280924567</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01905457190754335</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4.498797628168144e-24</v>
+        <v>1.609617717817374e-78</v>
       </c>
     </row>
     <row r="16">
@@ -825,19 +778,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>3.124375667252805e-06</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.418377383863167e-06</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9999954572469488</v>
+        <v>5.044554283263594e-37</v>
       </c>
     </row>
     <row r="17">
@@ -856,13 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9984913654478864</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001508634552113599</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.378911087055579e-20</v>
+        <v>1.413324859814392e-75</v>
       </c>
     </row>
     <row r="18">
@@ -881,13 +828,10 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>8.701810171668019e-18</v>
+        <v>0.01699510893765099</v>
       </c>
       <c r="F18" t="n">
-        <v>1.73289644088277e-18</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
+        <v>0.983004891062349</v>
       </c>
     </row>
     <row r="19">
@@ -900,19 +844,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3988116546943388</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6011883453055894</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7.192701504395306e-14</v>
+        <v>4.662710422532653e-79</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +872,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999896704916958</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1.032950830413329e-05</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6.380929209401282e-17</v>
+        <v>3.445148048023012e-64</v>
       </c>
     </row>
     <row r="21">
@@ -956,13 +894,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6369431262158399</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3630568737819351</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.225042520060694e-12</v>
+        <v>1.179693874995054e-73</v>
       </c>
     </row>
     <row r="22">
@@ -981,13 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999874062888694</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.259371113060668e-05</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.703919512633276e-24</v>
+        <v>1.733052692550053e-99</v>
       </c>
     </row>
     <row r="23">
@@ -1006,13 +938,10 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>6.95075596628408e-19</v>
+        <v>3.556223465606134e-05</v>
       </c>
       <c r="F23" t="n">
-        <v>9.23806991212004e-22</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
+        <v>0.9999644377653439</v>
       </c>
     </row>
     <row r="24">
@@ -1025,19 +954,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2240663132706526</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7759336867293475</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4.686895349388496e-53</v>
+        <v>1.41910660054016e-139</v>
       </c>
     </row>
     <row r="25">
@@ -1050,19 +976,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4576909110867951</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.542309088913205</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.74450989391711e-34</v>
+        <v>8.156113214393498e-77</v>
       </c>
     </row>
     <row r="26">
@@ -1075,19 +998,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2803859731094322</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7196140268876227</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.945006065023606e-12</v>
+        <v>1.122540861077599e-45</v>
       </c>
     </row>
     <row r="27">
@@ -1106,12 +1026,9 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2.43092219663653e-27</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.312771402995716e-30</v>
-      </c>
-      <c r="G27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1125,19 +1042,16 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1532082812487736</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0007260021743408798</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.8460657165768855</v>
+        <v>9.381978972213362e-43</v>
       </c>
     </row>
     <row r="29">
@@ -1156,12 +1070,9 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>4.150956638193203e-129</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>5.606193087830236e-138</v>
-      </c>
-      <c r="G29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1181,12 +1092,9 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>3.008155015899652e-56</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>2.910855129134498e-59</v>
-      </c>
-      <c r="G30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1206,13 +1114,10 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6717665684721295</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3282334315278629</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7.563093153151979e-15</v>
+        <v>1.021860173449953e-77</v>
       </c>
     </row>
     <row r="32">
@@ -1225,19 +1130,16 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.009632252489449114</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9903677475101794</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.714466380308182e-13</v>
+        <v>3.652668072077491e-74</v>
       </c>
     </row>
     <row r="33">
@@ -1256,13 +1158,10 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>2.66232254093986e-43</v>
+        <v>1.782285430351749e-10</v>
       </c>
       <c r="F33" t="n">
-        <v>1.11266761474873e-50</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
+        <v>0.9999999998217715</v>
       </c>
     </row>
     <row r="34">
@@ -1275,19 +1174,16 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04333350049406969</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06057350193081879</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.8960929975751115</v>
+        <v>1.832500149384973e-62</v>
       </c>
     </row>
     <row r="35">
@@ -1306,13 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.999927598101092</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>7.24018989079139e-05</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.916197345101366e-35</v>
+        <v>8.130510142834432e-84</v>
       </c>
     </row>
     <row r="36">
@@ -1331,13 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9999802646698374</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1.973533016264458e-05</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.724801526153289e-29</v>
+        <v>4.929587278113905e-87</v>
       </c>
     </row>
     <row r="37">
@@ -1350,19 +1240,16 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.006416975032948294</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1.906443616440184e-05</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.9935639605308874</v>
+        <v>4.646578664185266e-28</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1262,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.09498466112074938</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9050153388792506</v>
-      </c>
-      <c r="G38" t="n">
-        <v>7.050015049737664e-32</v>
+        <v>1.463243133224925e-82</v>
       </c>
     </row>
     <row r="39">
@@ -1400,19 +1284,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0005388038213686952</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1.516545682472353e-05</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.9994460307218066</v>
+        <v>1.340270747521398e-21</v>
       </c>
     </row>
     <row r="40">
@@ -1431,12 +1312,9 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.495612522761132e-26</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2.596358540080893e-31</v>
-      </c>
-      <c r="G40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1456,13 +1334,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9999006813955612</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>9.931839703670421e-05</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.074020662935571e-10</v>
+        <v>3.445779503539908e-68</v>
       </c>
     </row>
     <row r="42">
@@ -1481,13 +1356,10 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7499714127064112</v>
+        <v>0.9999999999999929</v>
       </c>
       <c r="F42" t="n">
-        <v>0.250026080215792</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.507077796712183e-06</v>
+        <v>7.127400455702353e-15</v>
       </c>
     </row>
     <row r="43">
@@ -1506,13 +1378,10 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9290654203917926</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.07092911285065778</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5.466757549642126e-06</v>
+        <v>3.992114239111314e-36</v>
       </c>
     </row>
     <row r="44">
@@ -1531,13 +1400,10 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6569798047148179</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3430201952851822</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.611510792553359e-35</v>
+        <v>7.5635896512696e-91</v>
       </c>
     </row>
     <row r="45">
@@ -1556,13 +1422,10 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9997693669121318</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0002306330878681958</v>
-      </c>
-      <c r="G45" t="n">
-        <v>8.811591974323307e-51</v>
+        <v>9.917885857891092e-134</v>
       </c>
     </row>
     <row r="46">
@@ -1581,13 +1444,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9952511476158195</v>
+        <v>0.9999999999999516</v>
       </c>
       <c r="F46" t="n">
-        <v>0.004475958960352145</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.0002728934238284575</v>
+        <v>4.845941584343292e-14</v>
       </c>
     </row>
     <row r="47">
@@ -1606,13 +1466,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9983108016548048</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.001689198344133037</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.062138385548015e-12</v>
+        <v>4.016722511916493e-55</v>
       </c>
     </row>
     <row r="48">
@@ -1631,13 +1488,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9108208495833645</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.08917915041663542</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.022888951985608e-38</v>
+        <v>6.018295009623318e-97</v>
       </c>
     </row>
     <row r="49">
@@ -1656,13 +1510,10 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9350327730969752</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.06496722690302491</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1.527786265356812e-30</v>
+        <v>1.609737819974522e-80</v>
       </c>
     </row>
     <row r="50">
@@ -1681,13 +1532,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9999360502509059</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>6.394974909314845e-05</v>
-      </c>
-      <c r="G50" t="n">
-        <v>9.561284120974118e-16</v>
+        <v>1.824192131242626e-74</v>
       </c>
     </row>
     <row r="51">
@@ -1706,13 +1554,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6229944085308912</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3770055914691088</v>
-      </c>
-      <c r="G51" t="n">
-        <v>9.907824469792886e-21</v>
+        <v>1.142336343209834e-68</v>
       </c>
     </row>
     <row r="52">
@@ -1731,13 +1576,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9944182469771469</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.005581753022853109</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.005702454277184e-27</v>
+        <v>3.030379149355854e-86</v>
       </c>
     </row>
     <row r="53">
@@ -1756,13 +1598,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9999133405720879</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>8.66594279122167e-05</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.059624237892311e-18</v>
+        <v>2.474341003465087e-79</v>
       </c>
     </row>
     <row r="54">
@@ -1781,13 +1620,10 @@
         <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>2.004943502035567e-14</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>3.322913471479718e-14</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.9999999999999467</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1806,13 +1642,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9564962365211082</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.04350376347889199</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3.032732997552055e-31</v>
+        <v>1.374047905883196e-73</v>
       </c>
     </row>
     <row r="56">
@@ -1831,13 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.638536766897436</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3614589038808997</v>
-      </c>
-      <c r="G56" t="n">
-        <v>4.329221664260327e-06</v>
+        <v>4.502973077607376e-24</v>
       </c>
     </row>
     <row r="57">
@@ -1856,13 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9979730436751713</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0.002026956324822479</v>
-      </c>
-      <c r="G57" t="n">
-        <v>6.512314248976573e-15</v>
+        <v>1.139766782156641e-54</v>
       </c>
     </row>
     <row r="58">
@@ -1881,13 +1708,10 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9195842620582673</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.08041573793860067</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3.131948992312367e-12</v>
+        <v>1.421536527508347e-53</v>
       </c>
     </row>
     <row r="59">
@@ -1906,13 +1730,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9922004723671815</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0077995276315212</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1.297101432264194e-12</v>
+        <v>2.660537023863921e-60</v>
       </c>
     </row>
     <row r="60">
@@ -1925,19 +1746,16 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>3.732099145639373e-05</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>3.250615407559886e-07</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.9999623539470027</v>
+        <v>7.744726967636735e-38</v>
       </c>
     </row>
     <row r="61">
@@ -1956,13 +1774,10 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9705459698079257</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.02945403019207438</v>
-      </c>
-      <c r="G61" t="n">
-        <v>9.484674457049457e-31</v>
+        <v>2.267464102385565e-74</v>
       </c>
     </row>
     <row r="62">
@@ -1975,19 +1790,16 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.295002152091984e-07</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1.366018203794167e-13</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.9999996704996481</v>
+        <v>5.451601255273687e-48</v>
       </c>
     </row>
     <row r="63">
@@ -2000,19 +1812,16 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0.08927038467129274</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1.261260288793052e-08</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.9107296027161044</v>
+        <v>2.944195105806111e-51</v>
       </c>
     </row>
     <row r="64">
@@ -2031,13 +1840,10 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8762125933602762</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1237874066397238</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3.408474282215384e-57</v>
+        <v>3.507205636231559e-108</v>
       </c>
     </row>
     <row r="65">
@@ -2056,13 +1862,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9999959937670201</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>4.006232979961294e-06</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1.576692438306417e-29</v>
+        <v>6.812005380082613e-94</v>
       </c>
     </row>
     <row r="66">
@@ -2081,13 +1884,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9875301449467805</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01240070546251824</v>
-      </c>
-      <c r="G66" t="n">
-        <v>6.91495907013125e-05</v>
+        <v>3.54337829728852e-23</v>
       </c>
     </row>
     <row r="67">
@@ -2106,13 +1906,10 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9999960554273716</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>3.944572628390219e-06</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2.864153847845084e-25</v>
+        <v>8.087946063832083e-76</v>
       </c>
     </row>
     <row r="68">
@@ -2131,13 +1928,10 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9999669789922229</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>3.302100777716364e-05</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1.930936588715053e-33</v>
+        <v>1.412275830284387e-84</v>
       </c>
     </row>
     <row r="69">
@@ -2156,13 +1950,10 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9999632945799031</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>3.670542009705244e-05</v>
-      </c>
-      <c r="G69" t="n">
-        <v>4.697481973403386e-33</v>
+        <v>2.021433089725943e-82</v>
       </c>
     </row>
     <row r="70">
@@ -2175,19 +1966,16 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0.002458855404762359</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9975411445952377</v>
-      </c>
-      <c r="G70" t="n">
-        <v>2.406250744078365e-46</v>
+        <v>2.416797698862943e-91</v>
       </c>
     </row>
     <row r="71">
@@ -2206,13 +1994,10 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9999987822540598</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1.217745940199271e-06</v>
-      </c>
-      <c r="G71" t="n">
-        <v>3.303265697648755e-22</v>
+        <v>3.014909642620987e-70</v>
       </c>
     </row>
     <row r="72">
@@ -2225,19 +2010,16 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002482543454250794</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.999751745654575</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8.488936488665015e-48</v>
+        <v>3.189313432433863e-71</v>
       </c>
     </row>
     <row r="73">
@@ -2256,13 +2038,10 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9999948139210582</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>5.125899779179261e-06</v>
-      </c>
-      <c r="G73" t="n">
-        <v>6.017916271040533e-08</v>
+        <v>5.738352245701207e-37</v>
       </c>
     </row>
     <row r="74">
@@ -2281,13 +2060,10 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9999449407018309</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>5.505929816906266e-05</v>
-      </c>
-      <c r="G74" t="n">
-        <v>6.833587995480438e-29</v>
+        <v>1.135034115623168e-76</v>
       </c>
     </row>
     <row r="75">
@@ -2300,19 +2076,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0.01098498864690647</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9890150113530936</v>
-      </c>
-      <c r="G75" t="n">
-        <v>5.66899518812121e-54</v>
+        <v>2.080075291104721e-94</v>
       </c>
     </row>
     <row r="76">
@@ -2325,19 +2098,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1442436633302083</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8557563366697917</v>
-      </c>
-      <c r="G76" t="n">
-        <v>7.023418906444119e-45</v>
+        <v>2.079882876375173e-57</v>
       </c>
     </row>
     <row r="77">
@@ -2356,13 +2126,10 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9999417445798559</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>5.825542014420381e-05</v>
-      </c>
-      <c r="G77" t="n">
-        <v>5.51696116189423e-35</v>
+        <v>7.533421482350176e-87</v>
       </c>
     </row>
     <row r="78">
@@ -2381,13 +2148,10 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9999717728844356</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>2.822711556440757e-05</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1.321304559678692e-34</v>
+        <v>1.303471074394248e-96</v>
       </c>
     </row>
     <row r="79">
@@ -2406,13 +2170,10 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9635710096324143</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.03642899036758569</v>
-      </c>
-      <c r="G79" t="n">
-        <v>3.410378636784788e-52</v>
+        <v>1.463626712271747e-96</v>
       </c>
     </row>
     <row r="80">
@@ -2431,13 +2192,10 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9908313495555527</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.009168650444447188</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2.073313315216523e-31</v>
+        <v>3.13591215436143e-98</v>
       </c>
     </row>
     <row r="81">
@@ -2456,13 +2214,10 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9999854122081221</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1.458779187791298e-05</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1.00696922245563e-22</v>
+        <v>3.992053037929373e-63</v>
       </c>
     </row>
     <row r="82">
@@ -2481,13 +2236,10 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.999966910781521</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>3.308921847890679e-05</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1.41010689307958e-30</v>
+        <v>4.206147316481281e-81</v>
       </c>
     </row>
     <row r="83">
@@ -2506,13 +2258,10 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9999696298656593</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>3.037013434060333e-05</v>
-      </c>
-      <c r="G83" t="n">
-        <v>4.065163661332865e-25</v>
+        <v>4.155202614111305e-77</v>
       </c>
     </row>
     <row r="84">
@@ -2531,13 +2280,10 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9998328595992477</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0001671404007521673</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1.120452697030819e-20</v>
+        <v>6.897706654690354e-36</v>
       </c>
     </row>
     <row r="85">
@@ -2556,13 +2302,10 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.999945265017957</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>5.473498204297656e-05</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1.684015033355128e-34</v>
+        <v>4.67089290898385e-81</v>
       </c>
     </row>
     <row r="86">
@@ -2581,13 +2324,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9963689107218756</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0.003630522840004884</v>
-      </c>
-      <c r="G86" t="n">
-        <v>5.664381195102757e-07</v>
+        <v>8.931750434423954e-41</v>
       </c>
     </row>
     <row r="87">
@@ -2606,13 +2346,10 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9999775486987587</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>2.245130124139129e-05</v>
-      </c>
-      <c r="G87" t="n">
-        <v>5.71619455600599e-18</v>
+        <v>5.725899408693859e-83</v>
       </c>
     </row>
     <row r="88">
@@ -2631,13 +2368,10 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9889930612421522</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0.01100693875784772</v>
-      </c>
-      <c r="G88" t="n">
-        <v>5.891602868157833e-38</v>
+        <v>7.227113632700376e-114</v>
       </c>
     </row>
     <row r="89">
@@ -2656,13 +2390,10 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9999320233050427</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>6.79766949572144e-05</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1.786640236678842e-20</v>
+        <v>4.407300399224881e-86</v>
       </c>
     </row>
     <row r="90">
@@ -2681,13 +2412,10 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9999057318964706</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>9.426805359779769e-05</v>
-      </c>
-      <c r="G90" t="n">
-        <v>4.99314744653177e-11</v>
+        <v>1.426504804317872e-64</v>
       </c>
     </row>
     <row r="91">
@@ -2706,13 +2434,10 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9997824195959727</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0002175804040099458</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1.723061962502887e-14</v>
+        <v>9.886212380755626e-51</v>
       </c>
     </row>
     <row r="92">
@@ -2725,19 +2450,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>9.922175724617697e-12</v>
+        <v>0.9814601522568263</v>
       </c>
       <c r="F92" t="n">
-        <v>1.720321286510475e-15</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0.9999999999900762</v>
+        <v>0.01853984774317377</v>
       </c>
     </row>
     <row r="93">
@@ -2756,13 +2478,10 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9999817585885391</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>1.824141146086042e-05</v>
-      </c>
-      <c r="G93" t="n">
-        <v>8.414690157788287e-20</v>
+        <v>1.546268431557672e-76</v>
       </c>
     </row>
     <row r="94">
@@ -2775,19 +2494,16 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>7.158030310885373e-09</v>
+        <v>0.9999999999999939</v>
       </c>
       <c r="F94" t="n">
-        <v>2.096809049643013e-13</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0.99999999284176</v>
+        <v>6.15922523110683e-15</v>
       </c>
     </row>
     <row r="95">
@@ -2800,19 +2516,16 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>0.008340321990449071</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>8.810204922876148e-07</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.9916587969890586</v>
+        <v>6.304919383656712e-34</v>
       </c>
     </row>
     <row r="96">
@@ -2831,13 +2544,10 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9989851142932532</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0.001014885706746842</v>
-      </c>
-      <c r="G96" t="n">
-        <v>3.57593542919148e-28</v>
+        <v>1.048337247348803e-76</v>
       </c>
     </row>
     <row r="97">
@@ -2850,19 +2560,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0003714143748977118</v>
+        <v>0.9999999999997959</v>
       </c>
       <c r="F97" t="n">
-        <v>5.76928097841936e-09</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0.9996285798558214</v>
+        <v>2.040144272109393e-13</v>
       </c>
     </row>
     <row r="98">
@@ -2875,19 +2582,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>4.438234330609455e-10</v>
+        <v>0.999729077464217</v>
       </c>
       <c r="F98" t="n">
-        <v>2.678640621388119e-14</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0.9999999995561497</v>
+        <v>0.0002709225357829525</v>
       </c>
     </row>
     <row r="99">
@@ -2906,13 +2610,10 @@
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>2.863426211223333e-17</v>
+        <v>3.869013528889909e-05</v>
       </c>
       <c r="F99" t="n">
-        <v>1.455850193617012e-21</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1</v>
+        <v>0.9999613098647111</v>
       </c>
     </row>
     <row r="100">
@@ -2931,13 +2632,10 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9999504570118481</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>4.954298815189554e-05</v>
-      </c>
-      <c r="G100" t="n">
-        <v>2.398769228291588e-21</v>
+        <v>2.626663797566259e-81</v>
       </c>
     </row>
     <row r="101">
@@ -2950,19 +2648,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1.678561179612068e-11</v>
+        <v>0.999999999999992</v>
       </c>
       <c r="F101" t="n">
-        <v>1.803643974750925e-18</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.9999999999832143</v>
+        <v>8.047373893192517e-15</v>
       </c>
     </row>
     <row r="102">
@@ -2981,13 +2676,10 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0.99994670333769</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>5.329666230993446e-05</v>
-      </c>
-      <c r="G102" t="n">
-        <v>9.850804292476601e-20</v>
+        <v>5.589050481825875e-37</v>
       </c>
     </row>
     <row r="103">
@@ -3006,13 +2698,10 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9998819610713157</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0001180389262787494</v>
-      </c>
-      <c r="G103" t="n">
-        <v>2.405642277144721e-12</v>
+        <v>2.420911351399018e-68</v>
       </c>
     </row>
     <row r="104">
@@ -3031,13 +2720,10 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9987424151626896</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0.001257584837310572</v>
-      </c>
-      <c r="G104" t="n">
-        <v>7.760326291667794e-26</v>
+        <v>2.075117379696439e-86</v>
       </c>
     </row>
     <row r="105">
@@ -3056,13 +2742,10 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8482686270221487</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1517313729778513</v>
-      </c>
-      <c r="G105" t="n">
-        <v>7.52560199499016e-24</v>
+        <v>3.248441693378059e-59</v>
       </c>
     </row>
     <row r="106">
@@ -3081,13 +2764,10 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9854785063521261</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0145214936478739</v>
-      </c>
-      <c r="G106" t="n">
-        <v>4.857068663952198e-48</v>
+        <v>3.709047647820681e-117</v>
       </c>
     </row>
     <row r="107">
@@ -3106,13 +2786,10 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>0.999872098475392</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0.000127901524607978</v>
-      </c>
-      <c r="G107" t="n">
-        <v>2.126624483654823e-20</v>
+        <v>2.116388502952834e-73</v>
       </c>
     </row>
     <row r="108">
@@ -3131,13 +2808,10 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9994453357909996</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0.000554664209000366</v>
-      </c>
-      <c r="G108" t="n">
-        <v>4.216516236110956e-28</v>
+        <v>3.055519321021086e-75</v>
       </c>
     </row>
     <row r="109">
@@ -3156,13 +2830,10 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9977202859796401</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0.002279714020359775</v>
-      </c>
-      <c r="G109" t="n">
-        <v>5.099772218030908e-17</v>
+        <v>2.99057134244601e-35</v>
       </c>
     </row>
     <row r="110">
@@ -3181,12 +2852,9 @@
         <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>7.870656135538957e-33</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>1.578478699517768e-35</v>
-      </c>
-      <c r="G110" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3206,13 +2874,10 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9947406791137487</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0.005259320886251244</v>
-      </c>
-      <c r="G111" t="n">
-        <v>7.587332497573636e-32</v>
+        <v>6.97422052506608e-86</v>
       </c>
     </row>
     <row r="112">
@@ -3231,13 +2896,10 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9863451403303135</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>0.01365485966968641</v>
-      </c>
-      <c r="G112" t="n">
-        <v>5.356982499517082e-30</v>
+        <v>2.679307310484173e-86</v>
       </c>
     </row>
     <row r="113">
@@ -3256,13 +2918,10 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9999386794079174</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>6.132059208263986e-05</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1.470221119072497e-22</v>
+        <v>1.060341644354227e-38</v>
       </c>
     </row>
     <row r="114">
@@ -3281,13 +2940,10 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8302587659044659</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1697412340955341</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1.2118754674781e-32</v>
+        <v>5.620455272212034e-61</v>
       </c>
     </row>
     <row r="115">
@@ -3306,13 +2962,10 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9998946443583365</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0001053552284476002</v>
-      </c>
-      <c r="G115" t="n">
-        <v>4.132159137837432e-10</v>
+        <v>4.273813700906526e-28</v>
       </c>
     </row>
     <row r="116">
@@ -3331,13 +2984,10 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9993870255902225</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0006129744097775943</v>
-      </c>
-      <c r="G116" t="n">
-        <v>2.627560919132533e-28</v>
+        <v>2.815419484678681e-70</v>
       </c>
     </row>
     <row r="117">
@@ -3356,13 +3006,10 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.8981323618924694</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1018676381075307</v>
-      </c>
-      <c r="G117" t="n">
-        <v>4.991825316075436e-27</v>
+        <v>5.085208884959161e-57</v>
       </c>
     </row>
     <row r="118">
@@ -3375,19 +3022,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0904790638313272</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0.9095209361686727</v>
-      </c>
-      <c r="G118" t="n">
-        <v>2.665458416715137e-42</v>
+        <v>3.600072384991597e-87</v>
       </c>
     </row>
     <row r="119">
@@ -3406,13 +3050,10 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9962667022678233</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0.003733297732176656</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2.589045718651061e-23</v>
+        <v>1.789013042099961e-73</v>
       </c>
     </row>
     <row r="120">
@@ -3431,13 +3072,10 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0.9984752108333114</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>0.001524789166688551</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1.154711976995953e-22</v>
+        <v>1.138224110583429e-57</v>
       </c>
     </row>
     <row r="121">
@@ -3456,12 +3094,9 @@
         <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>4.456802047971459e-22</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>7.704778265151464e-25</v>
-      </c>
-      <c r="G121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3481,13 +3116,10 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0.9926625636157923</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.007337436384207632</v>
-      </c>
-      <c r="G122" t="n">
-        <v>2.304299978866069e-30</v>
+        <v>4.875343748967822e-81</v>
       </c>
     </row>
     <row r="123">
@@ -3506,13 +3138,10 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>0.9994706978164697</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0005293021668323604</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1.669806604574665e-11</v>
+        <v>4.53856607586994e-53</v>
       </c>
     </row>
     <row r="124">
@@ -3531,13 +3160,10 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9989237210793824</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0.001076278920617657</v>
-      </c>
-      <c r="G124" t="n">
-        <v>5.282938634209598e-29</v>
+        <v>4.911152584426363e-76</v>
       </c>
     </row>
     <row r="125">
@@ -3556,13 +3182,10 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>0.9968396904306176</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0.003160309569382291</v>
-      </c>
-      <c r="G125" t="n">
-        <v>4.457879328874208e-28</v>
+        <v>8.269151808037446e-73</v>
       </c>
     </row>
     <row r="126">
@@ -3581,13 +3204,10 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0.9946201489338129</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0.005379851066187162</v>
-      </c>
-      <c r="G126" t="n">
-        <v>3.109979883142864e-18</v>
+        <v>8.946066934690704e-59</v>
       </c>
     </row>
     <row r="127">
@@ -3606,13 +3226,10 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>0.9995504256778375</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0004495694851761768</v>
-      </c>
-      <c r="G127" t="n">
-        <v>4.836986459412392e-09</v>
+        <v>2.686462246723118e-26</v>
       </c>
     </row>
     <row r="128">
@@ -3631,13 +3248,10 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>0.99975266101438</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0002473373246424556</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1.660977567300842e-09</v>
+        <v>6.306714917946874e-45</v>
       </c>
     </row>
     <row r="129">
@@ -3650,19 +3264,16 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>1.899576214836721e-14</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>4.628389982582935e-20</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.9999999999999809</v>
+        <v>1.97045043013422e-35</v>
       </c>
     </row>
     <row r="130">
@@ -3681,13 +3292,10 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.998093312200735</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>0.001906029443386023</v>
-      </c>
-      <c r="G130" t="n">
-        <v>6.583558788791796e-07</v>
+        <v>7.423595295947116e-26</v>
       </c>
     </row>
     <row r="131">
@@ -3706,13 +3314,10 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0.9971856557705454</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>0.002814344229454629</v>
-      </c>
-      <c r="G131" t="n">
-        <v>9.409291967695316e-35</v>
+        <v>2.691281359547506e-97</v>
       </c>
     </row>
     <row r="132">
@@ -3731,13 +3336,10 @@
         <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>3.884446486122541e-13</v>
+        <v>0.0008397513025389935</v>
       </c>
       <c r="F132" t="n">
-        <v>5.409269156614729e-18</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0.9999999999996116</v>
+        <v>0.999160248697461</v>
       </c>
     </row>
     <row r="133">
@@ -3756,13 +3358,10 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>0.9982473050442552</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>0.001752694955641257</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1.034615193599074e-13</v>
+        <v>1.084301738810881e-58</v>
       </c>
     </row>
     <row r="134">
@@ -3781,12 +3380,9 @@
         <v>3</v>
       </c>
       <c r="E134" t="n">
-        <v>2.892416773177278e-53</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>4.996417949562336e-60</v>
-      </c>
-      <c r="G134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3806,13 +3402,10 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.9997194443635227</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0002805556364773963</v>
-      </c>
-      <c r="G135" t="n">
-        <v>1.448860787081434e-25</v>
+        <v>1.868746677403937e-92</v>
       </c>
     </row>
     <row r="136">
@@ -3831,12 +3424,9 @@
         <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>1.945159048303669e-35</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>2.870909376751626e-40</v>
-      </c>
-      <c r="G136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3856,12 +3446,9 @@
         <v>3</v>
       </c>
       <c r="E137" t="n">
-        <v>2.674780488989943e-66</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>1.367217038306943e-71</v>
-      </c>
-      <c r="G137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3881,12 +3468,9 @@
         <v>3</v>
       </c>
       <c r="E138" t="n">
-        <v>8.156969462301038e-46</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>3.8777132516483e-53</v>
-      </c>
-      <c r="G138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3900,19 +3484,16 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>3.686232532778001e-09</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>6.40064993112299e-15</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0.9999999963137611</v>
+        <v>2.811082136612035e-33</v>
       </c>
     </row>
     <row r="140">
@@ -3931,12 +3512,9 @@
         <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>1.603148442798741e-27</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>3.920188830791756e-33</v>
-      </c>
-      <c r="G140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3950,19 +3528,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>1.792303109280076e-05</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>1.418460525361744e-07</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.9999819351228546</v>
+        <v>1.425531600778556e-46</v>
       </c>
     </row>
     <row r="142">
@@ -3981,12 +3556,9 @@
         <v>3</v>
       </c>
       <c r="E142" t="n">
-        <v>6.587654924963972e-63</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>1.794309607721464e-71</v>
-      </c>
-      <c r="G142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4006,12 +3578,9 @@
         <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>8.176920197762366e-57</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>3.324640954546813e-61</v>
-      </c>
-      <c r="G143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4031,13 +3600,10 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9284079747686683</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07159173726627974</v>
-      </c>
-      <c r="G144" t="n">
-        <v>2.879650520893045e-07</v>
+        <v>1.269769912977781e-20</v>
       </c>
     </row>
     <row r="145">
@@ -4050,19 +3616,16 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1.514671214912772e-08</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>7.888669458918179e-10</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0.9999999840644209</v>
+        <v>9.324389051253835e-36</v>
       </c>
     </row>
     <row r="146">
@@ -4081,13 +3644,10 @@
         <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>3.103533102536889e-12</v>
+        <v>0.01473584179931742</v>
       </c>
       <c r="F146" t="n">
-        <v>7.804244206114689e-17</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.9999999999968965</v>
+        <v>0.9852641582006826</v>
       </c>
     </row>
     <row r="147">
@@ -4106,12 +3666,9 @@
         <v>3</v>
       </c>
       <c r="E147" t="n">
-        <v>7.827422744916965e-29</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>1.645925330552953e-34</v>
-      </c>
-      <c r="G147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4131,12 +3688,9 @@
         <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>5.062908702487437e-40</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>3.227407029978285e-44</v>
-      </c>
-      <c r="G148" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4156,12 +3710,9 @@
         <v>3</v>
       </c>
       <c r="E149" t="n">
-        <v>6.992905335495158e-36</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>1.48176933966868e-41</v>
-      </c>
-      <c r="G149" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4175,19 +3726,16 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>5.752029423075814e-11</v>
+        <v>0.9999999999999887</v>
       </c>
       <c r="F150" t="n">
-        <v>1.051330019661266e-15</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.9999999999424787</v>
+        <v>1.130134306549867e-14</v>
       </c>
     </row>
     <row r="151">
@@ -4206,13 +3754,10 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>0.9979026860181356</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>0.002097313975193188</v>
-      </c>
-      <c r="G151" t="n">
-        <v>6.671052238618433e-12</v>
+        <v>3.035495895768416e-64</v>
       </c>
     </row>
     <row r="152">
@@ -4231,13 +3776,10 @@
         <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>1.397932342949231e-23</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="F152" t="n">
-        <v>9.606288143067756e-29</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
+        <v>0.9999999999999944</v>
       </c>
     </row>
     <row r="153">
@@ -4256,13 +3798,10 @@
         <v>3</v>
       </c>
       <c r="E153" t="n">
-        <v>1.241649939710985e-21</v>
+        <v>2.557509759526511e-12</v>
       </c>
       <c r="F153" t="n">
-        <v>3.245574328748688e-27</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
+        <v>0.9999999999974425</v>
       </c>
     </row>
     <row r="154">
@@ -4281,13 +3820,10 @@
         <v>3</v>
       </c>
       <c r="E154" t="n">
-        <v>3.46519847520965e-11</v>
+        <v>5.81756864903582e-13</v>
       </c>
       <c r="F154" t="n">
-        <v>1.861174104740867e-15</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.9999999999653462</v>
+        <v>0.9999999999994182</v>
       </c>
     </row>
     <row r="155">
@@ -4300,19 +3836,16 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>1.313856895574915e-12</v>
+        <v>0.9491043331273357</v>
       </c>
       <c r="F155" t="n">
-        <v>4.361707862449598e-19</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0.9999999999986862</v>
+        <v>0.05089566687266438</v>
       </c>
     </row>
     <row r="156">
@@ -4325,19 +3858,16 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1091261530161097</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8537364864318115</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.03713736055207868</v>
+        <v>2.432567358340005e-19</v>
       </c>
     </row>
     <row r="157">
@@ -4356,13 +3886,10 @@
         <v>3</v>
       </c>
       <c r="E157" t="n">
-        <v>7.620436187909726e-15</v>
+        <v>1.186430065303057e-09</v>
       </c>
       <c r="F157" t="n">
-        <v>5.840556397654362e-22</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0.9999999999999925</v>
+        <v>0.9999999988135699</v>
       </c>
     </row>
     <row r="158">
@@ -4381,13 +3908,10 @@
         <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>9.363939300424779e-24</v>
+        <v>2.322500225804269e-06</v>
       </c>
       <c r="F158" t="n">
-        <v>1.286779490700112e-30</v>
-      </c>
-      <c r="G158" t="n">
-        <v>1</v>
+        <v>0.9999976774997742</v>
       </c>
     </row>
     <row r="159">
@@ -4406,13 +3930,10 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0.9994273810221117</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0005726189066266033</v>
-      </c>
-      <c r="G159" t="n">
-        <v>7.126174937233559e-11</v>
+        <v>1.305817558997166e-23</v>
       </c>
     </row>
     <row r="160">
@@ -4425,19 +3946,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>8.753582209305526e-18</v>
+        <v>0.9999999999999838</v>
       </c>
       <c r="F160" t="n">
-        <v>7.68764749953448e-22</v>
-      </c>
-      <c r="G160" t="n">
-        <v>1</v>
+        <v>1.621461321839528e-14</v>
       </c>
     </row>
     <row r="161">
@@ -4456,13 +3974,10 @@
         <v>3</v>
       </c>
       <c r="E161" t="n">
-        <v>7.524559322128178e-06</v>
+        <v>4.099284806502457e-05</v>
       </c>
       <c r="F161" t="n">
-        <v>8.500023256826748e-09</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.9999924669406547</v>
+        <v>0.999959007151935</v>
       </c>
     </row>
     <row r="162">
@@ -4481,13 +3996,10 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.9999851000969864</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>1.485948349826435e-05</v>
-      </c>
-      <c r="G162" t="n">
-        <v>4.041951551779744e-08</v>
+        <v>1.054117232386011e-51</v>
       </c>
     </row>
     <row r="163">
@@ -4506,13 +4018,10 @@
         <v>3</v>
       </c>
       <c r="E163" t="n">
-        <v>8.334816257094361e-23</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F163" t="n">
-        <v>1.931386815251301e-25</v>
-      </c>
-      <c r="G163" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="164">
@@ -4525,19 +4034,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>5.342967907377972e-05</v>
+        <v>0.9999998446152031</v>
       </c>
       <c r="F164" t="n">
-        <v>2.892395573113681e-09</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.9999465674285306</v>
+        <v>1.553847969330774e-07</v>
       </c>
     </row>
     <row r="165">
@@ -4556,13 +4062,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>0.8704088668453721</v>
+        <v>0.999999748385011</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0001944975811842939</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.1293966355734435</v>
+        <v>2.516149889773066e-07</v>
       </c>
     </row>
     <row r="166">
@@ -4575,19 +4078,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>0.02815372051686455</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>1.584515690680049e-06</v>
-      </c>
-      <c r="G166" t="n">
-        <v>0.9718446949674447</v>
+        <v>1.489889563757671e-20</v>
       </c>
     </row>
     <row r="167">
@@ -4606,12 +4106,9 @@
         <v>3</v>
       </c>
       <c r="E167" t="n">
-        <v>6.277391314335143e-21</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>7.835706329093476e-24</v>
-      </c>
-      <c r="G167" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4631,13 +4128,10 @@
         <v>3</v>
       </c>
       <c r="E168" t="n">
-        <v>1.177449725891353e-14</v>
+        <v>2.869957604900719e-10</v>
       </c>
       <c r="F168" t="n">
-        <v>2.419425239247891e-18</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.9999999999999882</v>
+        <v>0.9999999997130042</v>
       </c>
     </row>
     <row r="169">
@@ -4650,19 +4144,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>0.172215447721334</v>
+        <v>1</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8277845522786659</v>
-      </c>
-      <c r="G169" t="n">
-        <v>1.29931904475297e-35</v>
+        <v>2.822229591265894e-77</v>
       </c>
     </row>
     <row r="170">
@@ -4681,13 +4172,10 @@
         <v>3</v>
       </c>
       <c r="E170" t="n">
-        <v>1.230366211360548e-16</v>
+        <v>5.022338100957313e-11</v>
       </c>
       <c r="F170" t="n">
-        <v>3.245304591470334e-20</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999497766</v>
       </c>
     </row>
     <row r="171">
@@ -4706,13 +4194,10 @@
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>0.99908297630243</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0009170233340248365</v>
-      </c>
-      <c r="G171" t="n">
-        <v>3.635450297770159e-10</v>
+        <v>2.737552937780181e-67</v>
       </c>
     </row>
     <row r="172">
@@ -4731,13 +4216,10 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.861290805132672</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>8.330692879644624e-05</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.1386258879385315</v>
+        <v>1.099719250925226e-17</v>
       </c>
     </row>
     <row r="173">
@@ -4750,19 +4232,16 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0003761675276060683</v>
+        <v>0.9999999999998967</v>
       </c>
       <c r="F173" t="n">
-        <v>1.937770785980285e-06</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.9996218947016079</v>
+        <v>1.03279172623032e-13</v>
       </c>
     </row>
     <row r="174">
@@ -4775,19 +4254,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>0.002409872894059108</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>6.54552369131632e-05</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0.9975246718690278</v>
+        <v>5.285550425442777e-21</v>
       </c>
     </row>
     <row r="175">
@@ -4806,13 +4282,10 @@
         <v>3</v>
       </c>
       <c r="E175" t="n">
-        <v>3.492154735004326e-23</v>
+        <v>5.221936882904288e-09</v>
       </c>
       <c r="F175" t="n">
-        <v>2.056305524972748e-27</v>
-      </c>
-      <c r="G175" t="n">
-        <v>1</v>
+        <v>0.9999999947780631</v>
       </c>
     </row>
     <row r="176">
@@ -4825,19 +4298,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>6.128073366687651e-13</v>
+        <v>0.9999999999998623</v>
       </c>
       <c r="F176" t="n">
-        <v>1.545037638558703e-16</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0.9999999999993869</v>
+        <v>1.37719891139067e-13</v>
       </c>
     </row>
     <row r="177">
@@ -4856,13 +4326,10 @@
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>0.9936063791507063</v>
+        <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>0.006393620817793746</v>
-      </c>
-      <c r="G177" t="n">
-        <v>3.149984621632717e-11</v>
+        <v>5.489985249430737e-57</v>
       </c>
     </row>
     <row r="178">
@@ -4875,19 +4342,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0001036251859386742</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="F178" t="n">
-        <v>4.071264304106994e-12</v>
-      </c>
-      <c r="G178" t="n">
-        <v>0.9998963748099902</v>
+        <v>5.215915498840885e-16</v>
       </c>
     </row>
     <row r="179">
@@ -4906,13 +4370,10 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>0.9280894592419763</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="F179" t="n">
-        <v>2.985017040282939e-05</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0.07188069058762095</v>
+        <v>6.210189895481204e-16</v>
       </c>
     </row>
     <row r="180">
@@ -4931,12 +4392,9 @@
         <v>3</v>
       </c>
       <c r="E180" t="n">
-        <v>1.596486065828927e-42</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>9.688750143493451e-51</v>
-      </c>
-      <c r="G180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4956,13 +4414,10 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>0.9996310380313496</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>0.0003689619686502433</v>
-      </c>
-      <c r="G181" t="n">
-        <v>2.210500928040214e-16</v>
+        <v>5.073173296138807e-56</v>
       </c>
     </row>
     <row r="182">
@@ -4975,19 +4430,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>0.003615855403871552</v>
+        <v>0.9999999999932476</v>
       </c>
       <c r="F182" t="n">
-        <v>1.828249048324477e-07</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0.9963839617712236</v>
+        <v>6.752414602997817e-12</v>
       </c>
     </row>
     <row r="183">
@@ -5000,19 +4452,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>1.214354562361737e-09</v>
+        <v>0.9996232942942751</v>
       </c>
       <c r="F183" t="n">
-        <v>1.717376865871008e-14</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.9999999987856283</v>
+        <v>0.0003767057057248544</v>
       </c>
     </row>
     <row r="184">
@@ -5025,19 +4474,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0.07044377238697187</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9295562276130281</v>
-      </c>
-      <c r="G184" t="n">
-        <v>2.174566288917771e-19</v>
+        <v>1.221430662086427e-67</v>
       </c>
     </row>
     <row r="185">
@@ -5050,19 +4496,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>4.61676328594808e-11</v>
+        <v>0.9999999999988174</v>
       </c>
       <c r="F185" t="n">
-        <v>2.107603360356048e-16</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0.9999999999538323</v>
+        <v>1.182582729386715e-12</v>
       </c>
     </row>
     <row r="186">
@@ -5075,19 +4518,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>3.137150263653287e-17</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>2.811252094735606e-22</v>
-      </c>
-      <c r="G186" t="n">
-        <v>1</v>
+        <v>2.038688593524277e-27</v>
       </c>
     </row>
     <row r="187">
@@ -5100,19 +4540,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>3.517813961156545e-05</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>1.014452830881122e-10</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0.9999648217589431</v>
+        <v>2.346121991954196e-29</v>
       </c>
     </row>
     <row r="188">
@@ -5125,19 +4562,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>1.014673624042187e-16</v>
+        <v>0.9999999999352089</v>
       </c>
       <c r="F188" t="n">
-        <v>7.81425476329462e-21</v>
-      </c>
-      <c r="G188" t="n">
-        <v>1</v>
+        <v>6.479105186463488e-11</v>
       </c>
     </row>
     <row r="189">
@@ -5156,12 +4590,9 @@
         <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>4.155098803469096e-35</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>2.52949084277402e-39</v>
-      </c>
-      <c r="G189" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5181,12 +4612,9 @@
         <v>3</v>
       </c>
       <c r="E190" t="n">
-        <v>3.427508792046227e-31</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>1.851043181526799e-34</v>
-      </c>
-      <c r="G190" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5206,13 +4634,10 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>0.9960586730750471</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>0.003941326924831311</v>
-      </c>
-      <c r="G191" t="n">
-        <v>1.213632096838554e-13</v>
+        <v>2.211854617653043e-24</v>
       </c>
     </row>
     <row r="192">
@@ -5231,13 +4656,10 @@
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>0.9964455835682403</v>
+        <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>0.003554416431759609</v>
-      </c>
-      <c r="G192" t="n">
-        <v>2.055349579375182e-32</v>
+        <v>3.907690364409713e-83</v>
       </c>
     </row>
     <row r="193">
@@ -5256,13 +4678,10 @@
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>0.9792939731397984</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
-        <v>0.02070602686020175</v>
-      </c>
-      <c r="G193" t="n">
-        <v>7.636074033959563e-37</v>
+        <v>3.278520096354075e-97</v>
       </c>
     </row>
     <row r="194">
@@ -5281,13 +4700,10 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.999407102821206</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0005928971787939031</v>
-      </c>
-      <c r="G194" t="n">
-        <v>6.511980881050138e-29</v>
+        <v>2.753948691442971e-66</v>
       </c>
     </row>
     <row r="195">
@@ -5306,13 +4722,10 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.9141361465791881</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>0.08586385342081193</v>
-      </c>
-      <c r="G195" t="n">
-        <v>3.308392945809581e-43</v>
+        <v>1.381377642058521e-78</v>
       </c>
     </row>
     <row r="196">
@@ -5331,13 +4744,10 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.9962693186222243</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>7.445219828720182e-06</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0.003723236157946741</v>
+        <v>2.487796485270032e-23</v>
       </c>
     </row>
     <row r="197">
@@ -5356,12 +4766,9 @@
         <v>3</v>
       </c>
       <c r="E197" t="n">
-        <v>2.124234677395084e-34</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>1.106606378344374e-38</v>
-      </c>
-      <c r="G197" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5381,13 +4788,10 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.829472558284012</v>
+        <v>1</v>
       </c>
       <c r="F198" t="n">
-        <v>0.170527441715988</v>
-      </c>
-      <c r="G198" t="n">
-        <v>8.234967928428704e-26</v>
+        <v>2.565233740796401e-94</v>
       </c>
     </row>
     <row r="199">
@@ -5406,13 +4810,10 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>0.8662191333346366</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>0.1337808666653633</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1.113353498248052e-39</v>
+        <v>3.48628969860672e-109</v>
       </c>
     </row>
     <row r="200">
@@ -5431,13 +4832,10 @@
         <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.9997865654786324</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>0.000213434521367667</v>
-      </c>
-      <c r="G200" t="n">
-        <v>1.578328539596711e-18</v>
+        <v>2.151762096433536e-66</v>
       </c>
     </row>
     <row r="201">
@@ -5450,19 +4848,16 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.9386343260964012</v>
+        <v>1</v>
       </c>
       <c r="F201" t="n">
-        <v>0.06136567390359882</v>
-      </c>
-      <c r="G201" t="n">
-        <v>2.843174666881501e-31</v>
+        <v>6.713620566580402e-76</v>
       </c>
     </row>
     <row r="202">
@@ -5481,13 +4876,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.9821549923608862</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>8.202373494953408e-05</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0.01776298390416427</v>
+        <v>1.665801618772482e-18</v>
       </c>
     </row>
     <row r="203">
@@ -5506,13 +4898,10 @@
         <v>3</v>
       </c>
       <c r="E203" t="n">
-        <v>1.178100880455004e-14</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>9.306263433931688e-19</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0.9999999999999882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -5531,13 +4920,10 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>0.9787621031044127</v>
+        <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>0.02123789689542238</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1.648968693469638e-13</v>
+        <v>6.31106971379135e-36</v>
       </c>
     </row>
     <row r="205">
@@ -5556,13 +4942,10 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>0.9933904297553344</v>
+        <v>1</v>
       </c>
       <c r="F205" t="n">
-        <v>0.00660957024466557</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1.719768407769154e-18</v>
+        <v>6.186732219326921e-88</v>
       </c>
     </row>
     <row r="206">
@@ -5578,16 +4961,13 @@
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>1.015638210643479e-07</v>
+        <v>1</v>
       </c>
       <c r="F206" t="n">
-        <v>6.221921825830707e-11</v>
-      </c>
-      <c r="G206" t="n">
-        <v>0.9999998983739596</v>
+        <v>5.886533146129404e-33</v>
       </c>
     </row>
     <row r="207">
@@ -5600,19 +4980,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0.01278511794368981</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>7.22200598869848e-07</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0.9872141598557113</v>
+        <v>2.281351913552158e-52</v>
       </c>
     </row>
     <row r="208">
@@ -5625,19 +5002,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>0.1487337389709831</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
-        <v>0.8512662610290168</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1.818516605447594e-17</v>
+        <v>9.302093280710014e-93</v>
       </c>
     </row>
     <row r="209">
@@ -5656,13 +5030,10 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>0.9440503020679697</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>6.865795848592631e-05</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0.05588103997354437</v>
+        <v>8.612292478415106e-24</v>
       </c>
     </row>
     <row r="210">
@@ -5681,13 +5052,10 @@
         <v>3</v>
       </c>
       <c r="E210" t="n">
-        <v>2.459713651521691e-17</v>
+        <v>0.2703774588591723</v>
       </c>
       <c r="F210" t="n">
-        <v>1.855782281965734e-20</v>
-      </c>
-      <c r="G210" t="n">
-        <v>1</v>
+        <v>0.7296225411408277</v>
       </c>
     </row>
     <row r="211">
@@ -5700,19 +5068,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>2.390248872779615e-08</v>
+        <v>0.9999999999604896</v>
       </c>
       <c r="F211" t="n">
-        <v>1.027049572362561e-14</v>
-      </c>
-      <c r="G211" t="n">
-        <v>0.999999976097501</v>
+        <v>3.95104160218467e-11</v>
       </c>
     </row>
     <row r="212">
@@ -5725,19 +5090,16 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D212" t="n">
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>0.9932125113745492</v>
+        <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>0.006787488625450535</v>
-      </c>
-      <c r="G212" t="n">
-        <v>2.805908824159893e-16</v>
+        <v>1.108468348357597e-69</v>
       </c>
     </row>
     <row r="213">
@@ -5756,13 +5118,10 @@
         <v>3</v>
       </c>
       <c r="E213" t="n">
-        <v>5.205298818720101e-10</v>
+        <v>3.70345310498621e-05</v>
       </c>
       <c r="F213" t="n">
-        <v>1.440257984345567e-14</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0.9999999994794557</v>
+        <v>0.9999629654689501</v>
       </c>
     </row>
     <row r="214">
@@ -5781,13 +5140,10 @@
         <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>0.9998813272691779</v>
+        <v>1</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0001133592887608296</v>
-      </c>
-      <c r="G214" t="n">
-        <v>5.313442061309378e-06</v>
+        <v>2.796477770378162e-24</v>
       </c>
     </row>
     <row r="215">
@@ -5806,13 +5162,10 @@
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>0.9966707043391699</v>
+        <v>1</v>
       </c>
       <c r="F215" t="n">
-        <v>0.003329295660829935</v>
-      </c>
-      <c r="G215" t="n">
-        <v>6.479673633601073e-22</v>
+        <v>5.449189912517303e-48</v>
       </c>
     </row>
     <row r="216">
@@ -5831,13 +5184,10 @@
         <v>3</v>
       </c>
       <c r="E216" t="n">
-        <v>6.652417957940076e-15</v>
+        <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>7.374416576838135e-20</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.9999999999999933</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -5856,13 +5206,10 @@
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>0.9963995412247291</v>
+        <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>0.0036004586531497</v>
-      </c>
-      <c r="G217" t="n">
-        <v>1.22121287104827e-10</v>
+        <v>1.692060713411116e-65</v>
       </c>
     </row>
     <row r="218">
@@ -5881,13 +5228,10 @@
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>0.9996184025070135</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>0.0003760239111856786</v>
-      </c>
-      <c r="G218" t="n">
-        <v>5.573581800820326e-06</v>
+        <v>1.358366446136724e-23</v>
       </c>
     </row>
     <row r="219">
@@ -5906,13 +5250,10 @@
         <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>0.9997723344099404</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>0.0002276460918833892</v>
-      </c>
-      <c r="G219" t="n">
-        <v>1.949817624198253e-08</v>
+        <v>7.550778079001156e-66</v>
       </c>
     </row>
     <row r="220">
@@ -5925,19 +5266,16 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>1.353933363738241e-11</v>
+        <v>0.9999998870675341</v>
       </c>
       <c r="F220" t="n">
-        <v>5.613169476204184e-17</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0.9999999999864606</v>
+        <v>1.129324659681379e-07</v>
       </c>
     </row>
     <row r="221">
@@ -5956,12 +5294,9 @@
         <v>3</v>
       </c>
       <c r="E221" t="n">
-        <v>2.051112895143067e-36</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>6.261604756359285e-42</v>
-      </c>
-      <c r="G221" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5981,13 +5316,10 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>0.9998277688142136</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0001719285089474133</v>
-      </c>
-      <c r="G222" t="n">
-        <v>3.026768390207801e-07</v>
+        <v>5.996224738311571e-28</v>
       </c>
     </row>
     <row r="223">
@@ -6006,13 +5338,10 @@
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5564807001718851</v>
+        <v>1</v>
       </c>
       <c r="F223" t="n">
-        <v>0.4435192998281149</v>
-      </c>
-      <c r="G223" t="n">
-        <v>4.801381504122917e-34</v>
+        <v>2.277952280292786e-83</v>
       </c>
     </row>
     <row r="224">
@@ -6031,13 +5360,10 @@
         <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>0.9927384464683222</v>
+        <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>0.007261553531677714</v>
-      </c>
-      <c r="G224" t="n">
-        <v>5.722586475372274e-39</v>
+        <v>6.07737193615386e-89</v>
       </c>
     </row>
     <row r="225">
@@ -6056,13 +5382,10 @@
         <v>1</v>
       </c>
       <c r="E225" t="n">
-        <v>0.9979941495470832</v>
+        <v>1</v>
       </c>
       <c r="F225" t="n">
-        <v>0.002005850452916702</v>
-      </c>
-      <c r="G225" t="n">
-        <v>8.98422224087827e-27</v>
+        <v>4.78266549028381e-76</v>
       </c>
     </row>
     <row r="226">
@@ -6072,22 +5395,19 @@
         </is>
       </c>
       <c r="B226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" t="n">
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8144072128536445</v>
+        <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>0.1855927871463556</v>
-      </c>
-      <c r="G226" t="n">
-        <v>2.750203486991994e-22</v>
+        <v>4.076907601834036e-63</v>
       </c>
     </row>
     <row r="227">
@@ -6106,12 +5426,9 @@
         <v>3</v>
       </c>
       <c r="E227" t="n">
-        <v>1.384935410666222e-18</v>
+        <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>7.699292622681426e-24</v>
-      </c>
-      <c r="G227" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6131,13 +5448,10 @@
         <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>0.9994141993509844</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0005858006490154728</v>
-      </c>
-      <c r="G228" t="n">
-        <v>1.04066055875601e-28</v>
+        <v>2.443547167939101e-80</v>
       </c>
     </row>
     <row r="229">
@@ -6156,12 +5470,9 @@
         <v>3</v>
       </c>
       <c r="E229" t="n">
-        <v>5.844785858942106e-30</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>2.679198177281848e-33</v>
-      </c>
-      <c r="G229" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6181,13 +5492,10 @@
         <v>3</v>
       </c>
       <c r="E230" t="n">
-        <v>7.469342326656154e-13</v>
+        <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>2.998350931058425e-17</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0.999999999999253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -6203,16 +5511,13 @@
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231" t="n">
-        <v>0.2686349931789204</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
-        <v>0.7313650068210796</v>
-      </c>
-      <c r="G231" t="n">
-        <v>3.95524463373581e-32</v>
+        <v>1.869532087778915e-87</v>
       </c>
     </row>
     <row r="232">
@@ -6231,13 +5536,10 @@
         <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>0.9698788191598549</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>0.03012118084014518</v>
-      </c>
-      <c r="G232" t="n">
-        <v>6.579138042772044e-27</v>
+        <v>1.209104784598425e-72</v>
       </c>
     </row>
     <row r="233">
@@ -6256,13 +5558,10 @@
         <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>0.8893480618340152</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1106519381659848</v>
-      </c>
-      <c r="G233" t="n">
-        <v>1.919912913185403e-31</v>
+        <v>5.380220299741286e-72</v>
       </c>
     </row>
     <row r="234">
@@ -6281,12 +5580,9 @@
         <v>3</v>
       </c>
       <c r="E234" t="n">
-        <v>6.171165691474373e-25</v>
+        <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>2.204585651314021e-29</v>
-      </c>
-      <c r="G234" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6306,13 +5602,10 @@
         <v>1</v>
       </c>
       <c r="E235" t="n">
-        <v>0.7828238470897687</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>0.2171761529102314</v>
-      </c>
-      <c r="G235" t="n">
-        <v>8.852378618564675e-38</v>
+        <v>1.140863131935348e-90</v>
       </c>
     </row>
     <row r="236">
@@ -6331,12 +5624,9 @@
         <v>3</v>
       </c>
       <c r="E236" t="n">
-        <v>6.514406329158804e-32</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>1.008193000469149e-36</v>
-      </c>
-      <c r="G236" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6356,13 +5646,10 @@
         <v>1</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9324216841645221</v>
+        <v>1</v>
       </c>
       <c r="F237" t="n">
-        <v>0.06757831583547791</v>
-      </c>
-      <c r="G237" t="n">
-        <v>1.750332447628084e-22</v>
+        <v>5.17416097708262e-57</v>
       </c>
     </row>
     <row r="238">
@@ -6381,13 +5668,10 @@
         <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9079011008008311</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>0.09209889919916886</v>
-      </c>
-      <c r="G238" t="n">
-        <v>3.841795911905917e-25</v>
+        <v>4.032958337046771e-63</v>
       </c>
     </row>
     <row r="239">
@@ -6406,13 +5690,10 @@
         <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9812250301269169</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>0.01877496987174898</v>
-      </c>
-      <c r="G239" t="n">
-        <v>1.334128842077602e-12</v>
+        <v>3.770049886913116e-70</v>
       </c>
     </row>
     <row r="240">
@@ -6431,13 +5712,10 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9976631683622095</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>0.002336831637790527</v>
-      </c>
-      <c r="G240" t="n">
-        <v>5.604936139623648e-31</v>
+        <v>2.537588020841055e-65</v>
       </c>
     </row>
     <row r="241">
@@ -6456,13 +5734,10 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9965227762286866</v>
+        <v>1</v>
       </c>
       <c r="F241" t="n">
-        <v>0.003477223771313482</v>
-      </c>
-      <c r="G241" t="n">
-        <v>5.535327606021869e-35</v>
+        <v>2.941772218398596e-88</v>
       </c>
     </row>
     <row r="242">
@@ -6481,13 +5756,10 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9999942000004347</v>
+        <v>1</v>
       </c>
       <c r="F242" t="n">
-        <v>5.799999565323212e-06</v>
-      </c>
-      <c r="G242" t="n">
-        <v>6.17960879420007e-56</v>
+        <v>5.742403049017179e-117</v>
       </c>
     </row>
     <row r="243">
@@ -6506,13 +5778,10 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9908467521783334</v>
+        <v>1</v>
       </c>
       <c r="F243" t="n">
-        <v>0.009153247821666674</v>
-      </c>
-      <c r="G243" t="n">
-        <v>5.439767626469993e-44</v>
+        <v>4.359492981552906e-100</v>
       </c>
     </row>
     <row r="244">
@@ -6531,13 +5800,10 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9898059896370828</v>
+        <v>1</v>
       </c>
       <c r="F244" t="n">
-        <v>0.01019401036291718</v>
-      </c>
-      <c r="G244" t="n">
-        <v>1.630885507967255e-27</v>
+        <v>2.900933325723693e-67</v>
       </c>
     </row>
     <row r="245">
@@ -6556,13 +5822,10 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.9999271265097378</v>
+        <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>7.287325626063288e-05</v>
-      </c>
-      <c r="G245" t="n">
-        <v>2.340014843627983e-10</v>
+        <v>2.59856089872457e-60</v>
       </c>
     </row>
     <row r="246">
@@ -6581,13 +5844,10 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.9999468217984029</v>
+        <v>1</v>
       </c>
       <c r="F246" t="n">
-        <v>5.317820159724976e-05</v>
-      </c>
-      <c r="G246" t="n">
-        <v>2.156390026592585e-39</v>
+        <v>5.749436212529882e-88</v>
       </c>
     </row>
     <row r="247">
@@ -6606,13 +5866,10 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.9999767168786988</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>2.32831212574836e-05</v>
-      </c>
-      <c r="G247" t="n">
-        <v>4.370191390194611e-14</v>
+        <v>1.265753830306269e-66</v>
       </c>
     </row>
     <row r="248">
@@ -6631,13 +5888,10 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.9522342373844825</v>
+        <v>1</v>
       </c>
       <c r="F248" t="n">
-        <v>0.04776576261551745</v>
-      </c>
-      <c r="G248" t="n">
-        <v>1.07735987957441e-28</v>
+        <v>5.501779502428273e-67</v>
       </c>
     </row>
     <row r="249">
@@ -6656,13 +5910,10 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>0.9914373619450524</v>
+        <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>0.008562638054947593</v>
-      </c>
-      <c r="G249" t="n">
-        <v>1.869073835460701e-36</v>
+        <v>9.470995508867851e-91</v>
       </c>
     </row>
     <row r="250">
@@ -6681,13 +5932,10 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.9931130852752955</v>
+        <v>1</v>
       </c>
       <c r="F250" t="n">
-        <v>0.006886914724704428</v>
-      </c>
-      <c r="G250" t="n">
-        <v>1.764600210286172e-36</v>
+        <v>1.70723894154804e-86</v>
       </c>
     </row>
     <row r="251">
@@ -6706,13 +5954,10 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9922950453301113</v>
+        <v>1</v>
       </c>
       <c r="F251" t="n">
-        <v>0.007704954669888721</v>
-      </c>
-      <c r="G251" t="n">
-        <v>3.726178815735047e-40</v>
+        <v>3.304719503168349e-91</v>
       </c>
     </row>
     <row r="252">
@@ -6731,13 +5976,10 @@
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9916268338029839</v>
+        <v>1</v>
       </c>
       <c r="F252" t="n">
-        <v>0.008373166197016214</v>
-      </c>
-      <c r="G252" t="n">
-        <v>2.604814110555107e-32</v>
+        <v>2.267479240546902e-86</v>
       </c>
     </row>
     <row r="253">
@@ -6750,19 +5992,16 @@
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D253" t="n">
         <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9220594925296278</v>
+        <v>1</v>
       </c>
       <c r="F253" t="n">
-        <v>0.0779405074703723</v>
-      </c>
-      <c r="G253" t="n">
-        <v>9.649062903675408e-23</v>
+        <v>2.834082512345294e-58</v>
       </c>
     </row>
     <row r="254">
@@ -6775,19 +6014,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.09251859979419982</v>
+        <v>1</v>
       </c>
       <c r="F254" t="n">
-        <v>0.9074814002058003</v>
-      </c>
-      <c r="G254" t="n">
-        <v>8.472149642891397e-32</v>
+        <v>7.933372119766671e-95</v>
       </c>
     </row>
     <row r="255">
@@ -6800,19 +6036,16 @@
         <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.01479058136081872</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>0.9852094186391813</v>
-      </c>
-      <c r="G255" t="n">
-        <v>1.450400060345938e-36</v>
+        <v>8.575499320278659e-102</v>
       </c>
     </row>
     <row r="256">
@@ -6822,7 +6055,7 @@
         </is>
       </c>
       <c r="B256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
         <v>1</v>
@@ -6831,13 +6064,10 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9941010473697466</v>
+        <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>0.005898952630253456</v>
-      </c>
-      <c r="G256" t="n">
-        <v>3.61365446238452e-30</v>
+        <v>2.425383938116322e-90</v>
       </c>
     </row>
     <row r="257">
@@ -6856,13 +6086,10 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.9897240153167656</v>
+        <v>1</v>
       </c>
       <c r="F257" t="n">
-        <v>0.0102759846832343</v>
-      </c>
-      <c r="G257" t="n">
-        <v>8.710887820178603e-38</v>
+        <v>3.510176511334091e-104</v>
       </c>
     </row>
     <row r="258">
@@ -6872,22 +6099,19 @@
         </is>
       </c>
       <c r="B258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C258" t="n">
         <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.002702766393568608</v>
+        <v>1</v>
       </c>
       <c r="F258" t="n">
-        <v>0.9972972336064313</v>
-      </c>
-      <c r="G258" t="n">
-        <v>4.339816498880127e-31</v>
+        <v>1.93058035986702e-85</v>
       </c>
     </row>
     <row r="259">
@@ -6906,13 +6130,10 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9357212790306125</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>0.06427872096938736</v>
-      </c>
-      <c r="G259" t="n">
-        <v>4.905847598017339e-34</v>
+        <v>8.854184754393649e-100</v>
       </c>
     </row>
     <row r="260">
@@ -6931,13 +6152,10 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9745651838538226</v>
+        <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>0.0254348161461774</v>
-      </c>
-      <c r="G260" t="n">
-        <v>1.162812383077263e-41</v>
+        <v>1.820379205468295e-112</v>
       </c>
     </row>
     <row r="261">
@@ -6950,19 +6168,16 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0.4568239273715173</v>
+        <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>0.5431760726284827</v>
-      </c>
-      <c r="G261" t="n">
-        <v>1.309516386554037e-33</v>
+        <v>9.637882825216031e-102</v>
       </c>
     </row>
     <row r="262">
@@ -6975,19 +6190,16 @@
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0.4592790459374463</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>0.5407209540625536</v>
-      </c>
-      <c r="G262" t="n">
-        <v>3.674673083795742e-31</v>
+        <v>3.044787926154247e-81</v>
       </c>
     </row>
     <row r="263">
@@ -7006,13 +6218,10 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0.6424133429665312</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>0.3575866570334688</v>
-      </c>
-      <c r="G263" t="n">
-        <v>2.381993386855221e-22</v>
+        <v>3.605067691707584e-83</v>
       </c>
     </row>
     <row r="264">
@@ -7031,13 +6240,10 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.99984739406044</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>0.000152605939559959</v>
-      </c>
-      <c r="G264" t="n">
-        <v>1.915011386973616e-23</v>
+        <v>3.912465311272506e-76</v>
       </c>
     </row>
     <row r="265">
@@ -7056,13 +6262,10 @@
         <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0.9860409183750889</v>
+        <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>0.01395908162491114</v>
-      </c>
-      <c r="G265" t="n">
-        <v>3.444560014487434e-30</v>
+        <v>1.321885958360466e-79</v>
       </c>
     </row>
     <row r="266">
@@ -7081,13 +6284,10 @@
         <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0.995909569682116</v>
+        <v>1</v>
       </c>
       <c r="F266" t="n">
-        <v>0.004090430317884105</v>
-      </c>
-      <c r="G266" t="n">
-        <v>1.370873129315487e-38</v>
+        <v>1.795703671174096e-87</v>
       </c>
     </row>
     <row r="267">
@@ -7106,13 +6306,10 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.8794134971166455</v>
+        <v>1</v>
       </c>
       <c r="F267" t="n">
-        <v>0.1205865028833544</v>
-      </c>
-      <c r="G267" t="n">
-        <v>5.774297498596669e-30</v>
+        <v>1.343373760199249e-80</v>
       </c>
     </row>
     <row r="268">
@@ -7131,13 +6328,10 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.9858915970996538</v>
+        <v>1</v>
       </c>
       <c r="F268" t="n">
-        <v>0.01410840290034625</v>
-      </c>
-      <c r="G268" t="n">
-        <v>2.858856496962257e-31</v>
+        <v>1.621627684530572e-82</v>
       </c>
     </row>
     <row r="269">
@@ -7156,13 +6350,10 @@
         <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.9330663222691633</v>
+        <v>1</v>
       </c>
       <c r="F269" t="n">
-        <v>0.06693367773083669</v>
-      </c>
-      <c r="G269" t="n">
-        <v>8.105350641213544e-28</v>
+        <v>3.536021665922123e-81</v>
       </c>
     </row>
     <row r="270">
@@ -7181,13 +6372,10 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0.9308528032707329</v>
+        <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>0.06914719672926693</v>
-      </c>
-      <c r="G270" t="n">
-        <v>2.31658204927648e-24</v>
+        <v>3.640943162817839e-77</v>
       </c>
     </row>
     <row r="271">
@@ -7206,13 +6394,10 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.996569074032493</v>
+        <v>1</v>
       </c>
       <c r="F271" t="n">
-        <v>0.003430925965550857</v>
-      </c>
-      <c r="G271" t="n">
-        <v>1.956122925593641e-12</v>
+        <v>1.443907239692218e-49</v>
       </c>
     </row>
     <row r="272">
@@ -7231,13 +6416,10 @@
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0.6499774665280567</v>
+        <v>1</v>
       </c>
       <c r="F272" t="n">
-        <v>0.3500225334719434</v>
-      </c>
-      <c r="G272" t="n">
-        <v>4.664395687976026e-43</v>
+        <v>3.395024674866315e-120</v>
       </c>
     </row>
     <row r="273">
@@ -7256,13 +6438,10 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.5110027174231291</v>
+        <v>1</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4889972825768709</v>
-      </c>
-      <c r="G273" t="n">
-        <v>2.338510623573212e-26</v>
+        <v>3.720676233907525e-81</v>
       </c>
     </row>
     <row r="274">
@@ -7272,22 +6451,19 @@
         </is>
       </c>
       <c r="B274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>0.03047746694880172</v>
+        <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>0.9695225330511983</v>
-      </c>
-      <c r="G274" t="n">
-        <v>1.013467356756302e-42</v>
+        <v>8.181046080867267e-125</v>
       </c>
     </row>
     <row r="275">
@@ -7297,22 +6473,19 @@
         </is>
       </c>
       <c r="B275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
         <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>0.7450118025908699</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>0.2549881974091301</v>
-      </c>
-      <c r="G275" t="n">
-        <v>3.004095904865443e-42</v>
+        <v>2.211668721742538e-124</v>
       </c>
     </row>
     <row r="276">
@@ -7331,13 +6504,10 @@
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.7795467064058303</v>
+        <v>1</v>
       </c>
       <c r="F276" t="n">
-        <v>0.2204532935941697</v>
-      </c>
-      <c r="G276" t="n">
-        <v>1.093809530675285e-34</v>
+        <v>3.313970069565536e-111</v>
       </c>
     </row>
     <row r="277">
@@ -7356,13 +6526,10 @@
         <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0.8923791214937214</v>
+        <v>1</v>
       </c>
       <c r="F277" t="n">
-        <v>0.1076208785062787</v>
-      </c>
-      <c r="G277" t="n">
-        <v>7.530125204966352e-18</v>
+        <v>2.871306364170116e-70</v>
       </c>
     </row>
     <row r="278">
@@ -7381,13 +6548,10 @@
         <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>0.9796126272352909</v>
+        <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>0.02005970697903846</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0.00032766578567086</v>
+        <v>3.697905730434467e-27</v>
       </c>
     </row>
     <row r="279">
@@ -7406,12 +6570,9 @@
         <v>3</v>
       </c>
       <c r="E279" t="n">
-        <v>2.294369900964399e-31</v>
+        <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>3.686096110036996e-35</v>
-      </c>
-      <c r="G279" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7431,13 +6592,10 @@
         <v>1</v>
       </c>
       <c r="E280" t="n">
-        <v>0.994740692737531</v>
+        <v>1</v>
       </c>
       <c r="F280" t="n">
-        <v>0.00525930726246916</v>
-      </c>
-      <c r="G280" t="n">
-        <v>3.542956477287938e-36</v>
+        <v>2.148451556055198e-86</v>
       </c>
     </row>
     <row r="281">
@@ -7456,13 +6614,10 @@
         <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>0.6569797564650154</v>
+        <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>0.3430202435349846</v>
-      </c>
-      <c r="G281" t="n">
-        <v>2.192273221090858e-38</v>
+        <v>2.600747995354838e-94</v>
       </c>
     </row>
     <row r="282">
@@ -7481,13 +6636,10 @@
         <v>1</v>
       </c>
       <c r="E282" t="n">
-        <v>0.8522487360710671</v>
+        <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>0.147751263928933</v>
-      </c>
-      <c r="G282" t="n">
-        <v>7.383350965450501e-42</v>
+        <v>1.653234063907241e-114</v>
       </c>
     </row>
     <row r="283">
@@ -7506,13 +6658,10 @@
         <v>1</v>
       </c>
       <c r="E283" t="n">
-        <v>0.9695368636876834</v>
+        <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>0.0304631363123167</v>
-      </c>
-      <c r="G283" t="n">
-        <v>3.238116375935817e-31</v>
+        <v>4.684503877960972e-91</v>
       </c>
     </row>
     <row r="284">
@@ -7525,19 +6674,16 @@
         <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D284" t="n">
         <v>1</v>
       </c>
       <c r="E284" t="n">
-        <v>0.918986457535833</v>
+        <v>1</v>
       </c>
       <c r="F284" t="n">
-        <v>0.08101354246416707</v>
-      </c>
-      <c r="G284" t="n">
-        <v>2.956104273265506e-36</v>
+        <v>1.084152831942607e-94</v>
       </c>
     </row>
     <row r="285">
@@ -7550,19 +6696,16 @@
         <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D285" t="n">
         <v>1</v>
       </c>
       <c r="E285" t="n">
-        <v>0.5999093527367141</v>
+        <v>1</v>
       </c>
       <c r="F285" t="n">
-        <v>0.400090647263286</v>
-      </c>
-      <c r="G285" t="n">
-        <v>1.605442850051178e-31</v>
+        <v>1.644487284740848e-75</v>
       </c>
     </row>
     <row r="286">
@@ -7578,16 +6721,13 @@
         <v>2</v>
       </c>
       <c r="D286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>0.399678313547528</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>0.600321686452472</v>
-      </c>
-      <c r="G286" t="n">
-        <v>3.237111742680726e-33</v>
+        <v>4.975011334829153e-74</v>
       </c>
     </row>
     <row r="287">
@@ -7600,19 +6740,16 @@
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D287" t="n">
         <v>1</v>
       </c>
       <c r="E287" t="n">
-        <v>0.8870339748969177</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
-        <v>0.1129660251030822</v>
-      </c>
-      <c r="G287" t="n">
-        <v>1.845510896678766e-28</v>
+        <v>3.805514365852717e-84</v>
       </c>
     </row>
     <row r="288">
@@ -7631,13 +6768,10 @@
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>0.9248742784189371</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>0.07512572158106286</v>
-      </c>
-      <c r="G288" t="n">
-        <v>2.981862459146728e-36</v>
+        <v>2.640043300741546e-103</v>
       </c>
     </row>
     <row r="289">
@@ -7656,13 +6790,10 @@
         <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>0.9921407358770273</v>
+        <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>0.007859264122972592</v>
-      </c>
-      <c r="G289" t="n">
-        <v>2.280205109306539e-22</v>
+        <v>1.094627204448849e-59</v>
       </c>
     </row>
     <row r="290">
@@ -7681,13 +6812,10 @@
         <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>0.9807749478333576</v>
+        <v>1</v>
       </c>
       <c r="F290" t="n">
-        <v>0.01922505216664237</v>
-      </c>
-      <c r="G290" t="n">
-        <v>1.278246593898778e-36</v>
+        <v>7.868852144484467e-90</v>
       </c>
     </row>
     <row r="291">
@@ -7706,13 +6834,10 @@
         <v>1</v>
       </c>
       <c r="E291" t="n">
-        <v>0.9653654294528493</v>
+        <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>0.03463457054715068</v>
-      </c>
-      <c r="G291" t="n">
-        <v>8.514103645516752e-22</v>
+        <v>2.389252751912886e-63</v>
       </c>
     </row>
     <row r="292">
@@ -7731,12 +6856,9 @@
         <v>3</v>
       </c>
       <c r="E292" t="n">
-        <v>8.05497874919727e-24</v>
+        <v>0</v>
       </c>
       <c r="F292" t="n">
-        <v>1.513646066676685e-29</v>
-      </c>
-      <c r="G292" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7756,13 +6878,10 @@
         <v>1</v>
       </c>
       <c r="E293" t="n">
-        <v>0.9962283222779791</v>
+        <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>0.003771677722021046</v>
-      </c>
-      <c r="G293" t="n">
-        <v>1.206647137586476e-31</v>
+        <v>1.17018341308291e-70</v>
       </c>
     </row>
     <row r="294">
@@ -7781,12 +6900,9 @@
         <v>3</v>
       </c>
       <c r="E294" t="n">
-        <v>5.644381676269288e-41</v>
+        <v>0</v>
       </c>
       <c r="F294" t="n">
-        <v>1.295927209617741e-42</v>
-      </c>
-      <c r="G294" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7806,13 +6922,10 @@
         <v>3</v>
       </c>
       <c r="E295" t="n">
-        <v>1.296071007042675e-06</v>
+        <v>0.4144874612827859</v>
       </c>
       <c r="F295" t="n">
-        <v>1.622814614517076e-11</v>
-      </c>
-      <c r="G295" t="n">
-        <v>0.9999987039127648</v>
+        <v>0.5855125387172141</v>
       </c>
     </row>
     <row r="296">
@@ -7831,13 +6944,10 @@
         <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>0.9897744383890923</v>
+        <v>1</v>
       </c>
       <c r="F296" t="n">
-        <v>0.01022556161090768</v>
-      </c>
-      <c r="G296" t="n">
-        <v>8.284370407452495e-18</v>
+        <v>1.420304415433706e-59</v>
       </c>
     </row>
     <row r="297">
@@ -7856,12 +6966,9 @@
         <v>3</v>
       </c>
       <c r="E297" t="n">
-        <v>9.474473583511146e-39</v>
+        <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>7.16993876433125e-41</v>
-      </c>
-      <c r="G297" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7881,13 +6988,10 @@
         <v>1</v>
       </c>
       <c r="E298" t="n">
-        <v>0.7167947278587867</v>
+        <v>1</v>
       </c>
       <c r="F298" t="n">
-        <v>0.2832052721412133</v>
-      </c>
-      <c r="G298" t="n">
-        <v>2.67665002856225e-19</v>
+        <v>9.500547906193115e-73</v>
       </c>
     </row>
     <row r="299">
@@ -7906,13 +7010,10 @@
         <v>1</v>
       </c>
       <c r="E299" t="n">
-        <v>0.6036338423070458</v>
+        <v>1</v>
       </c>
       <c r="F299" t="n">
-        <v>0.3963661576929542</v>
-      </c>
-      <c r="G299" t="n">
-        <v>1.492633568152601e-34</v>
+        <v>2.119077035752054e-89</v>
       </c>
     </row>
     <row r="300">
@@ -7931,12 +7032,9 @@
         <v>3</v>
       </c>
       <c r="E300" t="n">
-        <v>4.61841004924574e-32</v>
+        <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>1.540247816825955e-34</v>
-      </c>
-      <c r="G300" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7956,13 +7054,10 @@
         <v>3</v>
       </c>
       <c r="E301" t="n">
-        <v>0.007565113216882607</v>
+        <v>0.01570406432302596</v>
       </c>
       <c r="F301" t="n">
-        <v>2.303456409745842e-07</v>
-      </c>
-      <c r="G301" t="n">
-        <v>0.9924346564374764</v>
+        <v>0.984295935676974</v>
       </c>
     </row>
     <row r="302">
@@ -7981,13 +7076,10 @@
         <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>0.9998999059828615</v>
+        <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>0.000100089650050934</v>
-      </c>
-      <c r="G302" t="n">
-        <v>4.367087588692211e-09</v>
+        <v>1.366772373646436e-36</v>
       </c>
     </row>
     <row r="303">
@@ -8006,12 +7098,9 @@
         <v>3</v>
       </c>
       <c r="E303" t="n">
-        <v>2.358749523344202e-62</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>1.580578209813729e-68</v>
-      </c>
-      <c r="G303" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8022,7 +7111,7 @@
         </is>
       </c>
       <c r="B304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C304" t="n">
         <v>1</v>
@@ -8031,13 +7120,10 @@
         <v>1</v>
       </c>
       <c r="E304" t="n">
-        <v>0.9909751931236458</v>
+        <v>1</v>
       </c>
       <c r="F304" t="n">
-        <v>0.009024806876354151</v>
-      </c>
-      <c r="G304" t="n">
-        <v>3.987718882843544e-36</v>
+        <v>1.026201572258133e-83</v>
       </c>
     </row>
     <row r="305">
@@ -8047,7 +7133,7 @@
         </is>
       </c>
       <c r="B305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C305" t="n">
         <v>1</v>
@@ -8056,13 +7142,10 @@
         <v>1</v>
       </c>
       <c r="E305" t="n">
-        <v>0.9983342227881874</v>
+        <v>1</v>
       </c>
       <c r="F305" t="n">
-        <v>0.001665777211812657</v>
-      </c>
-      <c r="G305" t="n">
-        <v>1.933211459891826e-33</v>
+        <v>9.378511513329239e-82</v>
       </c>
     </row>
     <row r="306">
@@ -8081,13 +7164,10 @@
         <v>1</v>
       </c>
       <c r="E306" t="n">
-        <v>0.9998515911592036</v>
+        <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>0.0001484088407965042</v>
-      </c>
-      <c r="G306" t="n">
-        <v>8.045963798180108e-20</v>
+        <v>7.748635088255171e-71</v>
       </c>
     </row>
     <row r="307">
@@ -8106,12 +7186,9 @@
         <v>3</v>
       </c>
       <c r="E307" t="n">
-        <v>1.272057524040049e-18</v>
+        <v>0</v>
       </c>
       <c r="F307" t="n">
-        <v>8.360190676480656e-23</v>
-      </c>
-      <c r="G307" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8131,13 +7208,10 @@
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>0.9978512244967422</v>
+        <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>0.002148775503257743</v>
-      </c>
-      <c r="G308" t="n">
-        <v>1.558205630755049e-26</v>
+        <v>3.304995144299605e-89</v>
       </c>
     </row>
     <row r="309">
@@ -8156,13 +7230,10 @@
         <v>1</v>
       </c>
       <c r="E309" t="n">
-        <v>0.9998110993993856</v>
+        <v>1</v>
       </c>
       <c r="F309" t="n">
-        <v>0.000188900600614106</v>
-      </c>
-      <c r="G309" t="n">
-        <v>1.513639633224811e-16</v>
+        <v>2.826832091757825e-72</v>
       </c>
     </row>
     <row r="310">
@@ -8181,13 +7252,10 @@
         <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>0.997259744430591</v>
+        <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>0.001215144382507842</v>
-      </c>
-      <c r="G310" t="n">
-        <v>0.001525111186901139</v>
+        <v>3.413488834297605e-44</v>
       </c>
     </row>
     <row r="311">
@@ -8206,13 +7274,10 @@
         <v>1</v>
       </c>
       <c r="E311" t="n">
-        <v>0.9999032019941132</v>
+        <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>9.679800588677554e-05</v>
-      </c>
-      <c r="G311" t="n">
-        <v>3.435874632320647e-22</v>
+        <v>7.05300437947001e-96</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/artifacts/all_sites_classified.xlsx
@@ -479,7 +479,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.577323370632145e-37</v>
+        <v>1.199332638614625e-33</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.659608448613661e-44</v>
+        <v>1.173285790160116e-42</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>6.396275756989901e-41</v>
+        <v>6.042105967083661e-26</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4.184700140099287e-106</v>
+        <v>6.168015329438651e-69</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.139548109503929e-56</v>
+        <v>1.716433868785215e-63</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.813599903472144e-58</v>
+        <v>3.424819123230451e-46</v>
       </c>
     </row>
     <row r="8">
@@ -608,10 +608,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.9999999999999976</v>
       </c>
       <c r="F8" t="n">
-        <v>1.366398330948042e-40</v>
+        <v>2.388837844630031e-15</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>6.546577214714725e-74</v>
+        <v>2.089440988644228e-36</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>9.016568227907951e-86</v>
+        <v>2.018517970816981e-53</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9326987859514e-77</v>
+        <v>2.001891747775909e-41</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1.601654070353406e-72</v>
+        <v>4.029735761860855e-37</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.999999999999953</v>
       </c>
       <c r="F13" t="n">
-        <v>1.140009424704253e-41</v>
+        <v>4.696196104419833e-14</v>
       </c>
     </row>
     <row r="14">
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.9999999994918025</v>
       </c>
       <c r="F14" t="n">
-        <v>7.89138125903788e-40</v>
+        <v>5.081974841232115e-10</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.609617717817374e-78</v>
+        <v>7.53828940962104e-40</v>
       </c>
     </row>
     <row r="16">
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.9999997126923796</v>
       </c>
       <c r="F16" t="n">
-        <v>5.044554283263594e-37</v>
+        <v>2.873076203992431e-07</v>
       </c>
     </row>
     <row r="17">
@@ -809,7 +809,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.413324859814392e-75</v>
+        <v>5.039285031630996e-35</v>
       </c>
     </row>
     <row r="18">
@@ -828,10 +828,10 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01699510893765099</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F18" t="n">
-        <v>0.983004891062349</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="19">
@@ -853,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>4.662710422532653e-79</v>
+        <v>1.117335668810021e-34</v>
       </c>
     </row>
     <row r="20">
@@ -875,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>3.445148048023012e-64</v>
+        <v>1.396065548043512e-22</v>
       </c>
     </row>
     <row r="21">
@@ -897,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1.179693874995054e-73</v>
+        <v>1.672362304921065e-33</v>
       </c>
     </row>
     <row r="22">
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.733052692550053e-99</v>
+        <v>3.267204788406294e-38</v>
       </c>
     </row>
     <row r="23">
@@ -938,10 +938,10 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>3.556223465606134e-05</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999644377653439</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -963,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1.41910660054016e-139</v>
+        <v>1.914207364647955e-99</v>
       </c>
     </row>
     <row r="25">
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>8.156113214393498e-77</v>
+        <v>1.824953474562628e-65</v>
       </c>
     </row>
     <row r="26">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1.122540861077599e-45</v>
+        <v>7.354964154073112e-33</v>
       </c>
     </row>
     <row r="27">
@@ -1048,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.9999996363650142</v>
       </c>
       <c r="F28" t="n">
-        <v>9.381978972213362e-43</v>
+        <v>3.636349857832106e-07</v>
       </c>
     </row>
     <row r="29">
@@ -1117,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1.021860173449953e-77</v>
+        <v>6.691181247923985e-36</v>
       </c>
     </row>
     <row r="32">
@@ -1139,7 +1139,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>3.652668072077491e-74</v>
+        <v>7.455778092272394e-39</v>
       </c>
     </row>
     <row r="33">
@@ -1158,10 +1158,10 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>1.782285430351749e-10</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9999999998217715</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1183,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>1.832500149384973e-62</v>
+        <v>9.713493213127435e-22</v>
       </c>
     </row>
     <row r="35">
@@ -1205,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>8.130510142834432e-84</v>
+        <v>6.668760709602801e-55</v>
       </c>
     </row>
     <row r="36">
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>4.929587278113905e-87</v>
+        <v>1.651291669204573e-53</v>
       </c>
     </row>
     <row r="37">
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.9999998542242583</v>
       </c>
       <c r="F37" t="n">
-        <v>4.646578664185266e-28</v>
+        <v>1.457757417433898e-07</v>
       </c>
     </row>
     <row r="38">
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1.463243133224925e-82</v>
+        <v>1.034528388671709e-60</v>
       </c>
     </row>
     <row r="39">
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1.340270747521398e-21</v>
+        <v>9.861108687451642e-19</v>
       </c>
     </row>
     <row r="40">
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>3.445779503539908e-68</v>
+        <v>9.319522622598534e-22</v>
       </c>
     </row>
     <row r="42">
@@ -1356,10 +1356,10 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9999999999999929</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>7.127400455702353e-15</v>
+        <v>1.036210251835477e-19</v>
       </c>
     </row>
     <row r="43">
@@ -1381,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>3.992114239111314e-36</v>
+        <v>6.133540036478301e-21</v>
       </c>
     </row>
     <row r="44">
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>7.5635896512696e-91</v>
+        <v>1.488584298147384e-64</v>
       </c>
     </row>
     <row r="45">
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>9.917885857891092e-134</v>
+        <v>4.012636057680724e-83</v>
       </c>
     </row>
     <row r="46">
@@ -1444,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9999999999999516</v>
+        <v>0.9999999999970181</v>
       </c>
       <c r="F46" t="n">
-        <v>4.845941584343292e-14</v>
+        <v>2.981992123844975e-12</v>
       </c>
     </row>
     <row r="47">
@@ -1469,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>4.016722511916493e-55</v>
+        <v>2.709719398728267e-29</v>
       </c>
     </row>
     <row r="48">
@@ -1491,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>6.018295009623318e-97</v>
+        <v>1.790048085525715e-62</v>
       </c>
     </row>
     <row r="49">
@@ -1513,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1.609737819974522e-80</v>
+        <v>3.398434401868494e-52</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1.824192131242626e-74</v>
+        <v>3.473382725785135e-30</v>
       </c>
     </row>
     <row r="51">
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1.142336343209834e-68</v>
+        <v>2.3384847406434e-40</v>
       </c>
     </row>
     <row r="52">
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>3.030379149355854e-86</v>
+        <v>2.573150928823708e-51</v>
       </c>
     </row>
     <row r="53">
@@ -1601,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>2.474341003465087e-79</v>
+        <v>9.711146261963411e-35</v>
       </c>
     </row>
     <row r="54">
@@ -1620,10 +1620,10 @@
         <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>5.03597163969971e-13</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0.9999999999994964</v>
       </c>
     </row>
     <row r="55">
@@ -1645,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1.374047905883196e-73</v>
+        <v>7.665084190292496e-51</v>
       </c>
     </row>
     <row r="56">
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.9999999999999988</v>
       </c>
       <c r="F56" t="n">
-        <v>4.502973077607376e-24</v>
+        <v>1.187559122961883e-15</v>
       </c>
     </row>
     <row r="57">
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1.139766782156641e-54</v>
+        <v>7.547405145492466e-33</v>
       </c>
     </row>
     <row r="58">
@@ -1711,7 +1711,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1.421536527508347e-53</v>
+        <v>1.020442393211269e-26</v>
       </c>
     </row>
     <row r="59">
@@ -1733,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.660537023863921e-60</v>
+        <v>8.947741392771144e-34</v>
       </c>
     </row>
     <row r="60">
@@ -1752,10 +1752,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0.9999913101908001</v>
       </c>
       <c r="F60" t="n">
-        <v>7.744726967636735e-38</v>
+        <v>8.689809199881563e-06</v>
       </c>
     </row>
     <row r="61">
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>2.267464102385565e-74</v>
+        <v>1.634080996157957e-49</v>
       </c>
     </row>
     <row r="62">
@@ -1790,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>6.731273873050725e-05</v>
       </c>
       <c r="F62" t="n">
-        <v>5.451601255273687e-48</v>
+        <v>0.9999326872612695</v>
       </c>
     </row>
     <row r="63">
@@ -1812,16 +1812,16 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>1.065295743840622e-06</v>
       </c>
       <c r="F63" t="n">
-        <v>2.944195105806111e-51</v>
+        <v>0.9999989347042562</v>
       </c>
     </row>
     <row r="64">
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>3.507205636231559e-108</v>
+        <v>5.074082142040603e-103</v>
       </c>
     </row>
     <row r="65">
@@ -1865,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>6.812005380082613e-94</v>
+        <v>5.193482912033308e-54</v>
       </c>
     </row>
     <row r="66">
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>3.54337829728852e-23</v>
+        <v>4.073436036269165e-18</v>
       </c>
     </row>
     <row r="67">
@@ -1909,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>8.087946063832083e-76</v>
+        <v>1.060958734999698e-42</v>
       </c>
     </row>
     <row r="68">
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1.412275830284387e-84</v>
+        <v>4.763054836477829e-55</v>
       </c>
     </row>
     <row r="69">
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>2.021433089725943e-82</v>
+        <v>1.93961375318955e-54</v>
       </c>
     </row>
     <row r="70">
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>2.416797698862943e-91</v>
+        <v>4.101051528316695e-95</v>
       </c>
     </row>
     <row r="71">
@@ -1997,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>3.014909642620987e-70</v>
+        <v>3.277982496222288e-41</v>
       </c>
     </row>
     <row r="72">
@@ -2019,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>3.189313432433863e-71</v>
+        <v>3.176435642706704e-88</v>
       </c>
     </row>
     <row r="73">
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>5.738352245701207e-37</v>
+        <v>7.201977008015237e-25</v>
       </c>
     </row>
     <row r="74">
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1.135034115623168e-76</v>
+        <v>4.224015311864802e-47</v>
       </c>
     </row>
     <row r="75">
@@ -2085,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>2.080075291104721e-94</v>
+        <v>5.437254760380851e-93</v>
       </c>
     </row>
     <row r="76">
@@ -2107,7 +2107,7 @@
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>2.079882876375173e-57</v>
+        <v>3.829439490083123e-78</v>
       </c>
     </row>
     <row r="77">
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>7.533421482350176e-87</v>
+        <v>8.126724642791498e-53</v>
       </c>
     </row>
     <row r="78">
@@ -2151,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1.303471074394248e-96</v>
+        <v>8.875853829513741e-58</v>
       </c>
     </row>
     <row r="79">
@@ -2173,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>1.463626712271747e-96</v>
+        <v>4.633799925133159e-95</v>
       </c>
     </row>
     <row r="80">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>3.13591215436143e-98</v>
+        <v>2.589172106867175e-59</v>
       </c>
     </row>
     <row r="81">
@@ -2217,7 +2217,7 @@
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>3.992053037929373e-63</v>
+        <v>1.222840326387715e-41</v>
       </c>
     </row>
     <row r="82">
@@ -2239,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>4.206147316481281e-81</v>
+        <v>2.112857739238259e-49</v>
       </c>
     </row>
     <row r="83">
@@ -2261,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>4.155202614111305e-77</v>
+        <v>4.309442990085995e-50</v>
       </c>
     </row>
     <row r="84">
@@ -2283,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>6.897706654690354e-36</v>
+        <v>3.782011554230605e-30</v>
       </c>
     </row>
     <row r="85">
@@ -2305,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>4.67089290898385e-81</v>
+        <v>5.27933238877908e-53</v>
       </c>
     </row>
     <row r="86">
@@ -2324,10 +2324,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="F86" t="n">
-        <v>8.931750434423954e-41</v>
+        <v>6.787816468198647e-16</v>
       </c>
     </row>
     <row r="87">
@@ -2349,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>5.725899408693859e-83</v>
+        <v>2.617189809202924e-33</v>
       </c>
     </row>
     <row r="88">
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>7.227113632700376e-114</v>
+        <v>7.075921286025123e-64</v>
       </c>
     </row>
     <row r="89">
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>4.407300399224881e-86</v>
+        <v>7.211723501052157e-38</v>
       </c>
     </row>
     <row r="90">
@@ -2415,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>1.426504804317872e-64</v>
+        <v>5.913566595489617e-26</v>
       </c>
     </row>
     <row r="91">
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>9.886212380755626e-51</v>
+        <v>9.824591800808564e-22</v>
       </c>
     </row>
     <row r="92">
@@ -2450,16 +2450,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9814601522568263</v>
+        <v>2.886579864025407e-15</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01853984774317377</v>
+        <v>0.9999999999999971</v>
       </c>
     </row>
     <row r="93">
@@ -2481,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>1.546268431557672e-76</v>
+        <v>4.833042074013063e-29</v>
       </c>
     </row>
     <row r="94">
@@ -2494,16 +2494,16 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9999999999999939</v>
+        <v>2.460254222569347e-13</v>
       </c>
       <c r="F94" t="n">
-        <v>6.15922523110683e-15</v>
+        <v>0.999999999999754</v>
       </c>
     </row>
     <row r="95">
@@ -2522,10 +2522,10 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0.6102359777569556</v>
       </c>
       <c r="F95" t="n">
-        <v>6.304919383656712e-34</v>
+        <v>0.3897640222430444</v>
       </c>
     </row>
     <row r="96">
@@ -2547,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1.048337247348803e-76</v>
+        <v>7.961340274514087e-46</v>
       </c>
     </row>
     <row r="97">
@@ -2560,16 +2560,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9999999999997959</v>
+        <v>1.484011491470483e-08</v>
       </c>
       <c r="F97" t="n">
-        <v>2.040144272109393e-13</v>
+        <v>0.9999999851598851</v>
       </c>
     </row>
     <row r="98">
@@ -2582,16 +2582,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>0.999729077464217</v>
+        <v>1.760813717055498e-13</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0002709225357829525</v>
+        <v>0.9999999999998239</v>
       </c>
     </row>
     <row r="99">
@@ -2610,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>3.869013528889909e-05</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9999613098647111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2635,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>2.626663797566259e-81</v>
+        <v>3.667815673455339e-34</v>
       </c>
     </row>
     <row r="101">
@@ -2648,16 +2648,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" t="n">
-        <v>0.999999999999992</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>8.047373893192517e-15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2679,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>5.589050481825875e-37</v>
+        <v>2.515772713292779e-27</v>
       </c>
     </row>
     <row r="103">
@@ -2701,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>2.420911351399018e-68</v>
+        <v>1.191947692910314e-33</v>
       </c>
     </row>
     <row r="104">
@@ -2723,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>2.075117379696439e-86</v>
+        <v>5.108993913715701e-54</v>
       </c>
     </row>
     <row r="105">
@@ -2745,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>3.248441693378059e-59</v>
+        <v>1.204565794276014e-45</v>
       </c>
     </row>
     <row r="106">
@@ -2767,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>3.709047647820681e-117</v>
+        <v>3.513430728671856e-81</v>
       </c>
     </row>
     <row r="107">
@@ -2789,7 +2789,7 @@
         <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>2.116388502952834e-73</v>
+        <v>4.386978313230252e-36</v>
       </c>
     </row>
     <row r="108">
@@ -2811,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>3.055519321021086e-75</v>
+        <v>4.844667475227295e-43</v>
       </c>
     </row>
     <row r="109">
@@ -2833,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>2.99057134244601e-35</v>
+        <v>2.779953706359493e-26</v>
       </c>
     </row>
     <row r="110">
@@ -2877,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>6.97422052506608e-86</v>
+        <v>1.620371233433568e-57</v>
       </c>
     </row>
     <row r="112">
@@ -2899,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>2.679307310484173e-86</v>
+        <v>5.117695915348364e-58</v>
       </c>
     </row>
     <row r="113">
@@ -2921,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>1.060341644354227e-38</v>
+        <v>1.396393683073103e-31</v>
       </c>
     </row>
     <row r="114">
@@ -2943,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>5.620455272212034e-61</v>
+        <v>1.065813014841401e-52</v>
       </c>
     </row>
     <row r="115">
@@ -2962,10 +2962,10 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0.9999999999405469</v>
       </c>
       <c r="F115" t="n">
-        <v>4.273813700906526e-28</v>
+        <v>5.945305797850317e-11</v>
       </c>
     </row>
     <row r="116">
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>2.815419484678681e-70</v>
+        <v>8.644013298807627e-48</v>
       </c>
     </row>
     <row r="117">
@@ -3009,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>5.085208884959161e-57</v>
+        <v>1.09142646358683e-44</v>
       </c>
     </row>
     <row r="118">
@@ -3031,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>3.600072384991597e-87</v>
+        <v>2.516988326066144e-64</v>
       </c>
     </row>
     <row r="119">
@@ -3053,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>1.789013042099961e-73</v>
+        <v>1.11727630211235e-38</v>
       </c>
     </row>
     <row r="120">
@@ -3075,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>1.138224110583429e-57</v>
+        <v>5.942839282088825e-35</v>
       </c>
     </row>
     <row r="121">
@@ -3119,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>4.875343748967822e-81</v>
+        <v>1.175062378947631e-48</v>
       </c>
     </row>
     <row r="123">
@@ -3141,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>4.53856607586994e-53</v>
+        <v>4.400147392641071e-23</v>
       </c>
     </row>
     <row r="124">
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>4.911152584426363e-76</v>
+        <v>1.370046238423682e-47</v>
       </c>
     </row>
     <row r="125">
@@ -3185,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>8.269151808037446e-73</v>
+        <v>1.997695181822952e-45</v>
       </c>
     </row>
     <row r="126">
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>8.946066934690704e-59</v>
+        <v>3.012187221665299e-35</v>
       </c>
     </row>
     <row r="127">
@@ -3226,10 +3226,10 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="F127" t="n">
-        <v>2.686462246723118e-26</v>
+        <v>9.934284824000907e-16</v>
       </c>
     </row>
     <row r="128">
@@ -3251,7 +3251,7 @@
         <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>6.306714917946874e-45</v>
+        <v>1.233772833151426e-23</v>
       </c>
     </row>
     <row r="129">
@@ -3264,16 +3264,16 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>4.674777328572688e-06</v>
       </c>
       <c r="F129" t="n">
-        <v>1.97045043013422e-35</v>
+        <v>0.9999953252226714</v>
       </c>
     </row>
     <row r="130">
@@ -3292,10 +3292,10 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0.9999999999946196</v>
       </c>
       <c r="F130" t="n">
-        <v>7.423595295947116e-26</v>
+        <v>5.380311969280921e-12</v>
       </c>
     </row>
     <row r="131">
@@ -3317,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>2.691281359547506e-97</v>
+        <v>1.116982432328305e-55</v>
       </c>
     </row>
     <row r="132">
@@ -3336,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0008397513025389935</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.999160248697461</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3361,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>1.084301738810881e-58</v>
+        <v>2.247246868713836e-31</v>
       </c>
     </row>
     <row r="134">
@@ -3405,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>1.868746677403937e-92</v>
+        <v>3.271976631845593e-46</v>
       </c>
     </row>
     <row r="136">
@@ -3484,16 +3484,16 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>7.850080253613001e-07</v>
       </c>
       <c r="F139" t="n">
-        <v>2.811082136612035e-33</v>
+        <v>0.9999992149919746</v>
       </c>
     </row>
     <row r="140">
@@ -3534,10 +3534,10 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0.9999999912866361</v>
       </c>
       <c r="F141" t="n">
-        <v>1.425531600778556e-46</v>
+        <v>8.713363909794169e-09</v>
       </c>
     </row>
     <row r="142">
@@ -3600,10 +3600,10 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="F144" t="n">
-        <v>1.269769912977781e-20</v>
+        <v>3.770862471303513e-16</v>
       </c>
     </row>
     <row r="145">
@@ -3622,10 +3622,10 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.9999852773924723</v>
       </c>
       <c r="F145" t="n">
-        <v>9.324389051253835e-36</v>
+        <v>1.472260752770979e-05</v>
       </c>
     </row>
     <row r="146">
@@ -3644,10 +3644,10 @@
         <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>0.01473584179931742</v>
+        <v>6.960054754756584e-11</v>
       </c>
       <c r="F146" t="n">
-        <v>0.9852641582006826</v>
+        <v>0.9999999999303995</v>
       </c>
     </row>
     <row r="147">
@@ -3726,16 +3726,16 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
-        <v>0.9999999999999887</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>1.130134306549867e-14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -3757,7 +3757,7 @@
         <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>3.035495895768416e-64</v>
+        <v>2.995524398217906e-25</v>
       </c>
     </row>
     <row r="152">
@@ -3776,10 +3776,10 @@
         <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>5.551115123125783e-15</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.9999999999999944</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -3798,10 +3798,10 @@
         <v>3</v>
       </c>
       <c r="E153" t="n">
-        <v>2.557509759526511e-12</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.9999999999974425</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -3820,10 +3820,10 @@
         <v>3</v>
       </c>
       <c r="E154" t="n">
-        <v>5.81756864903582e-13</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="F154" t="n">
-        <v>0.9999999999994182</v>
+        <v>0.9999999999999973</v>
       </c>
     </row>
     <row r="155">
@@ -3836,16 +3836,16 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>0.9491043331273357</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.05089566687266438</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -3867,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>2.432567358340005e-19</v>
+        <v>8.273176359759718e-19</v>
       </c>
     </row>
     <row r="157">
@@ -3886,10 +3886,10 @@
         <v>3</v>
       </c>
       <c r="E157" t="n">
-        <v>1.186430065303057e-09</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9999999988135699</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -3908,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>2.322500225804269e-06</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9999976774997742</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -3933,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>1.305817558997166e-23</v>
+        <v>2.355666001554521e-17</v>
       </c>
     </row>
     <row r="160">
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" t="n">
-        <v>0.9999999999999838</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>1.621461321839528e-14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -3974,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="E161" t="n">
-        <v>4.099284806502457e-05</v>
+        <v>3.00761760718693e-07</v>
       </c>
       <c r="F161" t="n">
-        <v>0.999959007151935</v>
+        <v>0.9999996992382393</v>
       </c>
     </row>
     <row r="162">
@@ -3999,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>1.054117232386011e-51</v>
+        <v>2.040193906631919e-19</v>
       </c>
     </row>
     <row r="163">
@@ -4018,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="E163" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -4034,16 +4034,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>0.9999998446152031</v>
+        <v>6.226232640571538e-09</v>
       </c>
       <c r="F164" t="n">
-        <v>1.553847969330774e-07</v>
+        <v>0.9999999937737674</v>
       </c>
     </row>
     <row r="165">
@@ -4059,13 +4059,13 @@
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
-        <v>0.999999748385011</v>
+        <v>0.06018345541915215</v>
       </c>
       <c r="F165" t="n">
-        <v>2.516149889773066e-07</v>
+        <v>0.9398165445808478</v>
       </c>
     </row>
     <row r="166">
@@ -4078,16 +4078,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0.000793761495665124</v>
       </c>
       <c r="F166" t="n">
-        <v>1.489889563757671e-20</v>
+        <v>0.9992062385043349</v>
       </c>
     </row>
     <row r="167">
@@ -4128,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="E168" t="n">
-        <v>2.869957604900719e-10</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9999999997130042</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -4153,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="F169" t="n">
-        <v>2.822229591265894e-77</v>
+        <v>1.728602974572313e-61</v>
       </c>
     </row>
     <row r="170">
@@ -4172,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="E170" t="n">
-        <v>5.022338100957313e-11</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.9999999999497766</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4197,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>2.737552937780181e-67</v>
+        <v>6.314225424552599e-18</v>
       </c>
     </row>
     <row r="172">
@@ -4210,16 +4210,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0.06790612717678668</v>
       </c>
       <c r="F172" t="n">
-        <v>1.099719250925226e-17</v>
+        <v>0.9320938728232133</v>
       </c>
     </row>
     <row r="173">
@@ -4232,16 +4232,16 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E173" t="n">
-        <v>0.9999999999998967</v>
+        <v>1.590266880402424e-07</v>
       </c>
       <c r="F173" t="n">
-        <v>1.03279172623032e-13</v>
+        <v>0.999999840973312</v>
       </c>
     </row>
     <row r="174">
@@ -4254,16 +4254,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>0.02055211378863708</v>
       </c>
       <c r="F174" t="n">
-        <v>5.285550425442777e-21</v>
+        <v>0.9794478862113629</v>
       </c>
     </row>
     <row r="175">
@@ -4282,10 +4282,10 @@
         <v>3</v>
       </c>
       <c r="E175" t="n">
-        <v>5.221936882904288e-09</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0.9999999947780631</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4298,16 +4298,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E176" t="n">
-        <v>0.9999999999998623</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>1.37719891139067e-13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>5.489985249430737e-57</v>
+        <v>1.429199719180842e-19</v>
       </c>
     </row>
     <row r="178">
@@ -4342,16 +4342,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E178" t="n">
-        <v>0.9999999999999994</v>
+        <v>3.335864917630715e-11</v>
       </c>
       <c r="F178" t="n">
-        <v>5.215915498840885e-16</v>
+        <v>0.9999999999666414</v>
       </c>
     </row>
     <row r="179">
@@ -4364,16 +4364,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
-        <v>0.9999999999999993</v>
+        <v>0.2641238528619723</v>
       </c>
       <c r="F179" t="n">
-        <v>6.210189895481204e-16</v>
+        <v>0.7358761471380277</v>
       </c>
     </row>
     <row r="180">
@@ -4417,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>5.073173296138807e-56</v>
+        <v>8.569627115366297e-31</v>
       </c>
     </row>
     <row r="182">
@@ -4430,16 +4430,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E182" t="n">
-        <v>0.9999999999932476</v>
+        <v>5.150744015747222e-07</v>
       </c>
       <c r="F182" t="n">
-        <v>6.752414602997817e-12</v>
+        <v>0.9999994849255984</v>
       </c>
     </row>
     <row r="183">
@@ -4452,16 +4452,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" t="n">
-        <v>0.9996232942942751</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0003767057057248544</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>1.221430662086427e-67</v>
+        <v>8.12014610632645e-45</v>
       </c>
     </row>
     <row r="185">
@@ -4496,16 +4496,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E185" t="n">
-        <v>0.9999999999988174</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="F185" t="n">
-        <v>1.182582729386715e-12</v>
+        <v>0.9999999999999996</v>
       </c>
     </row>
     <row r="186">
@@ -4518,16 +4518,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>1.949551631241775e-13</v>
       </c>
       <c r="F186" t="n">
-        <v>2.038688593524277e-27</v>
+        <v>0.999999999999805</v>
       </c>
     </row>
     <row r="187">
@@ -4546,10 +4546,10 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>0.9946352969639102</v>
       </c>
       <c r="F187" t="n">
-        <v>2.346121991954196e-29</v>
+        <v>0.00536470303608987</v>
       </c>
     </row>
     <row r="188">
@@ -4562,16 +4562,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9999999999352089</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>6.479105186463488e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -4637,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>2.211854617653043e-24</v>
+        <v>4.817430827108619e-24</v>
       </c>
     </row>
     <row r="192">
@@ -4659,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>3.907690364409713e-83</v>
+        <v>4.124391140161618e-55</v>
       </c>
     </row>
     <row r="193">
@@ -4681,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="F193" t="n">
-        <v>3.278520096354075e-97</v>
+        <v>6.586551838065959e-64</v>
       </c>
     </row>
     <row r="194">
@@ -4703,7 +4703,7 @@
         <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>2.753948691442971e-66</v>
+        <v>9.139791080077798e-47</v>
       </c>
     </row>
     <row r="195">
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>1.381377642058521e-78</v>
+        <v>8.75064710049317e-72</v>
       </c>
     </row>
     <row r="196">
@@ -4744,10 +4744,10 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0.9999999980006153</v>
       </c>
       <c r="F196" t="n">
-        <v>2.487796485270032e-23</v>
+        <v>1.999384645722805e-09</v>
       </c>
     </row>
     <row r="197">
@@ -4791,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="F198" t="n">
-        <v>2.565233740796401e-94</v>
+        <v>5.711301022210996e-48</v>
       </c>
     </row>
     <row r="199">
@@ -4813,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>3.48628969860672e-109</v>
+        <v>3.268883816586843e-74</v>
       </c>
     </row>
     <row r="200">
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>2.151762096433536e-66</v>
+        <v>5.680110940559333e-34</v>
       </c>
     </row>
     <row r="201">
@@ -4848,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
@@ -4857,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="F201" t="n">
-        <v>6.713620566580402e-76</v>
+        <v>9.536429863298484e-52</v>
       </c>
     </row>
     <row r="202">
@@ -4876,10 +4876,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0.9999999999648339</v>
       </c>
       <c r="F202" t="n">
-        <v>1.665801618772482e-18</v>
+        <v>3.516614159406322e-11</v>
       </c>
     </row>
     <row r="203">
@@ -4923,7 +4923,7 @@
         <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>6.31106971379135e-36</v>
+        <v>1.838167185957529e-28</v>
       </c>
     </row>
     <row r="205">
@@ -4945,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="F205" t="n">
-        <v>6.186732219326921e-88</v>
+        <v>2.429632440671838e-33</v>
       </c>
     </row>
     <row r="206">
@@ -4961,13 +4961,13 @@
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206" t="n">
-        <v>1</v>
+        <v>2.354512638669259e-05</v>
       </c>
       <c r="F206" t="n">
-        <v>5.886533146129404e-33</v>
+        <v>0.9999764548736133</v>
       </c>
     </row>
     <row r="207">
@@ -4986,10 +4986,10 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>0.9993421237016411</v>
       </c>
       <c r="F207" t="n">
-        <v>2.281351913552158e-52</v>
+        <v>0.0006578762983588496</v>
       </c>
     </row>
     <row r="208">
@@ -5011,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="F208" t="n">
-        <v>9.302093280710014e-93</v>
+        <v>4.139771087522393e-38</v>
       </c>
     </row>
     <row r="209">
@@ -5030,10 +5030,10 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>0.9779052058255584</v>
       </c>
       <c r="F209" t="n">
-        <v>8.612292478415106e-24</v>
+        <v>0.02209479417444156</v>
       </c>
     </row>
     <row r="210">
@@ -5052,10 +5052,10 @@
         <v>3</v>
       </c>
       <c r="E210" t="n">
-        <v>0.2703774588591723</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0.7296225411408277</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -5068,16 +5068,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E211" t="n">
-        <v>0.9999999999604896</v>
+        <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>3.95104160218467e-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>1.108468348357597e-69</v>
+        <v>4.569839137977101e-21</v>
       </c>
     </row>
     <row r="213">
@@ -5118,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="E213" t="n">
-        <v>3.70345310498621e-05</v>
+        <v>7.525091660909311e-13</v>
       </c>
       <c r="F213" t="n">
-        <v>0.9999629654689501</v>
+        <v>0.9999999999992475</v>
       </c>
     </row>
     <row r="214">
@@ -5140,10 +5140,10 @@
         <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>0.999995368554418</v>
       </c>
       <c r="F214" t="n">
-        <v>2.796477770378162e-24</v>
+        <v>4.631445582066786e-06</v>
       </c>
     </row>
     <row r="215">
@@ -5165,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="F215" t="n">
-        <v>5.449189912517303e-48</v>
+        <v>5.123128121411321e-35</v>
       </c>
     </row>
     <row r="216">
@@ -5209,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>1.692060713411116e-65</v>
+        <v>8.14479290270155e-22</v>
       </c>
     </row>
     <row r="218">
@@ -5228,10 +5228,10 @@
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0.999999990610989</v>
       </c>
       <c r="F218" t="n">
-        <v>1.358366446136724e-23</v>
+        <v>9.389010964969621e-09</v>
       </c>
     </row>
     <row r="219">
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>7.550778079001156e-66</v>
+        <v>1.618710306379945e-17</v>
       </c>
     </row>
     <row r="220">
@@ -5266,16 +5266,16 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E220" t="n">
-        <v>0.9999998870675341</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>1.129324659681379e-07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -5316,10 +5316,10 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>0.9999999994125454</v>
       </c>
       <c r="F222" t="n">
-        <v>5.996224738311571e-28</v>
+        <v>5.874546672866152e-10</v>
       </c>
     </row>
     <row r="223">
@@ -5341,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="F223" t="n">
-        <v>2.277952280292786e-83</v>
+        <v>4.344531674669104e-56</v>
       </c>
     </row>
     <row r="224">
@@ -5363,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>6.07737193615386e-89</v>
+        <v>6.065683575088284e-61</v>
       </c>
     </row>
     <row r="225">
@@ -5385,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="F225" t="n">
-        <v>4.78266549028381e-76</v>
+        <v>3.486534938233877e-44</v>
       </c>
     </row>
     <row r="226">
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="B226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
         <v>1</v>
@@ -5407,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>4.076907601834036e-63</v>
+        <v>7.083028421538855e-43</v>
       </c>
     </row>
     <row r="227">
@@ -5451,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="F228" t="n">
-        <v>2.443547167939101e-80</v>
+        <v>4.648658794846538e-43</v>
       </c>
     </row>
     <row r="229">
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="F231" t="n">
-        <v>1.869532087778915e-87</v>
+        <v>9.82261127684357e-57</v>
       </c>
     </row>
     <row r="232">
@@ -5539,7 +5539,7 @@
         <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>1.209104784598425e-72</v>
+        <v>1.771016794945137e-47</v>
       </c>
     </row>
     <row r="233">
@@ -5561,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>5.380220299741286e-72</v>
+        <v>1.986012712417376e-53</v>
       </c>
     </row>
     <row r="234">
@@ -5605,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>1.140863131935348e-90</v>
+        <v>8.918061151127495e-64</v>
       </c>
     </row>
     <row r="236">
@@ -5649,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="F237" t="n">
-        <v>5.17416097708262e-57</v>
+        <v>4.449461879022846e-39</v>
       </c>
     </row>
     <row r="238">
@@ -5671,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>4.032958337046771e-63</v>
+        <v>4.191204858781106e-46</v>
       </c>
     </row>
     <row r="239">
@@ -5693,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>3.770049886913116e-70</v>
+        <v>4.697180364627337e-24</v>
       </c>
     </row>
     <row r="240">
@@ -5715,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>2.537588020841055e-65</v>
+        <v>2.215633796328156e-46</v>
       </c>
     </row>
     <row r="241">
@@ -5737,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="F241" t="n">
-        <v>2.941772218398596e-88</v>
+        <v>1.013084909548486e-56</v>
       </c>
     </row>
     <row r="242">
@@ -5759,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="F242" t="n">
-        <v>5.742403049017179e-117</v>
+        <v>2.315864907708304e-88</v>
       </c>
     </row>
     <row r="243">
@@ -5781,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="F243" t="n">
-        <v>4.359492981552906e-100</v>
+        <v>4.36966033393382e-70</v>
       </c>
     </row>
     <row r="244">
@@ -5803,7 +5803,7 @@
         <v>1</v>
       </c>
       <c r="F244" t="n">
-        <v>2.900933325723693e-67</v>
+        <v>3.434256117044344e-50</v>
       </c>
     </row>
     <row r="245">
@@ -5822,10 +5822,10 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>1</v>
+        <v>0.9999999999999991</v>
       </c>
       <c r="F245" t="n">
-        <v>2.59856089872457e-60</v>
+        <v>8.441479298114408e-16</v>
       </c>
     </row>
     <row r="246">
@@ -5847,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="F246" t="n">
-        <v>5.749436212529882e-88</v>
+        <v>5.436187191726753e-61</v>
       </c>
     </row>
     <row r="247">
@@ -5869,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>1.265753830306269e-66</v>
+        <v>1.579578520516198e-17</v>
       </c>
     </row>
     <row r="248">
@@ -5891,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="F248" t="n">
-        <v>5.501779502428273e-67</v>
+        <v>1.330521191755839e-46</v>
       </c>
     </row>
     <row r="249">
@@ -5913,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>9.470995508867851e-91</v>
+        <v>7.906582940909219e-57</v>
       </c>
     </row>
     <row r="250">
@@ -5935,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="F250" t="n">
-        <v>1.70723894154804e-86</v>
+        <v>2.716016644410713e-56</v>
       </c>
     </row>
     <row r="251">
@@ -5957,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="F251" t="n">
-        <v>3.304719503168349e-91</v>
+        <v>8.811067288206335e-61</v>
       </c>
     </row>
     <row r="252">
@@ -5979,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="F252" t="n">
-        <v>2.267479240546902e-86</v>
+        <v>6.85251636536889e-50</v>
       </c>
     </row>
     <row r="253">
@@ -5992,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D253" t="n">
         <v>1</v>
@@ -6001,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="F253" t="n">
-        <v>2.834082512345294e-58</v>
+        <v>1.39748241544708e-39</v>
       </c>
     </row>
     <row r="254">
@@ -6023,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="F254" t="n">
-        <v>7.933372119766671e-95</v>
+        <v>9.841835692042748e-59</v>
       </c>
     </row>
     <row r="255">
@@ -6045,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>8.575499320278659e-102</v>
+        <v>1.490456061194171e-65</v>
       </c>
     </row>
     <row r="256">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="B256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C256" t="n">
         <v>1</v>
@@ -6067,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="F256" t="n">
-        <v>2.425383938116322e-90</v>
+        <v>1.66830270326526e-52</v>
       </c>
     </row>
     <row r="257">
@@ -6089,7 +6089,7 @@
         <v>1</v>
       </c>
       <c r="F257" t="n">
-        <v>3.510176511334091e-104</v>
+        <v>2.15727260361205e-62</v>
       </c>
     </row>
     <row r="258">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C258" t="n">
         <v>1</v>
@@ -6111,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="F258" t="n">
-        <v>1.93058035986702e-85</v>
+        <v>4.726797552755686e-59</v>
       </c>
     </row>
     <row r="259">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>8.854184754393649e-100</v>
+        <v>8.75383064385484e-60</v>
       </c>
     </row>
     <row r="260">
@@ -6155,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>1.820379205468295e-112</v>
+        <v>2.724000956467708e-69</v>
       </c>
     </row>
     <row r="261">
@@ -6177,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>9.637882825216031e-102</v>
+        <v>2.219502310943788e-60</v>
       </c>
     </row>
     <row r="262">
@@ -6199,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>3.044787926154247e-81</v>
+        <v>1.462817283208698e-54</v>
       </c>
     </row>
     <row r="263">
@@ -6221,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>3.605067691707584e-83</v>
+        <v>3.410682169904072e-44</v>
       </c>
     </row>
     <row r="264">
@@ -6243,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>3.912465311272506e-76</v>
+        <v>1.351626996070102e-37</v>
       </c>
     </row>
     <row r="265">
@@ -6265,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>1.321885958360466e-79</v>
+        <v>1.633998697777528e-49</v>
       </c>
     </row>
     <row r="266">
@@ -6287,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="F266" t="n">
-        <v>1.795703671174096e-87</v>
+        <v>8.261291240886273e-58</v>
       </c>
     </row>
     <row r="267">
@@ -6309,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="F267" t="n">
-        <v>1.343373760199249e-80</v>
+        <v>1.60716440849971e-49</v>
       </c>
     </row>
     <row r="268">
@@ -6331,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="F268" t="n">
-        <v>1.621627684530572e-82</v>
+        <v>1.932292759881871e-46</v>
       </c>
     </row>
     <row r="269">
@@ -6353,7 +6353,7 @@
         <v>1</v>
       </c>
       <c r="F269" t="n">
-        <v>3.536021665922123e-81</v>
+        <v>1.905814995064013e-45</v>
       </c>
     </row>
     <row r="270">
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>3.640943162817839e-77</v>
+        <v>1.567785390390113e-42</v>
       </c>
     </row>
     <row r="271">
@@ -6397,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="F271" t="n">
-        <v>1.443907239692218e-49</v>
+        <v>7.635911659078964e-23</v>
       </c>
     </row>
     <row r="272">
@@ -6419,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="F272" t="n">
-        <v>3.395024674866315e-120</v>
+        <v>1.777031624077567e-75</v>
       </c>
     </row>
     <row r="273">
@@ -6441,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="F273" t="n">
-        <v>3.720676233907525e-81</v>
+        <v>1.092173670081668e-49</v>
       </c>
     </row>
     <row r="274">
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="B274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D274" t="n">
         <v>1</v>
@@ -6463,7 +6463,7 @@
         <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>8.181046080867267e-125</v>
+        <v>3.319660230602048e-75</v>
       </c>
     </row>
     <row r="275">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="B275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275" t="n">
         <v>1</v>
@@ -6485,7 +6485,7 @@
         <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>2.211668721742538e-124</v>
+        <v>2.930894244344258e-72</v>
       </c>
     </row>
     <row r="276">
@@ -6507,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="F276" t="n">
-        <v>3.313970069565536e-111</v>
+        <v>1.009127814939101e-61</v>
       </c>
     </row>
     <row r="277">
@@ -6529,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="F277" t="n">
-        <v>2.871306364170116e-70</v>
+        <v>1.201407640033275e-35</v>
       </c>
     </row>
     <row r="278">
@@ -6548,10 +6548,10 @@
         <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>0.9999999999404049</v>
       </c>
       <c r="F278" t="n">
-        <v>3.697905730434467e-27</v>
+        <v>5.959508618057455e-11</v>
       </c>
     </row>
     <row r="279">
@@ -6595,7 +6595,7 @@
         <v>1</v>
       </c>
       <c r="F280" t="n">
-        <v>2.148451556055198e-86</v>
+        <v>6.916880142174007e-55</v>
       </c>
     </row>
     <row r="281">
@@ -6617,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>2.600747995354838e-94</v>
+        <v>1.009053598886692e-64</v>
       </c>
     </row>
     <row r="282">
@@ -6639,7 +6639,7 @@
         <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>1.653234063907241e-114</v>
+        <v>1.676130779701455e-70</v>
       </c>
     </row>
     <row r="283">
@@ -6661,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>4.684503877960972e-91</v>
+        <v>8.582824947717665e-51</v>
       </c>
     </row>
     <row r="284">
@@ -6674,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D284" t="n">
         <v>1</v>
@@ -6683,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="F284" t="n">
-        <v>1.084152831942607e-94</v>
+        <v>1.076714634396822e-57</v>
       </c>
     </row>
     <row r="285">
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D285" t="n">
         <v>1</v>
@@ -6705,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="F285" t="n">
-        <v>1.644487284740848e-75</v>
+        <v>1.241174180286148e-52</v>
       </c>
     </row>
     <row r="286">
@@ -6727,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>4.975011334829153e-74</v>
+        <v>2.036134186917154e-54</v>
       </c>
     </row>
     <row r="287">
@@ -6740,7 +6740,7 @@
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
         <v>1</v>
@@ -6749,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="F287" t="n">
-        <v>3.805514365852717e-84</v>
+        <v>2.784582011963818e-49</v>
       </c>
     </row>
     <row r="288">
@@ -6771,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>2.640043300741546e-103</v>
+        <v>1.649517017519102e-64</v>
       </c>
     </row>
     <row r="289">
@@ -6793,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1.094627204448849e-59</v>
+        <v>4.430018410827687e-37</v>
       </c>
     </row>
     <row r="290">
@@ -6815,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="F290" t="n">
-        <v>7.868852144484467e-90</v>
+        <v>3.426849466591519e-58</v>
       </c>
     </row>
     <row r="291">
@@ -6837,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>2.389252751912886e-63</v>
+        <v>1.221240102079025e-41</v>
       </c>
     </row>
     <row r="292">
@@ -6881,7 +6881,7 @@
         <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>1.17018341308291e-70</v>
+        <v>2.670699200576066e-50</v>
       </c>
     </row>
     <row r="294">
@@ -6922,10 +6922,10 @@
         <v>3</v>
       </c>
       <c r="E295" t="n">
-        <v>0.4144874612827859</v>
+        <v>0.003558576153247839</v>
       </c>
       <c r="F295" t="n">
-        <v>0.5855125387172141</v>
+        <v>0.9964414238467522</v>
       </c>
     </row>
     <row r="296">
@@ -6947,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="F296" t="n">
-        <v>1.420304415433706e-59</v>
+        <v>1.813435186897819e-36</v>
       </c>
     </row>
     <row r="297">
@@ -6991,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="F298" t="n">
-        <v>9.500547906193115e-73</v>
+        <v>1.204634204510237e-43</v>
       </c>
     </row>
     <row r="299">
@@ -7013,7 +7013,7 @@
         <v>1</v>
       </c>
       <c r="F299" t="n">
-        <v>2.119077035752054e-89</v>
+        <v>7.151847494819296e-59</v>
       </c>
     </row>
     <row r="300">
@@ -7054,10 +7054,10 @@
         <v>3</v>
       </c>
       <c r="E301" t="n">
-        <v>0.01570406432302596</v>
+        <v>0.00728369852665367</v>
       </c>
       <c r="F301" t="n">
-        <v>0.984295935676974</v>
+        <v>0.9927163014733463</v>
       </c>
     </row>
     <row r="302">
@@ -7079,7 +7079,7 @@
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>1.366772373646436e-36</v>
+        <v>3.871543392843321e-19</v>
       </c>
     </row>
     <row r="303">
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="B304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C304" t="n">
         <v>1</v>
@@ -7123,7 +7123,7 @@
         <v>1</v>
       </c>
       <c r="F304" t="n">
-        <v>1.026201572258133e-83</v>
+        <v>2.718185798961908e-54</v>
       </c>
     </row>
     <row r="305">
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="B305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C305" t="n">
         <v>1</v>
@@ -7145,7 +7145,7 @@
         <v>1</v>
       </c>
       <c r="F305" t="n">
-        <v>9.378511513329239e-82</v>
+        <v>4.562814881060605e-52</v>
       </c>
     </row>
     <row r="306">
@@ -7167,7 +7167,7 @@
         <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>7.748635088255171e-71</v>
+        <v>7.854765562315045e-40</v>
       </c>
     </row>
     <row r="307">
@@ -7211,7 +7211,7 @@
         <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>3.304995144299605e-89</v>
+        <v>7.605599737852427e-42</v>
       </c>
     </row>
     <row r="309">
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="F309" t="n">
-        <v>2.826832091757825e-72</v>
+        <v>2.049866209141783e-25</v>
       </c>
     </row>
     <row r="310">
@@ -7252,10 +7252,10 @@
         <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>1</v>
+        <v>0.9999999335651204</v>
       </c>
       <c r="F310" t="n">
-        <v>3.413488834297605e-44</v>
+        <v>6.643487955606443e-08</v>
       </c>
     </row>
     <row r="311">
@@ -7277,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>7.05300437947001e-96</v>
+        <v>1.320705189024616e-35</v>
       </c>
     </row>
   </sheetData>
